--- a/data/input/sku_master.xlsx
+++ b/data/input/sku_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C6830BC-D0D3-4AA3-84B9-EE5C05804355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A85C6266-F9AE-4AD6-AC76-677040D8152A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6332" uniqueCount="3041">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6333" uniqueCount="3042">
   <si>
     <t>FBA SKU</t>
   </si>
@@ -9160,6 +9160,9 @@
   </si>
   <si>
     <t>B0BVHZ5MKZ</t>
+  </si>
+  <si>
+    <t>B0H2FCK54H</t>
   </si>
 </sst>
 </file>
@@ -9270,7 +9273,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -9326,6 +9329,7 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -37147,7 +37151,9 @@
         <v>2869</v>
       </c>
       <c r="B898" s="5"/>
-      <c r="C898" s="5"/>
+      <c r="C898" s="19" t="s">
+        <v>3041</v>
+      </c>
       <c r="D898" s="5" t="s">
         <v>521</v>
       </c>

--- a/data/input/sku_master.xlsx
+++ b/data/input/sku_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A85C6266-F9AE-4AD6-AC76-677040D8152A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FE361CE-6714-46C3-BB2A-17E99E588D6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6333" uniqueCount="3042">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6336" uniqueCount="3045">
   <si>
     <t>FBA SKU</t>
   </si>
@@ -9163,6 +9163,15 @@
   </si>
   <si>
     <t>B0H2FCK54H</t>
+  </si>
+  <si>
+    <t>B0H2ZCQFTZ</t>
+  </si>
+  <si>
+    <t>B0H2Z6R6V8</t>
+  </si>
+  <si>
+    <t>B0H3LHF2WW</t>
   </si>
 </sst>
 </file>
@@ -9329,7 +9338,9 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -36744,7 +36755,9 @@
         <v>2842</v>
       </c>
       <c r="B885" s="5"/>
-      <c r="C885" s="5"/>
+      <c r="C885" s="19" t="s">
+        <v>3042</v>
+      </c>
       <c r="D885" s="5" t="s">
         <v>521</v>
       </c>
@@ -36771,7 +36784,9 @@
         <v>2844</v>
       </c>
       <c r="B886" s="5"/>
-      <c r="C886" s="5"/>
+      <c r="C886" s="19" t="s">
+        <v>3043</v>
+      </c>
       <c r="D886" s="5" t="s">
         <v>521</v>
       </c>
@@ -37151,7 +37166,7 @@
         <v>2869</v>
       </c>
       <c r="B898" s="5"/>
-      <c r="C898" s="19" t="s">
+      <c r="C898" t="s">
         <v>3041</v>
       </c>
       <c r="D898" s="5" t="s">
@@ -37593,7 +37608,9 @@
         <v>3030</v>
       </c>
       <c r="B914" s="5"/>
-      <c r="C914" s="5"/>
+      <c r="C914" s="19" t="s">
+        <v>3044</v>
+      </c>
       <c r="D914" s="5" t="s">
         <v>521</v>
       </c>

--- a/data/input/sku_master.xlsx
+++ b/data/input/sku_master.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCAA88DE-273D-457E-A148-7192D821578A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78574D12-5D4A-40AE-9E54-B7328B11C4AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
@@ -91972,7 +91972,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M3007" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}"/>
   <conditionalFormatting sqref="A1">
     <cfRule type="duplicateValues" dxfId="33" priority="103"/>
   </conditionalFormatting>

--- a/data/input/sku_master.xlsx
+++ b/data/input/sku_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78574D12-5D4A-40AE-9E54-B7328B11C4AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B7A349-E5A4-4EFC-98D9-FA3DF89A7FB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16769" uniqueCount="9295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16781" uniqueCount="9298">
   <si>
     <t>FBA SKU</t>
   </si>
@@ -27922,6 +27922,15 @@
   </si>
   <si>
     <t>B0FTKJC5JW</t>
+  </si>
+  <si>
+    <t>FBA80181</t>
+  </si>
+  <si>
+    <t>AI-04 Pro</t>
+  </si>
+  <si>
+    <t>B0H2FNV2RC</t>
   </si>
 </sst>
 </file>
@@ -28783,7 +28792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}">
-  <dimension ref="A1:M3007"/>
+  <dimension ref="A1:M3009"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.88671875" style="2" bestFit="1" customWidth="1"/>
@@ -91716,7 +91725,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="2993" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2993" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2993" s="2" t="s">
         <v>7203</v>
       </c>
@@ -91733,7 +91742,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="2994" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2994" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2994" s="2" t="s">
         <v>7204</v>
       </c>
@@ -91750,7 +91759,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="2995" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2995" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2995" s="2" t="s">
         <v>7205</v>
       </c>
@@ -91767,7 +91776,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="2996" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2996" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2996" s="2" t="s">
         <v>7206</v>
       </c>
@@ -91784,7 +91793,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="2997" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2997" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2997" s="2" t="s">
         <v>7207</v>
       </c>
@@ -91801,7 +91810,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="2998" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2998" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2998" s="2">
         <v>0</v>
       </c>
@@ -91818,7 +91827,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="2999" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2999" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2999" s="2">
         <v>0</v>
       </c>
@@ -91835,7 +91844,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="3000" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3000" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3000" s="2" t="s">
         <v>7208</v>
       </c>
@@ -91852,7 +91861,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="3001" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3001" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3001" s="2" t="s">
         <v>7209</v>
       </c>
@@ -91869,7 +91878,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="3002" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3002" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3002" s="2" t="s">
         <v>7210</v>
       </c>
@@ -91886,7 +91895,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="3003" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3003" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3003" s="2" t="s">
         <v>7211</v>
       </c>
@@ -91903,7 +91912,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="3004" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3004" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3004" s="2" t="s">
         <v>7212</v>
       </c>
@@ -91920,7 +91929,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="3005" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3005" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3005" s="2" t="s">
         <v>7213</v>
       </c>
@@ -91937,7 +91946,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="3006" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3006" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3006" s="2" t="s">
         <v>7214</v>
       </c>
@@ -91954,7 +91963,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="3007" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3007" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3007" s="2" t="s">
         <v>7215</v>
       </c>
@@ -91969,6 +91978,46 @@
       </c>
       <c r="J3007" s="5" t="s">
         <v>2645</v>
+      </c>
+    </row>
+    <row r="3008" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3008" s="2" t="s">
+        <v>9295</v>
+      </c>
+      <c r="D3008" s="5" t="s">
+        <v>521</v>
+      </c>
+      <c r="E3008" s="2" t="s">
+        <v>9296</v>
+      </c>
+      <c r="G3008" s="2" t="s">
+        <v>2954</v>
+      </c>
+      <c r="J3008" s="2" t="s">
+        <v>1098</v>
+      </c>
+      <c r="K3008" s="2" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="3009" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3009" s="2" t="s">
+        <v>2868</v>
+      </c>
+      <c r="C3009" s="2" t="s">
+        <v>9297</v>
+      </c>
+      <c r="D3009" s="5" t="s">
+        <v>521</v>
+      </c>
+      <c r="E3009" s="2" t="s">
+        <v>2896</v>
+      </c>
+      <c r="J3009" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="K3009" s="2" t="s">
+        <v>2917</v>
       </c>
     </row>
   </sheetData>

--- a/data/input/sku_master.xlsx
+++ b/data/input/sku_master.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B7A349-E5A4-4EFC-98D9-FA3DF89A7FB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38349CF2-A5BD-4384-B53C-6283B92C9B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16781" uniqueCount="9298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16784" uniqueCount="9300">
   <si>
     <t>FBA SKU</t>
   </si>
@@ -27931,13 +27931,19 @@
   </si>
   <si>
     <t>B0H2FNV2RC</t>
+  </si>
+  <si>
+    <t>FBA80215</t>
+  </si>
+  <si>
+    <t>SP-02</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -27983,6 +27989,12 @@
     </font>
     <font>
       <sz val="10"/>
+      <color theme="1"/>
+      <name val="Bookman Old Style"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Bookman Old Style"/>
       <family val="1"/>
@@ -28047,7 +28059,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -28109,11 +28121,98 @@
     <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="34">
+  <dxfs count="42">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -28792,7 +28891,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}">
-  <dimension ref="A1:M3009"/>
+  <dimension ref="A1:M3010"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.88671875" style="2" bestFit="1" customWidth="1"/>
@@ -92020,72 +92119,93 @@
         <v>2917</v>
       </c>
     </row>
+    <row r="3010" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3010" s="2" t="s">
+        <v>9298</v>
+      </c>
+      <c r="D3010" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3010" s="21" t="s">
+        <v>9299</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="33" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="111"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A95">
-    <cfRule type="duplicateValues" dxfId="32" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A144:A147">
-    <cfRule type="duplicateValues" dxfId="30" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A837:A840">
-    <cfRule type="duplicateValues" dxfId="29" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A126:B126">
-    <cfRule type="duplicateValues" dxfId="28" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A127:B143">
-    <cfRule type="duplicateValues" dxfId="27" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B59 A96:A107 A109:A125 A21:A29 B84 A3:A19 B35 A31:A94">
-    <cfRule type="duplicateValues" dxfId="26" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B95">
-    <cfRule type="duplicateValues" dxfId="25" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B125">
-    <cfRule type="duplicateValues" dxfId="23" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C95">
-    <cfRule type="duplicateValues" dxfId="22" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C98">
-    <cfRule type="duplicateValues" dxfId="20" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E127:E143">
-    <cfRule type="duplicateValues" dxfId="18" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E144">
-    <cfRule type="duplicateValues" dxfId="17" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E400">
-    <cfRule type="duplicateValues" dxfId="16" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="7" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="8" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="15" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="16" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E837:E840">
-    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="16" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="15" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="24" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="23" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:I1">
-    <cfRule type="duplicateValues" dxfId="0" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="115"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3010">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="7" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="8" stopIfTrue="1"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A124" r:id="rId1" display="https://sellercentral.amazon.in/skucentral?mSku=FBA79849&amp;condition=New&amp;ref_=myp_skuc" xr:uid="{F5F7F880-2E3B-44E2-BABD-2E8055A5AAE6}"/>

--- a/data/input/sku_master.xlsx
+++ b/data/input/sku_master.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38349CF2-A5BD-4384-B53C-6283B92C9B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A73E827F-C73A-42B0-B756-90949A21AEDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$3007</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$3009</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16784" uniqueCount="9300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16934" uniqueCount="9390">
   <si>
     <t>FBA SKU</t>
   </si>
@@ -27937,6 +27937,276 @@
   </si>
   <si>
     <t>SP-02</t>
+  </si>
+  <si>
+    <t>FBA80220</t>
+  </si>
+  <si>
+    <t>B0GDKG6QRV</t>
+  </si>
+  <si>
+    <t>AR11742</t>
+  </si>
+  <si>
+    <t>FBA80221</t>
+  </si>
+  <si>
+    <t>B0GDX6M95H</t>
+  </si>
+  <si>
+    <t>AR11743</t>
+  </si>
+  <si>
+    <t>FBA80222</t>
+  </si>
+  <si>
+    <t>B0GHJMFM23</t>
+  </si>
+  <si>
+    <t>AR11763</t>
+  </si>
+  <si>
+    <t>FBA80223</t>
+  </si>
+  <si>
+    <t>B0GHD9GN9C</t>
+  </si>
+  <si>
+    <t>AR11769</t>
+  </si>
+  <si>
+    <t>FBA80224</t>
+  </si>
+  <si>
+    <t>B0GTC9238R</t>
+  </si>
+  <si>
+    <t>AX4300</t>
+  </si>
+  <si>
+    <t>FBA80225</t>
+  </si>
+  <si>
+    <t>B0GTC9PS5Z</t>
+  </si>
+  <si>
+    <t>AX7178SET</t>
+  </si>
+  <si>
+    <t>FBA80226</t>
+  </si>
+  <si>
+    <t>B07SV6HR8T</t>
+  </si>
+  <si>
+    <t>DZ2237</t>
+  </si>
+  <si>
+    <t>FBA80227</t>
+  </si>
+  <si>
+    <t>B07SW9C6ZH</t>
+  </si>
+  <si>
+    <t>DZ2239</t>
+  </si>
+  <si>
+    <t>FBA80228</t>
+  </si>
+  <si>
+    <t>B07SYFYGR6</t>
+  </si>
+  <si>
+    <t>DZ4711</t>
+  </si>
+  <si>
+    <t>FBA80229</t>
+  </si>
+  <si>
+    <t>B07SYSQJDN</t>
+  </si>
+  <si>
+    <t>DZ4712</t>
+  </si>
+  <si>
+    <t>FBA80230</t>
+  </si>
+  <si>
+    <t>B0GTC2MW2C</t>
+  </si>
+  <si>
+    <t>ES5473</t>
+  </si>
+  <si>
+    <t>FBA80231</t>
+  </si>
+  <si>
+    <t>B0GTC3BMTN</t>
+  </si>
+  <si>
+    <t>ES5477</t>
+  </si>
+  <si>
+    <t>FBA80232</t>
+  </si>
+  <si>
+    <t>B0GTC7QS9P</t>
+  </si>
+  <si>
+    <t>ES5478</t>
+  </si>
+  <si>
+    <t>FBA80233</t>
+  </si>
+  <si>
+    <t>B0GTBY76NG</t>
+  </si>
+  <si>
+    <t>FS6166</t>
+  </si>
+  <si>
+    <t>FBA80234</t>
+  </si>
+  <si>
+    <t>B0GTCF15F4</t>
+  </si>
+  <si>
+    <t>FS6169</t>
+  </si>
+  <si>
+    <t>FBA80235</t>
+  </si>
+  <si>
+    <t>B0GF71S5WW</t>
+  </si>
+  <si>
+    <t>MK4992SET</t>
+  </si>
+  <si>
+    <t>FBA80236</t>
+  </si>
+  <si>
+    <t>B0GF7N3S44</t>
+  </si>
+  <si>
+    <t>MK4994SET</t>
+  </si>
+  <si>
+    <t>FBA80243</t>
+  </si>
+  <si>
+    <t>B0GTC998R6</t>
+  </si>
+  <si>
+    <t>MK7615</t>
+  </si>
+  <si>
+    <t>FBA80244</t>
+  </si>
+  <si>
+    <t>B0GTC4D5NP</t>
+  </si>
+  <si>
+    <t>MK7616</t>
+  </si>
+  <si>
+    <t>FBA80245</t>
+  </si>
+  <si>
+    <t>B0CLH9H16G</t>
+  </si>
+  <si>
+    <t>MK9107</t>
+  </si>
+  <si>
+    <t>FBA80246</t>
+  </si>
+  <si>
+    <t>B0CJJXL9TJ</t>
+  </si>
+  <si>
+    <t>MK9108</t>
+  </si>
+  <si>
+    <t>FBA80247</t>
+  </si>
+  <si>
+    <t>B0GTC5JGY7</t>
+  </si>
+  <si>
+    <t>MK9263</t>
+  </si>
+  <si>
+    <t>FBA80248</t>
+  </si>
+  <si>
+    <t>B0GTC9239V</t>
+  </si>
+  <si>
+    <t>MK9270SET</t>
+  </si>
+  <si>
+    <t>FBA80249</t>
+  </si>
+  <si>
+    <t>B0GTBY2FK6</t>
+  </si>
+  <si>
+    <t>MK9272SET</t>
+  </si>
+  <si>
+    <t>FBA80237</t>
+  </si>
+  <si>
+    <t>B0GF7CZNZC</t>
+  </si>
+  <si>
+    <t>MK7569</t>
+  </si>
+  <si>
+    <t>FBA80238</t>
+  </si>
+  <si>
+    <t>B0GF7BHFS4</t>
+  </si>
+  <si>
+    <t>MK7586</t>
+  </si>
+  <si>
+    <t>FBA80239</t>
+  </si>
+  <si>
+    <t>B0GTC5GQY4</t>
+  </si>
+  <si>
+    <t>MK7606</t>
+  </si>
+  <si>
+    <t>FBA80240</t>
+  </si>
+  <si>
+    <t>B0GTC2G6FF</t>
+  </si>
+  <si>
+    <t>MK7607</t>
+  </si>
+  <si>
+    <t>FBA80241</t>
+  </si>
+  <si>
+    <t>B0GTC6M3QM</t>
+  </si>
+  <si>
+    <t>MK7613</t>
+  </si>
+  <si>
+    <t>FBA80242</t>
+  </si>
+  <si>
+    <t>B0GTCB716R</t>
+  </si>
+  <si>
+    <t>MK7614</t>
   </si>
 </sst>
 </file>
@@ -28131,6 +28401,40 @@
   <dxfs count="42">
     <dxf>
       <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -28255,40 +28559,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -28891,7 +29161,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}">
-  <dimension ref="A1:M3010"/>
+  <dimension ref="A1:M3040"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.88671875" style="2" bestFit="1" customWidth="1"/>
@@ -92128,6 +92398,516 @@
       </c>
       <c r="E3010" s="21" t="s">
         <v>9299</v>
+      </c>
+    </row>
+    <row r="3011" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3011" s="2" t="s">
+        <v>9300</v>
+      </c>
+      <c r="C3011" s="2" t="s">
+        <v>9301</v>
+      </c>
+      <c r="D3011" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3011" s="2" t="s">
+        <v>9302</v>
+      </c>
+      <c r="J3011" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3012" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3012" s="2" t="s">
+        <v>9303</v>
+      </c>
+      <c r="C3012" s="2" t="s">
+        <v>9304</v>
+      </c>
+      <c r="D3012" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3012" s="2" t="s">
+        <v>9305</v>
+      </c>
+      <c r="J3012" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3013" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3013" s="2" t="s">
+        <v>9306</v>
+      </c>
+      <c r="C3013" s="2" t="s">
+        <v>9307</v>
+      </c>
+      <c r="D3013" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3013" s="2" t="s">
+        <v>9308</v>
+      </c>
+      <c r="J3013" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3014" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3014" s="2" t="s">
+        <v>9309</v>
+      </c>
+      <c r="C3014" s="2" t="s">
+        <v>9310</v>
+      </c>
+      <c r="D3014" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3014" s="2" t="s">
+        <v>9311</v>
+      </c>
+      <c r="J3014" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3015" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3015" s="2" t="s">
+        <v>9312</v>
+      </c>
+      <c r="C3015" s="2" t="s">
+        <v>9313</v>
+      </c>
+      <c r="D3015" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3015" s="2" t="s">
+        <v>9314</v>
+      </c>
+      <c r="J3015" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3016" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3016" s="2" t="s">
+        <v>9315</v>
+      </c>
+      <c r="C3016" s="2" t="s">
+        <v>9316</v>
+      </c>
+      <c r="D3016" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3016" s="2" t="s">
+        <v>9317</v>
+      </c>
+      <c r="J3016" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3017" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3017" s="2" t="s">
+        <v>9318</v>
+      </c>
+      <c r="C3017" s="2" t="s">
+        <v>9319</v>
+      </c>
+      <c r="D3017" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3017" s="2" t="s">
+        <v>9320</v>
+      </c>
+      <c r="J3017" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3018" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3018" s="2" t="s">
+        <v>9321</v>
+      </c>
+      <c r="C3018" s="2" t="s">
+        <v>9322</v>
+      </c>
+      <c r="D3018" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3018" s="2" t="s">
+        <v>9323</v>
+      </c>
+      <c r="J3018" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3019" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3019" s="2" t="s">
+        <v>9324</v>
+      </c>
+      <c r="C3019" s="2" t="s">
+        <v>9325</v>
+      </c>
+      <c r="D3019" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3019" s="2" t="s">
+        <v>9326</v>
+      </c>
+      <c r="J3019" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3020" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3020" s="2" t="s">
+        <v>9327</v>
+      </c>
+      <c r="C3020" s="2" t="s">
+        <v>9328</v>
+      </c>
+      <c r="D3020" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3020" s="2" t="s">
+        <v>9329</v>
+      </c>
+      <c r="J3020" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3021" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3021" s="2" t="s">
+        <v>9330</v>
+      </c>
+      <c r="C3021" s="2" t="s">
+        <v>9331</v>
+      </c>
+      <c r="D3021" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3021" s="2" t="s">
+        <v>9332</v>
+      </c>
+      <c r="J3021" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3022" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3022" s="2" t="s">
+        <v>9333</v>
+      </c>
+      <c r="C3022" s="2" t="s">
+        <v>9334</v>
+      </c>
+      <c r="D3022" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3022" s="2" t="s">
+        <v>9335</v>
+      </c>
+      <c r="J3022" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3023" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3023" s="2" t="s">
+        <v>9336</v>
+      </c>
+      <c r="C3023" s="2" t="s">
+        <v>9337</v>
+      </c>
+      <c r="D3023" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3023" s="2" t="s">
+        <v>9338</v>
+      </c>
+      <c r="J3023" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3024" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3024" s="2" t="s">
+        <v>9339</v>
+      </c>
+      <c r="C3024" s="2" t="s">
+        <v>9340</v>
+      </c>
+      <c r="D3024" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3024" s="2" t="s">
+        <v>9341</v>
+      </c>
+      <c r="J3024" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3025" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3025" s="2" t="s">
+        <v>9342</v>
+      </c>
+      <c r="C3025" s="2" t="s">
+        <v>9343</v>
+      </c>
+      <c r="D3025" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3025" s="2" t="s">
+        <v>9344</v>
+      </c>
+      <c r="J3025" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3026" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3026" s="2" t="s">
+        <v>9345</v>
+      </c>
+      <c r="C3026" s="2" t="s">
+        <v>9346</v>
+      </c>
+      <c r="D3026" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3026" s="2" t="s">
+        <v>9347</v>
+      </c>
+      <c r="J3026" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3027" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3027" s="2" t="s">
+        <v>9348</v>
+      </c>
+      <c r="C3027" s="2" t="s">
+        <v>9349</v>
+      </c>
+      <c r="D3027" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3027" s="2" t="s">
+        <v>9350</v>
+      </c>
+      <c r="J3027" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3028" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3028" s="2" t="s">
+        <v>9351</v>
+      </c>
+      <c r="C3028" s="2" t="s">
+        <v>9352</v>
+      </c>
+      <c r="D3028" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3028" s="2" t="s">
+        <v>9353</v>
+      </c>
+      <c r="J3028" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3029" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3029" s="2" t="s">
+        <v>9354</v>
+      </c>
+      <c r="C3029" s="2" t="s">
+        <v>9355</v>
+      </c>
+      <c r="D3029" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3029" s="2" t="s">
+        <v>9356</v>
+      </c>
+      <c r="J3029" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3030" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3030" s="2" t="s">
+        <v>9357</v>
+      </c>
+      <c r="C3030" s="2" t="s">
+        <v>9358</v>
+      </c>
+      <c r="D3030" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3030" s="2" t="s">
+        <v>9359</v>
+      </c>
+      <c r="J3030" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3031" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3031" s="2" t="s">
+        <v>9360</v>
+      </c>
+      <c r="C3031" s="2" t="s">
+        <v>9361</v>
+      </c>
+      <c r="D3031" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3031" s="2" t="s">
+        <v>9362</v>
+      </c>
+      <c r="J3031" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3032" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3032" s="2" t="s">
+        <v>9363</v>
+      </c>
+      <c r="C3032" s="2" t="s">
+        <v>9364</v>
+      </c>
+      <c r="D3032" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3032" s="2" t="s">
+        <v>9365</v>
+      </c>
+      <c r="J3032" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3033" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3033" s="2" t="s">
+        <v>9366</v>
+      </c>
+      <c r="C3033" s="2" t="s">
+        <v>9367</v>
+      </c>
+      <c r="D3033" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3033" s="2" t="s">
+        <v>9368</v>
+      </c>
+      <c r="J3033" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3034" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3034" s="2" t="s">
+        <v>9369</v>
+      </c>
+      <c r="C3034" s="2" t="s">
+        <v>9370</v>
+      </c>
+      <c r="D3034" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3034" s="2" t="s">
+        <v>9371</v>
+      </c>
+      <c r="J3034" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3035" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3035" s="2" t="s">
+        <v>9372</v>
+      </c>
+      <c r="C3035" s="2" t="s">
+        <v>9373</v>
+      </c>
+      <c r="D3035" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3035" s="2" t="s">
+        <v>9374</v>
+      </c>
+      <c r="J3035" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3036" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3036" s="2" t="s">
+        <v>9375</v>
+      </c>
+      <c r="C3036" s="2" t="s">
+        <v>9376</v>
+      </c>
+      <c r="D3036" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3036" s="2" t="s">
+        <v>9377</v>
+      </c>
+      <c r="J3036" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3037" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3037" s="2" t="s">
+        <v>9378</v>
+      </c>
+      <c r="C3037" s="2" t="s">
+        <v>9379</v>
+      </c>
+      <c r="D3037" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3037" s="2" t="s">
+        <v>9380</v>
+      </c>
+      <c r="J3037" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3038" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3038" s="2" t="s">
+        <v>9381</v>
+      </c>
+      <c r="C3038" s="2" t="s">
+        <v>9382</v>
+      </c>
+      <c r="D3038" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3038" s="2" t="s">
+        <v>9383</v>
+      </c>
+      <c r="J3038" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3039" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3039" s="2" t="s">
+        <v>9384</v>
+      </c>
+      <c r="C3039" s="2" t="s">
+        <v>9385</v>
+      </c>
+      <c r="D3039" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3039" s="2" t="s">
+        <v>9386</v>
+      </c>
+      <c r="J3039" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3040" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3040" s="2" t="s">
+        <v>9387</v>
+      </c>
+      <c r="C3040" s="2" t="s">
+        <v>9388</v>
+      </c>
+      <c r="D3040" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3040" s="2" t="s">
+        <v>9389</v>
+      </c>
+      <c r="J3040" s="5" t="s">
+        <v>2645</v>
       </c>
     </row>
   </sheetData>
@@ -92165,8 +92945,8 @@
     <cfRule type="duplicateValues" dxfId="29" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C98">
-    <cfRule type="duplicateValues" dxfId="28" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E127:E143">
     <cfRule type="duplicateValues" dxfId="26" priority="71"/>
@@ -92186,26 +92966,26 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="E837:E840">
     <cfRule type="duplicateValues" dxfId="16" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="24" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="23" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="20"/>
     <cfRule type="duplicateValues" dxfId="12" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="23" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="24" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:I1">
     <cfRule type="duplicateValues" dxfId="8" priority="115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3010">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="7" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="8" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="7" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="8" stopIfTrue="1"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A124" r:id="rId1" display="https://sellercentral.amazon.in/skucentral?mSku=FBA79849&amp;condition=New&amp;ref_=myp_skuc" xr:uid="{F5F7F880-2E3B-44E2-BABD-2E8055A5AAE6}"/>

--- a/data/input/sku_master.xlsx
+++ b/data/input/sku_master.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51803002-810A-4C69-AF65-5A946AAF9B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C8D269A-2426-4FEF-96B9-4F109B80077E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16934" uniqueCount="9390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16937" uniqueCount="9390">
   <si>
     <t>FBA SKU</t>
   </si>
@@ -55810,9 +55810,15 @@
       <c r="G882" s="5"/>
       <c r="H882" s="5"/>
       <c r="I882" s="5"/>
-      <c r="J882" s="5"/>
-      <c r="K882" s="5"/>
-      <c r="L882" s="5"/>
+      <c r="J882" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="K882" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="L882" s="5" t="s">
+        <v>369</v>
+      </c>
       <c r="M882" s="15"/>
     </row>
     <row r="883" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">

--- a/data/input/sku_master.xlsx
+++ b/data/input/sku_master.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\Nitesh Gdrive\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C8D269A-2426-4FEF-96B9-4F109B80077E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BD50C83-77EA-4CCF-BBB2-7998FBC52201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$3040</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$3041</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16937" uniqueCount="9390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16950" uniqueCount="9393">
   <si>
     <t>FBA SKU</t>
   </si>
@@ -28207,6 +28207,15 @@
   </si>
   <si>
     <t>MK7614</t>
+  </si>
+  <si>
+    <t>B0GYSS16FJ</t>
+  </si>
+  <si>
+    <t>FBA80111</t>
+  </si>
+  <si>
+    <t>MR-01_Part</t>
   </si>
 </sst>
 </file>
@@ -29161,7 +29170,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}">
-  <dimension ref="A1:M3040"/>
+  <dimension ref="A1:M3041"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.88671875" style="2" bestFit="1" customWidth="1"/>
@@ -55694,8 +55703,12 @@
       <c r="G878" s="5"/>
       <c r="H878" s="5"/>
       <c r="I878" s="5"/>
-      <c r="J878" s="5"/>
-      <c r="K878" s="5"/>
+      <c r="J878" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="K878" s="6" t="s">
+        <v>357</v>
+      </c>
       <c r="L878" s="5"/>
       <c r="M878" s="15"/>
     </row>
@@ -55725,8 +55738,12 @@
       <c r="I879" s="5" t="s">
         <v>2975</v>
       </c>
-      <c r="J879" s="5"/>
-      <c r="K879" s="5"/>
+      <c r="J879" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="K879" s="6" t="s">
+        <v>362</v>
+      </c>
       <c r="L879" s="5"/>
       <c r="M879" s="15"/>
     </row>
@@ -55756,8 +55773,12 @@
       <c r="I880" s="5" t="s">
         <v>2976</v>
       </c>
-      <c r="J880" s="5"/>
-      <c r="K880" s="5"/>
+      <c r="J880" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="K880" s="6" t="s">
+        <v>360</v>
+      </c>
       <c r="L880" s="5"/>
       <c r="M880" s="15"/>
     </row>
@@ -55787,8 +55808,12 @@
       <c r="I881" s="5" t="s">
         <v>2977</v>
       </c>
-      <c r="J881" s="5"/>
-      <c r="K881" s="5"/>
+      <c r="J881" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="K881" s="6" t="s">
+        <v>360</v>
+      </c>
       <c r="L881" s="5"/>
       <c r="M881" s="15"/>
     </row>
@@ -55810,15 +55835,13 @@
       <c r="G882" s="5"/>
       <c r="H882" s="5"/>
       <c r="I882" s="5"/>
-      <c r="J882" s="6" t="s">
+      <c r="J882" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="K882" s="6" t="s">
+      <c r="K882" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="L882" s="5" t="s">
-        <v>369</v>
-      </c>
+      <c r="L882" s="5"/>
       <c r="M882" s="15"/>
     </row>
     <row r="883" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -55847,8 +55870,12 @@
       <c r="I883" s="5" t="s">
         <v>2978</v>
       </c>
-      <c r="J883" s="5"/>
-      <c r="K883" s="5"/>
+      <c r="J883" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="K883" s="6" t="s">
+        <v>362</v>
+      </c>
       <c r="L883" s="5"/>
       <c r="M883" s="15"/>
     </row>
@@ -92914,6 +92941,20 @@
       </c>
       <c r="J3040" s="5" t="s">
         <v>2645</v>
+      </c>
+    </row>
+    <row r="3041" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3041" s="2" t="s">
+        <v>9391</v>
+      </c>
+      <c r="C3041" s="2" t="s">
+        <v>9390</v>
+      </c>
+      <c r="D3041" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3041" s="2" t="s">
+        <v>9392</v>
       </c>
     </row>
   </sheetData>

--- a/data/input/sku_master.xlsx
+++ b/data/input/sku_master.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\Nitesh Gdrive\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BD50C83-77EA-4CCF-BBB2-7998FBC52201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF4BFCDE-E1E9-45B4-A126-9F05DC20DC2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
@@ -19,6 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$3041</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16950" uniqueCount="9393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16952" uniqueCount="9393">
   <si>
     <t>FBA SKU</t>
   </si>
@@ -55703,12 +55704,8 @@
       <c r="G878" s="5"/>
       <c r="H878" s="5"/>
       <c r="I878" s="5"/>
-      <c r="J878" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="K878" s="6" t="s">
-        <v>357</v>
-      </c>
+      <c r="J878" s="5"/>
+      <c r="K878" s="5"/>
       <c r="L878" s="5"/>
       <c r="M878" s="15"/>
     </row>
@@ -55738,12 +55735,8 @@
       <c r="I879" s="5" t="s">
         <v>2975</v>
       </c>
-      <c r="J879" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="K879" s="6" t="s">
-        <v>362</v>
-      </c>
+      <c r="J879" s="5"/>
+      <c r="K879" s="5"/>
       <c r="L879" s="5"/>
       <c r="M879" s="15"/>
     </row>
@@ -55773,13 +55766,15 @@
       <c r="I880" s="5" t="s">
         <v>2976</v>
       </c>
-      <c r="J880" s="5" t="s">
+      <c r="J880" s="6" t="s">
         <v>355</v>
       </c>
       <c r="K880" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="L880" s="5"/>
+      <c r="L880" s="5" t="s">
+        <v>393</v>
+      </c>
       <c r="M880" s="15"/>
     </row>
     <row r="881" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -55808,13 +55803,15 @@
       <c r="I881" s="5" t="s">
         <v>2977</v>
       </c>
-      <c r="J881" s="5" t="s">
+      <c r="J881" s="6" t="s">
         <v>355</v>
       </c>
       <c r="K881" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="L881" s="5"/>
+      <c r="L881" s="5" t="s">
+        <v>393</v>
+      </c>
       <c r="M881" s="15"/>
     </row>
     <row r="882" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -55835,13 +55832,15 @@
       <c r="G882" s="5"/>
       <c r="H882" s="5"/>
       <c r="I882" s="5"/>
-      <c r="J882" s="5" t="s">
+      <c r="J882" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="K882" s="5" t="s">
+      <c r="K882" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="L882" s="5"/>
+      <c r="L882" s="5" t="s">
+        <v>369</v>
+      </c>
       <c r="M882" s="15"/>
     </row>
     <row r="883" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -55870,11 +55869,9 @@
       <c r="I883" s="5" t="s">
         <v>2978</v>
       </c>
-      <c r="J883" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="K883" s="6" t="s">
-        <v>362</v>
+      <c r="J883" s="5"/>
+      <c r="K883" s="5" t="s">
+        <v>367</v>
       </c>
       <c r="L883" s="5"/>
       <c r="M883" s="15"/>
@@ -56842,8 +56839,12 @@
       <c r="G916" s="5"/>
       <c r="H916" s="5"/>
       <c r="I916" s="5"/>
-      <c r="J916" s="5"/>
-      <c r="K916" s="5"/>
+      <c r="J916" s="16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K916" s="16" t="s">
+        <v>1293</v>
+      </c>
       <c r="L916" s="5"/>
       <c r="M916" s="15"/>
     </row>
@@ -56911,8 +56912,12 @@
       <c r="G919" s="5"/>
       <c r="H919" s="5"/>
       <c r="I919" s="5"/>
-      <c r="J919" s="5"/>
-      <c r="K919" s="5"/>
+      <c r="J919" s="16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K919" s="16" t="s">
+        <v>1293</v>
+      </c>
       <c r="L919" s="5"/>
       <c r="M919" s="15"/>
     </row>

--- a/data/input/sku_master.xlsx
+++ b/data/input/sku_master.xlsx
@@ -8,15 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\Nitesh Gdrive\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{976D9C33-F683-4FF6-A434-5C4FEDC16DE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E66BC89-0C0A-45A7-9C57-06BC79507239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$3041</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$3041</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16960" uniqueCount="9392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17439" uniqueCount="9404">
   <si>
     <t>FBA SKU</t>
   </si>
@@ -28213,6 +28216,42 @@
   </si>
   <si>
     <t>MR-01_Part</t>
+  </si>
+  <si>
+    <t>IXD Non-Hazmat</t>
+  </si>
+  <si>
+    <t>IXD Hazmat</t>
+  </si>
+  <si>
+    <t>Non-IXD Non Hazmat</t>
+  </si>
+  <si>
+    <t>MC</t>
+  </si>
+  <si>
+    <t>Spot Cleaner</t>
+  </si>
+  <si>
+    <t>Car Air Purifier</t>
+  </si>
+  <si>
+    <t>Spares</t>
+  </si>
+  <si>
+    <t>Hazmat Type 1p</t>
+  </si>
+  <si>
+    <t>Hazmat Type 3p</t>
+  </si>
+  <si>
+    <t>DP - Charges</t>
+  </si>
+  <si>
+    <t>1p Unit Cost - (Months Name)</t>
+  </si>
+  <si>
+    <t>T-Code (EAN)</t>
   </si>
 </sst>
 </file>
@@ -28335,7 +28374,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -28400,6 +28439,12 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -28407,6 +28452,18 @@
   <dxfs count="42">
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -28479,28 +28536,6 @@
     </dxf>
     <dxf>
       <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -28525,6 +28560,16 @@
       <font>
         <condense val="0"/>
         <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -28850,6 +28895,378 @@
 </styleSheet>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="AA"/>
+      <sheetName val="WM"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>ASIN</v>
+          </cell>
+          <cell r="O1" t="str">
+            <v>Master Carton</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="B2" t="str">
+            <v>B0CPFS24ML</v>
+          </cell>
+          <cell r="O2">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>B0BFWD6SNF</v>
+          </cell>
+          <cell r="O3">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="B4" t="str">
+            <v>B0BFVMDJ2K</v>
+          </cell>
+          <cell r="O4">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="B5" t="str">
+            <v>B0BFW59TRG</v>
+          </cell>
+          <cell r="O5">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="B6" t="str">
+            <v>B0BFVNS8HS</v>
+          </cell>
+          <cell r="O6">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="B7" t="str">
+            <v>B0CPT3Q25C</v>
+          </cell>
+          <cell r="O7">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="B8" t="str">
+            <v>B0CPT34B2L</v>
+          </cell>
+          <cell r="O8">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="B9" t="str">
+            <v>B0CPT2NY5M</v>
+          </cell>
+          <cell r="O9">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="B10" t="str">
+            <v>B0BF4VRJJ1</v>
+          </cell>
+          <cell r="O10">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="B11" t="str">
+            <v>B0BF4TKQKN</v>
+          </cell>
+          <cell r="O11">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="B12" t="str">
+            <v>B0DC3JRBW1</v>
+          </cell>
+          <cell r="O12">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="B13" t="str">
+            <v>B0DQ4ZK2WQ</v>
+          </cell>
+          <cell r="O13">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="B14" t="str">
+            <v>B0DQ51R95T</v>
+          </cell>
+          <cell r="O14">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="B15" t="str">
+            <v>B0DQ4YWSMC</v>
+          </cell>
+          <cell r="O15">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="B16" t="str">
+            <v>B0BF4S7V8C</v>
+          </cell>
+          <cell r="O16">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="B17" t="str">
+            <v>B0CPT25SD8</v>
+          </cell>
+          <cell r="O17">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="B18" t="str">
+            <v>B0BMV1WPHL</v>
+          </cell>
+          <cell r="O18">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="B19" t="str">
+            <v>B0BF4T7SWK</v>
+          </cell>
+          <cell r="O19">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="B20" t="str">
+            <v>B0DQ1PKNSP</v>
+          </cell>
+          <cell r="O20">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="B21" t="str">
+            <v>B0DQ1NV8D2</v>
+          </cell>
+          <cell r="O21">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="B22" t="str">
+            <v>B0CPFPT6DZ</v>
+          </cell>
+          <cell r="O22">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="B23" t="str">
+            <v>B0CPFN27Z2</v>
+          </cell>
+          <cell r="O23">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="B24" t="str">
+            <v>B0DB5VG39T</v>
+          </cell>
+          <cell r="O24">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="B25" t="str">
+            <v>B0DB5VVPSB</v>
+          </cell>
+          <cell r="O25">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="B26" t="str">
+            <v>B0DB5W4TCP</v>
+          </cell>
+          <cell r="O26">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="B27" t="str">
+            <v>B0DB5YTQZV</v>
+          </cell>
+          <cell r="O27">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="B28" t="str">
+            <v>B0DP2WC5VW</v>
+          </cell>
+          <cell r="O28">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="B29" t="str">
+            <v>B0DP2VVRND</v>
+          </cell>
+          <cell r="O29">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="B30" t="str">
+            <v>B0DP313R77</v>
+          </cell>
+          <cell r="O30">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="B31" t="str">
+            <v>B0DP2Z5DQ9</v>
+          </cell>
+          <cell r="O31">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="B32" t="str">
+            <v>B0DP3194QN</v>
+          </cell>
+          <cell r="O32">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="B33" t="str">
+            <v>B0DP32F346</v>
+          </cell>
+          <cell r="O33">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="B34" t="str">
+            <v>B0FN4FHH5Y</v>
+          </cell>
+          <cell r="O34">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="B35" t="str">
+            <v>B0FN4HDBN5</v>
+          </cell>
+          <cell r="O35">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="B36" t="str">
+            <v>B0FN4FPJ83</v>
+          </cell>
+          <cell r="O36">
+            <v>15</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="B37" t="str">
+            <v>B0FN4GQ9HT</v>
+          </cell>
+          <cell r="O37">
+            <v>24</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="B38" t="str">
+            <v>B0FN4D3C89</v>
+          </cell>
+          <cell r="O38">
+            <v>36</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="B39" t="str">
+            <v>B0FN4DSQ6P</v>
+          </cell>
+          <cell r="O39">
+            <v>18</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="B40" t="str">
+            <v>B0FHVWHQHR</v>
+          </cell>
+          <cell r="O40">
+            <v>16</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="B41" t="str">
+            <v>B0FN4HDM6Z</v>
+          </cell>
+          <cell r="O41">
+            <v>6</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="B42" t="str">
+            <v>B0FN4JG97R</v>
+          </cell>
+          <cell r="O42">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="B43" t="str">
+            <v>B0FN81FD8M</v>
+          </cell>
+          <cell r="O43">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="B44" t="str">
+            <v>B0CPT2YJX2</v>
+          </cell>
+          <cell r="O44">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -29167,7 +29584,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}">
-  <dimension ref="A1:M3041"/>
+  <dimension ref="A1:S3041"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.88671875" style="2" bestFit="1" customWidth="1"/>
@@ -29180,10 +29597,16 @@
     <col min="11" max="11" width="50.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="30.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="27.109375" style="3" customWidth="1"/>
-    <col min="14" max="16384" width="8.88671875" style="2"/>
+    <col min="14" max="14" width="17.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.77734375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="8.88671875" style="2"/>
+    <col min="17" max="17" width="12.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="24.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -29223,8 +29646,26 @@
       <c r="M1" s="9" t="s">
         <v>437</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N1" s="1" t="s">
+        <v>9399</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>9400</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>9395</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>9401</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>9402</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>9403</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>111</v>
       </c>
@@ -29256,8 +29697,17 @@
       <c r="M2" s="10">
         <v>1260</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N2" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P2" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>21</v>
       </c>
@@ -29297,8 +29747,17 @@
       <c r="M3" s="10">
         <v>1260</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N3" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P3" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
@@ -29338,8 +29797,17 @@
       <c r="M4" s="10">
         <v>1786</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N4" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P4" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>61</v>
       </c>
@@ -29379,8 +29847,17 @@
       <c r="M5" s="10">
         <v>413</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N5" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P5" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>59</v>
       </c>
@@ -29420,8 +29897,17 @@
       <c r="M6" s="10">
         <v>418</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N6" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P6" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>71</v>
       </c>
@@ -29461,8 +29947,17 @@
       <c r="M7" s="10">
         <v>413</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N7" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P7" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>199</v>
       </c>
@@ -29494,8 +29989,17 @@
       <c r="M8" s="10">
         <v>413</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N8" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P8" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>191</v>
       </c>
@@ -29527,8 +30031,17 @@
       <c r="M9" s="10">
         <v>558</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N9" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P9" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>125</v>
       </c>
@@ -29560,8 +30073,17 @@
       <c r="M10" s="10">
         <v>633</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N10" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P10" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>99</v>
       </c>
@@ -29593,8 +30115,17 @@
       <c r="M11" s="10">
         <v>1073</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N11" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P11" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>195</v>
       </c>
@@ -29626,8 +30157,17 @@
       <c r="M12" s="10">
         <v>527</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N12" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P12" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>169</v>
       </c>
@@ -29667,8 +30207,17 @@
       <c r="M13" s="10">
         <v>1512</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N13" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P13" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>149</v>
       </c>
@@ -29700,8 +30249,17 @@
       <c r="M14" s="10">
         <v>282</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N14" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P14" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>157</v>
       </c>
@@ -29733,8 +30291,17 @@
       <c r="M15" s="10">
         <v>282</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N15" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P15" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>97</v>
       </c>
@@ -29766,8 +30333,17 @@
       <c r="M16" s="10">
         <v>193</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N16" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P16" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>13</v>
       </c>
@@ -29807,8 +30383,17 @@
       <c r="M17" s="10">
         <v>1377</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N17" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P17" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>7</v>
       </c>
@@ -29848,8 +30433,17 @@
       <c r="M18" s="10">
         <v>1162</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N18" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P18" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>129</v>
       </c>
@@ -29889,8 +30483,17 @@
       <c r="M19" s="10">
         <v>533</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N19" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P19" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>77</v>
       </c>
@@ -29930,8 +30533,17 @@
       <c r="M20" s="10">
         <v>516</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N20" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P20" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>105</v>
       </c>
@@ -29971,8 +30583,17 @@
       <c r="M21" s="10">
         <v>606</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N21" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P21" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>173</v>
       </c>
@@ -30012,8 +30633,17 @@
       <c r="M22" s="10">
         <v>987</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N22" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P22" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>81</v>
       </c>
@@ -30053,8 +30683,17 @@
       <c r="M23" s="10">
         <v>728</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N23" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P23" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>151</v>
       </c>
@@ -30094,8 +30733,17 @@
       <c r="M24" s="10">
         <v>378</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N24" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P24" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>119</v>
       </c>
@@ -30135,8 +30783,17 @@
       <c r="M25" s="10">
         <v>389</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N25" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P25" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>43</v>
       </c>
@@ -30176,8 +30833,17 @@
       <c r="M26" s="10">
         <v>2357</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N26" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P26" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>73</v>
       </c>
@@ -30217,8 +30883,17 @@
       <c r="M27" s="10">
         <v>4052</v>
       </c>
-    </row>
-    <row r="28" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N27" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P27" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>147</v>
       </c>
@@ -30258,8 +30933,17 @@
       <c r="M28" s="10">
         <v>769</v>
       </c>
-    </row>
-    <row r="29" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N28" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P28" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>167</v>
       </c>
@@ -30299,8 +30983,17 @@
       <c r="M29" s="10">
         <v>444</v>
       </c>
-    </row>
-    <row r="30" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N29" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O29" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P29" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>137</v>
       </c>
@@ -30340,8 +31033,17 @@
       <c r="M30" s="10">
         <v>490</v>
       </c>
-    </row>
-    <row r="31" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N30" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P30" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>109</v>
       </c>
@@ -30381,8 +31083,17 @@
       <c r="M31" s="10">
         <v>714</v>
       </c>
-    </row>
-    <row r="32" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N31" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P31" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>153</v>
       </c>
@@ -30422,8 +31133,17 @@
       <c r="M32" s="10">
         <v>412</v>
       </c>
-    </row>
-    <row r="33" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N32" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O32" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P32" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>143</v>
       </c>
@@ -30463,8 +31183,17 @@
       <c r="M33" s="10">
         <v>413</v>
       </c>
-    </row>
-    <row r="34" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N33" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O33" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P33" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>141</v>
       </c>
@@ -30496,8 +31225,17 @@
       <c r="M34" s="10">
         <v>448</v>
       </c>
-    </row>
-    <row r="35" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N34" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O34" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P34" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>2707</v>
       </c>
@@ -30527,8 +31265,17 @@
       <c r="M35" s="10">
         <v>448</v>
       </c>
-    </row>
-    <row r="36" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N35" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P35" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>17</v>
       </c>
@@ -30568,8 +31315,17 @@
       <c r="M36" s="10">
         <v>409</v>
       </c>
-    </row>
-    <row r="37" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N36" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O36" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P36" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>3022</v>
       </c>
@@ -30599,8 +31355,17 @@
       <c r="M37" s="10">
         <v>409</v>
       </c>
-    </row>
-    <row r="38" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N37" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P37" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>3021</v>
       </c>
@@ -30640,8 +31405,17 @@
       <c r="M38" s="10">
         <v>710</v>
       </c>
-    </row>
-    <row r="39" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N38" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P38" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="11" t="s">
         <v>513</v>
       </c>
@@ -30673,8 +31447,17 @@
       <c r="M39" s="10">
         <v>356</v>
       </c>
-    </row>
-    <row r="40" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N39" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O39" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P39" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
         <v>161</v>
       </c>
@@ -30704,8 +31487,17 @@
       <c r="M40" s="10">
         <v>356</v>
       </c>
-    </row>
-    <row r="41" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N40" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P40" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>65</v>
       </c>
@@ -30745,8 +31537,17 @@
       <c r="M41" s="10">
         <v>562</v>
       </c>
-    </row>
-    <row r="42" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N41" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O41" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P41" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>89</v>
       </c>
@@ -30786,8 +31587,17 @@
       <c r="M42" s="10">
         <v>295</v>
       </c>
-    </row>
-    <row r="43" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N42" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P42" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>87</v>
       </c>
@@ -30827,8 +31637,17 @@
       <c r="M43" s="10">
         <v>295</v>
       </c>
-    </row>
-    <row r="44" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N43" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O43" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P43" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>179</v>
       </c>
@@ -30860,8 +31679,17 @@
       <c r="M44" s="10">
         <v>193</v>
       </c>
-    </row>
-    <row r="45" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N44" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O44" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P44" s="2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>95</v>
       </c>
@@ -30901,8 +31729,17 @@
       <c r="M45" s="10">
         <v>672</v>
       </c>
-    </row>
-    <row r="46" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N45" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O45" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P45" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>29</v>
       </c>
@@ -30942,8 +31779,17 @@
       <c r="M46" s="10">
         <v>896</v>
       </c>
-    </row>
-    <row r="47" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N46" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O46" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P46" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>133</v>
       </c>
@@ -30983,8 +31829,17 @@
       <c r="M47" s="10">
         <v>868</v>
       </c>
-    </row>
-    <row r="48" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N47" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O47" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P47" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>107</v>
       </c>
@@ -31024,8 +31879,17 @@
       <c r="M48" s="10">
         <v>961</v>
       </c>
-    </row>
-    <row r="49" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N48" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O48" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P48" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>4</v>
       </c>
@@ -31065,8 +31929,17 @@
       <c r="M49" s="10">
         <v>1381</v>
       </c>
-    </row>
-    <row r="50" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N49" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O49" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P49" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
         <v>27</v>
       </c>
@@ -31106,8 +31979,17 @@
       <c r="M50" s="10">
         <v>810</v>
       </c>
-    </row>
-    <row r="51" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N50" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O50" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P50" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>165</v>
       </c>
@@ -31147,8 +32029,17 @@
       <c r="M51" s="10">
         <v>1089</v>
       </c>
-    </row>
-    <row r="52" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N51" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O51" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P51" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
         <v>171</v>
       </c>
@@ -31180,8 +32071,17 @@
       <c r="M52" s="10">
         <v>1532</v>
       </c>
-    </row>
-    <row r="53" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N52" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O52" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P52" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
         <v>33</v>
       </c>
@@ -31221,8 +32121,17 @@
       <c r="M53" s="10">
         <v>1088</v>
       </c>
-    </row>
-    <row r="54" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N53" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="O53" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P53" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
         <v>51</v>
       </c>
@@ -31262,8 +32171,17 @@
       <c r="M54" s="10">
         <v>1291</v>
       </c>
-    </row>
-    <row r="55" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N54" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O54" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P54" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
         <v>39</v>
       </c>
@@ -31303,8 +32221,17 @@
       <c r="M55" s="10">
         <v>560</v>
       </c>
-    </row>
-    <row r="56" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N55" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O55" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P55" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
         <v>177</v>
       </c>
@@ -31344,8 +32271,17 @@
       <c r="M56" s="10">
         <v>1250</v>
       </c>
-    </row>
-    <row r="57" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N56" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O56" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P56" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
         <v>139</v>
       </c>
@@ -31385,8 +32321,17 @@
       <c r="M57" s="10">
         <v>483</v>
       </c>
-    </row>
-    <row r="58" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N57" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O57" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P57" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
         <v>201</v>
       </c>
@@ -31418,8 +32363,17 @@
       <c r="M58" s="10">
         <v>2775</v>
       </c>
-    </row>
-    <row r="59" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N58" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O58" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P58" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
         <v>2675</v>
       </c>
@@ -31459,8 +32413,17 @@
       <c r="M59" s="10">
         <v>2775</v>
       </c>
-    </row>
-    <row r="60" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N59" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="O59" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P59" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
         <v>131</v>
       </c>
@@ -31500,8 +32463,17 @@
       <c r="M60" s="10">
         <v>594</v>
       </c>
-    </row>
-    <row r="61" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N60" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O60" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P60" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>49</v>
       </c>
@@ -31541,8 +32513,17 @@
       <c r="M61" s="10">
         <v>560</v>
       </c>
-    </row>
-    <row r="62" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N61" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O61" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P61" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
         <v>101</v>
       </c>
@@ -31582,8 +32563,17 @@
       <c r="M62" s="10">
         <v>865</v>
       </c>
-    </row>
-    <row r="63" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N62" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O62" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P62" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
         <v>85</v>
       </c>
@@ -31623,8 +32613,17 @@
       <c r="M63" s="10">
         <v>814</v>
       </c>
-    </row>
-    <row r="64" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N63" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O63" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P63" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
         <v>175</v>
       </c>
@@ -31664,8 +32663,17 @@
       <c r="M64" s="10">
         <v>1392</v>
       </c>
-    </row>
-    <row r="65" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N64" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O64" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P64" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
         <v>117</v>
       </c>
@@ -31705,8 +32713,17 @@
       <c r="M65" s="10">
         <v>803</v>
       </c>
-    </row>
-    <row r="66" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N65" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O65" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P65" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
         <v>145</v>
       </c>
@@ -31746,8 +32763,17 @@
       <c r="M66" s="10">
         <v>1302</v>
       </c>
-    </row>
-    <row r="67" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N66" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O66" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P66" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
         <v>155</v>
       </c>
@@ -31787,8 +32813,17 @@
       <c r="M67" s="10">
         <v>594</v>
       </c>
-    </row>
-    <row r="68" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N67" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O67" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P67" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
         <v>113</v>
       </c>
@@ -31828,8 +32863,17 @@
       <c r="M68" s="10">
         <v>716</v>
       </c>
-    </row>
-    <row r="69" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N68" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O68" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P68" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
         <v>159</v>
       </c>
@@ -31861,8 +32905,17 @@
       <c r="M69" s="10">
         <v>460</v>
       </c>
-    </row>
-    <row r="70" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N69" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O69" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P69" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
         <v>31</v>
       </c>
@@ -31902,8 +32955,17 @@
       <c r="M70" s="10">
         <v>984</v>
       </c>
-    </row>
-    <row r="71" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N70" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="O70" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P70" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
         <v>19</v>
       </c>
@@ -31943,8 +33005,17 @@
       <c r="M71" s="10">
         <v>980</v>
       </c>
-    </row>
-    <row r="72" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N71" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="O71" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P71" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
         <v>135</v>
       </c>
@@ -31984,8 +33055,17 @@
       <c r="M72" s="10">
         <v>1095</v>
       </c>
-    </row>
-    <row r="73" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N72" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O72" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P72" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
         <v>79</v>
       </c>
@@ -32025,8 +33105,17 @@
       <c r="M73" s="10">
         <v>852</v>
       </c>
-    </row>
-    <row r="74" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N73" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O73" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P73" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
         <v>115</v>
       </c>
@@ -32066,8 +33155,17 @@
       <c r="M74" s="10">
         <v>1112</v>
       </c>
-    </row>
-    <row r="75" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N74" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O74" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P74" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
         <v>83</v>
       </c>
@@ -32107,8 +33205,17 @@
       <c r="M75" s="10">
         <v>1063</v>
       </c>
-    </row>
-    <row r="76" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N75" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O75" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P75" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
         <v>11</v>
       </c>
@@ -32148,8 +33255,17 @@
       <c r="M76" s="10">
         <v>2695</v>
       </c>
-    </row>
-    <row r="77" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N76" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="O76" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P76" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
         <v>189</v>
       </c>
@@ -32181,8 +33297,17 @@
       <c r="M77" s="10">
         <v>721</v>
       </c>
-    </row>
-    <row r="78" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N77" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O77" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P77" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
         <v>25</v>
       </c>
@@ -32222,8 +33347,17 @@
       <c r="M78" s="10">
         <v>536</v>
       </c>
-    </row>
-    <row r="79" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N78" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O78" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P78" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
         <v>163</v>
       </c>
@@ -32255,8 +33389,17 @@
       <c r="M79" s="10">
         <v>1307</v>
       </c>
-    </row>
-    <row r="80" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N79" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O79" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P79" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
         <v>197</v>
       </c>
@@ -32288,8 +33431,17 @@
       <c r="M80" s="10">
         <v>709</v>
       </c>
-    </row>
-    <row r="81" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N80" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O80" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P80" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
         <v>45</v>
       </c>
@@ -32329,8 +33481,17 @@
       <c r="M81" s="10">
         <v>1345</v>
       </c>
-    </row>
-    <row r="82" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N81" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O81" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P81" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
         <v>183</v>
       </c>
@@ -32362,8 +33523,17 @@
       <c r="M82" s="10">
         <v>710</v>
       </c>
-    </row>
-    <row r="83" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N82" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O82" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P82" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
         <v>55</v>
       </c>
@@ -32395,8 +33565,17 @@
       <c r="M83" s="10">
         <v>1306</v>
       </c>
-    </row>
-    <row r="84" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N83" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O83" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P83" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
         <v>2676</v>
       </c>
@@ -32436,8 +33615,17 @@
       <c r="M84" s="10">
         <v>1306</v>
       </c>
-    </row>
-    <row r="85" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N84" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O84" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P84" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
         <v>57</v>
       </c>
@@ -32477,8 +33665,17 @@
       <c r="M85" s="10">
         <v>1014</v>
       </c>
-    </row>
-    <row r="86" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N85" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O85" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P85" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
         <v>67</v>
       </c>
@@ -32518,8 +33715,17 @@
       <c r="M86" s="10">
         <v>1039</v>
       </c>
-    </row>
-    <row r="87" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N86" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O86" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P86" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
         <v>2944</v>
       </c>
@@ -32551,8 +33757,17 @@
       <c r="M87" s="10">
         <v>1039</v>
       </c>
-    </row>
-    <row r="88" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N87" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O87" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P87" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
         <v>185</v>
       </c>
@@ -32584,8 +33799,17 @@
       <c r="M88" s="10">
         <v>1837</v>
       </c>
-    </row>
-    <row r="89" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N88" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="O88" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P88" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="6" t="s">
         <v>187</v>
       </c>
@@ -32617,8 +33841,17 @@
       <c r="M89" s="10">
         <v>890</v>
       </c>
-    </row>
-    <row r="90" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N89" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O89" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P89" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
         <v>193</v>
       </c>
@@ -32650,8 +33883,17 @@
       <c r="M90" s="10">
         <v>714</v>
       </c>
-    </row>
-    <row r="91" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N90" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O90" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P90" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
         <v>69</v>
       </c>
@@ -32683,8 +33925,17 @@
       <c r="M91" s="10">
         <v>1422</v>
       </c>
-    </row>
-    <row r="92" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N91" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O91" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P91" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
         <v>121</v>
       </c>
@@ -32724,8 +33975,17 @@
       <c r="M92" s="10">
         <v>926</v>
       </c>
-    </row>
-    <row r="93" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N92" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O92" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P92" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
         <v>181</v>
       </c>
@@ -32757,8 +34017,17 @@
       <c r="M93" s="10">
         <v>765</v>
       </c>
-    </row>
-    <row r="94" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N93" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O93" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P93" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
         <v>3024</v>
       </c>
@@ -32790,8 +34059,17 @@
       <c r="M94" s="10">
         <v>970</v>
       </c>
-    </row>
-    <row r="95" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N94" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O94" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P94" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
         <v>203</v>
       </c>
@@ -32831,8 +34109,17 @@
       <c r="M95" s="10">
         <v>954</v>
       </c>
-    </row>
-    <row r="96" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N95" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="O95" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P95" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
         <v>35</v>
       </c>
@@ -32872,8 +34159,17 @@
       <c r="M96" s="10">
         <v>1443</v>
       </c>
-    </row>
-    <row r="97" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N96" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O96" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P96" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
         <v>228</v>
       </c>
@@ -32913,8 +34209,17 @@
       <c r="M97" s="10">
         <v>371</v>
       </c>
-    </row>
-    <row r="98" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N97" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O97" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P97" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
         <v>209</v>
       </c>
@@ -32946,8 +34251,17 @@
       <c r="M98" s="10">
         <v>975</v>
       </c>
-    </row>
-    <row r="99" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N98" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O98" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P98" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
         <v>211</v>
       </c>
@@ -32979,8 +34293,17 @@
       <c r="M99" s="10">
         <v>969</v>
       </c>
-    </row>
-    <row r="100" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N99" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="O99" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P99" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
         <v>215</v>
       </c>
@@ -33012,8 +34335,17 @@
       <c r="M100" s="10">
         <v>1175</v>
       </c>
-    </row>
-    <row r="101" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N100" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O100" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P100" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
         <v>91</v>
       </c>
@@ -33053,8 +34385,17 @@
       <c r="M101" s="10">
         <v>501</v>
       </c>
-    </row>
-    <row r="102" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N101" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O101" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P101" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
         <v>207</v>
       </c>
@@ -33094,8 +34435,17 @@
       <c r="M102" s="10">
         <v>501</v>
       </c>
-    </row>
-    <row r="103" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N102" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O102" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P102" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
         <v>75</v>
       </c>
@@ -33135,8 +34485,17 @@
       <c r="M103" s="10">
         <v>3423</v>
       </c>
-    </row>
-    <row r="104" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N103" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="O103" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P103" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
         <v>41</v>
       </c>
@@ -33176,8 +34535,17 @@
       <c r="M104" s="10">
         <v>829</v>
       </c>
-    </row>
-    <row r="105" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N104" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O104" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P104" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
         <v>53</v>
       </c>
@@ -33217,8 +34585,17 @@
       <c r="M105" s="10">
         <v>818</v>
       </c>
-    </row>
-    <row r="106" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N105" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O105" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P105" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
         <v>205</v>
       </c>
@@ -33258,8 +34635,17 @@
       <c r="M106" s="10">
         <v>10158</v>
       </c>
-    </row>
-    <row r="107" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N106" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="O106" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P106" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
         <v>230</v>
       </c>
@@ -33291,8 +34677,17 @@
       <c r="M107" s="10">
         <v>6416</v>
       </c>
-    </row>
-    <row r="108" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N107" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="O107" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P107" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
         <v>514</v>
       </c>
@@ -33324,8 +34719,17 @@
       <c r="M108" s="10">
         <v>781</v>
       </c>
-    </row>
-    <row r="109" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N108" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O108" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P108" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
         <v>219</v>
       </c>
@@ -33365,8 +34769,17 @@
       <c r="M109" s="10">
         <v>436</v>
       </c>
-    </row>
-    <row r="110" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N109" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O109" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P109" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
         <v>221</v>
       </c>
@@ -33406,8 +34819,17 @@
       <c r="M110" s="10">
         <v>980</v>
       </c>
-    </row>
-    <row r="111" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N110" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O110" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P110" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
         <v>223</v>
       </c>
@@ -33439,8 +34861,17 @@
       <c r="M111" s="10">
         <v>6146</v>
       </c>
-    </row>
-    <row r="112" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N111" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O111" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P111" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
         <v>225</v>
       </c>
@@ -33480,8 +34911,17 @@
       <c r="M112" s="10">
         <v>3229</v>
       </c>
-    </row>
-    <row r="113" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N112" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O112" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P112" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
         <v>213</v>
       </c>
@@ -33513,8 +34953,17 @@
       <c r="M113" s="10">
         <v>963</v>
       </c>
-    </row>
-    <row r="114" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N113" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O113" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P113" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
         <v>37</v>
       </c>
@@ -33554,8 +35003,17 @@
       <c r="M114" s="10">
         <v>2005</v>
       </c>
-    </row>
-    <row r="115" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N114" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O114" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P114" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
         <v>127</v>
       </c>
@@ -33595,8 +35053,17 @@
       <c r="M115" s="10">
         <v>1177</v>
       </c>
-    </row>
-    <row r="116" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N115" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O115" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P115" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
         <v>63</v>
       </c>
@@ -33628,8 +35095,17 @@
       <c r="M116" s="10">
         <v>1227</v>
       </c>
-    </row>
-    <row r="117" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N116" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O116" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P116" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
         <v>47</v>
       </c>
@@ -33661,8 +35137,17 @@
       <c r="M117" s="10">
         <v>2827</v>
       </c>
-    </row>
-    <row r="118" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N117" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O117" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P117" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
         <v>103</v>
       </c>
@@ -33702,8 +35187,17 @@
       <c r="M118" s="10">
         <v>373</v>
       </c>
-    </row>
-    <row r="119" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N118" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O118" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P118" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="5" t="s">
         <v>93</v>
       </c>
@@ -33743,8 +35237,17 @@
       <c r="M119" s="10">
         <v>324</v>
       </c>
-    </row>
-    <row r="120" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N119" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O119" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P119" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="5" t="s">
         <v>236</v>
       </c>
@@ -33784,8 +35287,17 @@
       <c r="M120" s="10">
         <v>261</v>
       </c>
-    </row>
-    <row r="121" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N120" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O120" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P120" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="5" t="s">
         <v>234</v>
       </c>
@@ -33825,8 +35337,17 @@
       <c r="M121" s="10">
         <v>297</v>
       </c>
-    </row>
-    <row r="122" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N121" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O121" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P121" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="5" t="s">
         <v>232</v>
       </c>
@@ -33866,8 +35387,17 @@
       <c r="M122" s="10">
         <v>1307</v>
       </c>
-    </row>
-    <row r="123" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N122" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O122" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P122" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="5" t="s">
         <v>238</v>
       </c>
@@ -33907,8 +35437,17 @@
       <c r="M123" s="10">
         <v>145</v>
       </c>
-    </row>
-    <row r="124" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N123" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O123" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P123" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="5" t="s">
         <v>240</v>
       </c>
@@ -33948,8 +35487,17 @@
       <c r="M124" s="10">
         <v>2004</v>
       </c>
-    </row>
-    <row r="125" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N124" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O124" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P124" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="5" t="s">
         <v>15</v>
       </c>
@@ -33989,8 +35537,17 @@
       <c r="M125" s="10">
         <v>663</v>
       </c>
-    </row>
-    <row r="126" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N125" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O125" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P125" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="5" t="s">
         <v>438</v>
       </c>
@@ -34030,8 +35587,17 @@
       <c r="M126" s="10">
         <v>899</v>
       </c>
-    </row>
-    <row r="127" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N126" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O126" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P126" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="4" t="s">
         <v>439</v>
       </c>
@@ -34063,8 +35629,17 @@
       <c r="M127" s="10">
         <v>82</v>
       </c>
-    </row>
-    <row r="128" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N127" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O127" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P127" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="4" t="s">
         <v>440</v>
       </c>
@@ -34096,8 +35671,17 @@
       <c r="M128" s="10">
         <v>40</v>
       </c>
-    </row>
-    <row r="129" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N128" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O128" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P128" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="4" t="s">
         <v>441</v>
       </c>
@@ -34129,8 +35713,17 @@
       <c r="M129" s="10">
         <v>300</v>
       </c>
-    </row>
-    <row r="130" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N129" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O129" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P129" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="4" t="s">
         <v>442</v>
       </c>
@@ -34162,8 +35755,17 @@
       <c r="M130" s="10">
         <v>250</v>
       </c>
-    </row>
-    <row r="131" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N130" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O130" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P130" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="4" t="s">
         <v>443</v>
       </c>
@@ -34195,8 +35797,17 @@
       <c r="M131" s="10">
         <v>108</v>
       </c>
-    </row>
-    <row r="132" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N131" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O131" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P131" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="4" t="s">
         <v>444</v>
       </c>
@@ -34228,8 +35839,17 @@
       <c r="M132" s="10">
         <v>145</v>
       </c>
-    </row>
-    <row r="133" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N132" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O132" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P132" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="4" t="s">
         <v>445</v>
       </c>
@@ -34261,8 +35881,17 @@
       <c r="M133" s="10">
         <v>35</v>
       </c>
-    </row>
-    <row r="134" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N133" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O133" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P133" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="4" t="s">
         <v>446</v>
       </c>
@@ -34294,8 +35923,17 @@
       <c r="M134" s="10">
         <v>45</v>
       </c>
-    </row>
-    <row r="135" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N134" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O134" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P134" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="4" t="s">
         <v>447</v>
       </c>
@@ -34327,8 +35965,17 @@
       <c r="M135" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="136" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N135" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O135" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P135" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="4" t="s">
         <v>448</v>
       </c>
@@ -34360,8 +36007,17 @@
       <c r="M136" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="137" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N136" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O136" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P136" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="4" t="s">
         <v>449</v>
       </c>
@@ -34393,8 +36049,17 @@
       <c r="M137" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="138" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N137" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O137" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P137" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="4" t="s">
         <v>450</v>
       </c>
@@ -34426,8 +36091,17 @@
       <c r="M138" s="10">
         <v>45</v>
       </c>
-    </row>
-    <row r="139" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N138" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O138" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P138" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="4" t="s">
         <v>451</v>
       </c>
@@ -34459,8 +36133,17 @@
       <c r="M139" s="10">
         <v>45</v>
       </c>
-    </row>
-    <row r="140" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N139" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O139" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P139" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="140" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="4" t="s">
         <v>452</v>
       </c>
@@ -34492,8 +36175,17 @@
       <c r="M140" s="10">
         <v>45</v>
       </c>
-    </row>
-    <row r="141" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N140" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O140" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P140" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="4" t="s">
         <v>453</v>
       </c>
@@ -34525,8 +36217,17 @@
       <c r="M141" s="10">
         <v>45</v>
       </c>
-    </row>
-    <row r="142" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N141" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O141" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P141" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="4" t="s">
         <v>454</v>
       </c>
@@ -34558,8 +36259,17 @@
       <c r="M142" s="10">
         <v>2350</v>
       </c>
-    </row>
-    <row r="143" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N142" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O142" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P142" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="4" t="s">
         <v>455</v>
       </c>
@@ -34591,8 +36301,17 @@
       <c r="M143" s="10">
         <v>500</v>
       </c>
-    </row>
-    <row r="144" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N143" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O143" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P143" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="13" t="s">
         <v>456</v>
       </c>
@@ -34624,8 +36343,17 @@
       <c r="M144" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="145" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N144" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O144" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P144" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="13" t="s">
         <v>457</v>
       </c>
@@ -34657,8 +36385,17 @@
       <c r="M145" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="146" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N145" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O145" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P145" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="13" t="s">
         <v>458</v>
       </c>
@@ -34690,8 +36427,17 @@
       <c r="M146" s="10">
         <v>2000</v>
       </c>
-    </row>
-    <row r="147" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N146" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O146" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P146" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="13" t="s">
         <v>459</v>
       </c>
@@ -34723,8 +36469,17 @@
       <c r="M147" s="10">
         <v>550</v>
       </c>
-    </row>
-    <row r="148" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N147" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O147" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P147" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="5" t="s">
         <v>1606</v>
       </c>
@@ -34764,8 +36519,17 @@
       <c r="M148" s="10">
         <v>0</v>
       </c>
-    </row>
-    <row r="149" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N148" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O148" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P148" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="5" t="s">
         <v>3025</v>
       </c>
@@ -34797,8 +36561,17 @@
       <c r="M149" s="10">
         <v>0</v>
       </c>
-    </row>
-    <row r="150" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N149" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O149" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P149" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="5" t="s">
         <v>523</v>
       </c>
@@ -34833,7 +36606,7 @@
         <v>2165.5744819986176</v>
       </c>
     </row>
-    <row r="151" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="5" t="s">
         <v>524</v>
       </c>
@@ -34868,7 +36641,7 @@
         <v>1475.9646878294116</v>
       </c>
     </row>
-    <row r="152" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="5" t="s">
         <v>525</v>
       </c>
@@ -34903,7 +36676,7 @@
         <v>4486.0109796000006</v>
       </c>
     </row>
-    <row r="153" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="5" t="s">
         <v>526</v>
       </c>
@@ -34938,7 +36711,7 @@
         <v>2021.2626509999998</v>
       </c>
     </row>
-    <row r="154" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="5" t="s">
         <v>527</v>
       </c>
@@ -34973,7 +36746,7 @@
         <v>2738.4848820000002</v>
       </c>
     </row>
-    <row r="155" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="5" t="s">
         <v>528</v>
       </c>
@@ -35008,7 +36781,7 @@
         <v>1201.7320127999999</v>
       </c>
     </row>
-    <row r="156" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:16" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="16" t="s">
         <v>529</v>
       </c>
@@ -35042,8 +36815,10 @@
       <c r="M156" s="17">
         <v>1679.60406096</v>
       </c>
-    </row>
-    <row r="157" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N156" s="2"/>
+      <c r="O156" s="2"/>
+    </row>
+    <row r="157" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="5" t="s">
         <v>1610</v>
       </c>
@@ -35078,7 +36853,7 @@
         <v>1679.6</v>
       </c>
     </row>
-    <row r="158" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="5" t="s">
         <v>530</v>
       </c>
@@ -35113,7 +36888,7 @@
         <v>4042.5253019999996</v>
       </c>
     </row>
-    <row r="159" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="5" t="s">
         <v>531</v>
       </c>
@@ -35148,7 +36923,7 @@
         <v>1499.646483</v>
       </c>
     </row>
-    <row r="160" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="5" t="s">
         <v>532</v>
       </c>
@@ -41897,7 +43672,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="353" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:15" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="16" t="s">
         <v>1209</v>
       </c>
@@ -41925,8 +43700,10 @@
       <c r="M353" s="17">
         <v>1108</v>
       </c>
-    </row>
-    <row r="354" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N353" s="2"/>
+      <c r="O353" s="2"/>
+    </row>
+    <row r="354" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="5" t="s">
         <v>1192</v>
       </c>
@@ -41955,7 +43732,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="355" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="5" t="s">
         <v>1193</v>
       </c>
@@ -41984,7 +43761,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="356" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="5" t="s">
         <v>1194</v>
       </c>
@@ -42013,7 +43790,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="357" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="5" t="s">
         <v>1195</v>
       </c>
@@ -42042,7 +43819,7 @@
         <v>2412</v>
       </c>
     </row>
-    <row r="358" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="5" t="s">
         <v>1196</v>
       </c>
@@ -42071,7 +43848,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="359" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="5" t="s">
         <v>1197</v>
       </c>
@@ -42100,7 +43877,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="360" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="5" t="s">
         <v>1198</v>
       </c>
@@ -42129,7 +43906,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="361" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="5" t="s">
         <v>1199</v>
       </c>
@@ -42158,7 +43935,7 @@
         <v>1689</v>
       </c>
     </row>
-    <row r="362" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="5" t="s">
         <v>1200</v>
       </c>
@@ -42187,7 +43964,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="363" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="5" t="s">
         <v>1201</v>
       </c>
@@ -42216,7 +43993,7 @@
         <v>1695</v>
       </c>
     </row>
-    <row r="364" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="5" t="s">
         <v>1202</v>
       </c>
@@ -42245,7 +44022,7 @@
         <v>1448</v>
       </c>
     </row>
-    <row r="365" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="5" t="s">
         <v>1203</v>
       </c>
@@ -42274,7 +44051,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="366" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="5" t="s">
         <v>1204</v>
       </c>
@@ -42303,7 +44080,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="367" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="5" t="s">
         <v>1205</v>
       </c>
@@ -42332,7 +44109,7 @@
         <v>2412</v>
       </c>
     </row>
-    <row r="368" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="5" t="s">
         <v>1206</v>
       </c>
@@ -42825,7 +44602,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="385" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A385" s="5" t="s">
         <v>1224</v>
       </c>
@@ -42854,7 +44631,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="386" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A386" s="5" t="s">
         <v>1312</v>
       </c>
@@ -42882,8 +44659,15 @@
       <c r="M386" s="15">
         <v>3269</v>
       </c>
-    </row>
-    <row r="387" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N386" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P386" s="2">
+        <f>_xlfn.XLOOKUP(C386,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="387" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A387" s="5" t="s">
         <v>1313</v>
       </c>
@@ -42911,8 +44695,15 @@
       <c r="M387" s="15">
         <v>3943</v>
       </c>
-    </row>
-    <row r="388" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N387" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P387" s="2">
+        <f>_xlfn.XLOOKUP(C387,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="388" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A388" s="5" t="s">
         <v>1314</v>
       </c>
@@ -42940,8 +44731,15 @@
       <c r="M388" s="15">
         <v>3943</v>
       </c>
-    </row>
-    <row r="389" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N388" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P388" s="2">
+        <f>_xlfn.XLOOKUP(C388,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="389" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A389" s="5" t="s">
         <v>1315</v>
       </c>
@@ -42969,8 +44767,15 @@
       <c r="M389" s="15">
         <v>3943</v>
       </c>
-    </row>
-    <row r="390" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N389" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P389" s="2">
+        <f>_xlfn.XLOOKUP(C389,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="390" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A390" s="5" t="s">
         <v>1316</v>
       </c>
@@ -42998,8 +44803,15 @@
       <c r="M390" s="15">
         <v>3943</v>
       </c>
-    </row>
-    <row r="391" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N390" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P390" s="2">
+        <f>_xlfn.XLOOKUP(C390,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="391" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A391" s="5" t="s">
         <v>1317</v>
       </c>
@@ -43027,8 +44839,14 @@
       <c r="M391" s="15">
         <v>3607</v>
       </c>
-    </row>
-    <row r="392" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N391" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P391" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="392" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A392" s="5" t="s">
         <v>1318</v>
       </c>
@@ -43056,8 +44874,14 @@
       <c r="M392" s="15">
         <v>3607</v>
       </c>
-    </row>
-    <row r="393" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N392" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P392" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="393" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A393" s="5" t="s">
         <v>1319</v>
       </c>
@@ -43085,8 +44909,14 @@
       <c r="M393" s="15">
         <v>3607</v>
       </c>
-    </row>
-    <row r="394" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N393" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P393" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="394" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A394" s="5" t="s">
         <v>1320</v>
       </c>
@@ -43114,8 +44944,14 @@
       <c r="M394" s="15">
         <v>3607</v>
       </c>
-    </row>
-    <row r="395" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N394" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P394" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="395" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A395" s="5" t="s">
         <v>1321</v>
       </c>
@@ -43143,8 +44979,14 @@
       <c r="M395" s="15">
         <v>3272</v>
       </c>
-    </row>
-    <row r="396" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N395" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P395" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="396" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A396" s="5" t="s">
         <v>1322</v>
       </c>
@@ -43172,8 +45014,14 @@
       <c r="M396" s="15">
         <v>3272</v>
       </c>
-    </row>
-    <row r="397" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N396" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P396" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="397" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A397" s="5" t="s">
         <v>1323</v>
       </c>
@@ -43201,8 +45049,14 @@
       <c r="M397" s="15">
         <v>3262</v>
       </c>
-    </row>
-    <row r="398" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N397" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P397" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="398" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A398" s="5" t="s">
         <v>1324</v>
       </c>
@@ -43230,8 +45084,14 @@
       <c r="M398" s="15">
         <v>3262</v>
       </c>
-    </row>
-    <row r="399" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N398" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P398" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="399" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A399" s="5" t="s">
         <v>1325</v>
       </c>
@@ -43259,8 +45119,15 @@
       <c r="M399" s="15">
         <v>7852</v>
       </c>
-    </row>
-    <row r="400" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N399" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P399" s="2">
+        <f>_xlfn.XLOOKUP(C399,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="400" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A400" s="5" t="s">
         <v>1326</v>
       </c>
@@ -43288,8 +45155,15 @@
       <c r="M400" s="15">
         <v>6978</v>
       </c>
-    </row>
-    <row r="401" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N400" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P400" s="2">
+        <f>_xlfn.XLOOKUP(C400,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="401" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A401" s="5" t="s">
         <v>1327</v>
       </c>
@@ -43317,8 +45191,15 @@
       <c r="M401" s="15">
         <v>7852</v>
       </c>
-    </row>
-    <row r="402" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N401" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P401" s="2">
+        <f>_xlfn.XLOOKUP(C401,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="402" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A402" s="5" t="s">
         <v>1328</v>
       </c>
@@ -43346,8 +45227,15 @@
       <c r="M402" s="15">
         <v>7852</v>
       </c>
-    </row>
-    <row r="403" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N402" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P402" s="2">
+        <f>_xlfn.XLOOKUP(C402,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="403" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A403" s="5" t="s">
         <v>1329</v>
       </c>
@@ -43375,8 +45263,15 @@
       <c r="M403" s="15">
         <v>6978</v>
       </c>
-    </row>
-    <row r="404" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N403" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P403" s="2">
+        <f>_xlfn.XLOOKUP(C403,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="404" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A404" s="5" t="s">
         <v>1330</v>
       </c>
@@ -43404,8 +45299,15 @@
       <c r="M404" s="15">
         <v>10654</v>
       </c>
-    </row>
-    <row r="405" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N404" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P404" s="2">
+        <f>_xlfn.XLOOKUP(C404,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="405" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A405" s="5" t="s">
         <v>1331</v>
       </c>
@@ -43433,8 +45335,15 @@
       <c r="M405" s="15">
         <v>10654</v>
       </c>
-    </row>
-    <row r="406" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N405" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P405" s="2">
+        <f>_xlfn.XLOOKUP(C405,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="406" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A406" s="5" t="s">
         <v>1332</v>
       </c>
@@ -43462,8 +45371,15 @@
       <c r="M406" s="15">
         <v>7018</v>
       </c>
-    </row>
-    <row r="407" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N406" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P406" s="2">
+        <f>_xlfn.XLOOKUP(C406,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="407" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A407" s="5" t="s">
         <v>1333</v>
       </c>
@@ -43491,8 +45407,15 @@
       <c r="M407" s="15">
         <v>7018</v>
       </c>
-    </row>
-    <row r="408" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N407" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P407" s="2">
+        <f>_xlfn.XLOOKUP(C407,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="408" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A408" s="5" t="s">
         <v>1334</v>
       </c>
@@ -43520,8 +45443,15 @@
       <c r="M408" s="15">
         <v>7018</v>
       </c>
-    </row>
-    <row r="409" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N408" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P408" s="2">
+        <f>_xlfn.XLOOKUP(C408,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="409" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A409" s="5" t="s">
         <v>1335</v>
       </c>
@@ -43549,8 +45479,15 @@
       <c r="M409" s="15">
         <v>7018</v>
       </c>
-    </row>
-    <row r="410" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N409" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P409" s="2">
+        <f>_xlfn.XLOOKUP(C409,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="410" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A410" s="5" t="s">
         <v>1336</v>
       </c>
@@ -43578,8 +45515,15 @@
       <c r="M410" s="15">
         <v>11345</v>
       </c>
-    </row>
-    <row r="411" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N410" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P410" s="2">
+        <f>_xlfn.XLOOKUP(C410,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="411" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A411" s="5" t="s">
         <v>1337</v>
       </c>
@@ -43607,8 +45551,15 @@
       <c r="M411" s="15">
         <v>11345</v>
       </c>
-    </row>
-    <row r="412" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N411" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P411" s="2">
+        <f>_xlfn.XLOOKUP(C411,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="412" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A412" s="5" t="s">
         <v>1338</v>
       </c>
@@ -43636,8 +45587,14 @@
       <c r="M412" s="15">
         <v>11345</v>
       </c>
-    </row>
-    <row r="413" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N412" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P412" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="413" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A413" s="5" t="s">
         <v>1339</v>
       </c>
@@ -43665,8 +45622,14 @@
       <c r="M413" s="15">
         <v>11345</v>
       </c>
-    </row>
-    <row r="414" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N413" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P413" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="414" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A414" s="5" t="s">
         <v>1340</v>
       </c>
@@ -43694,8 +45657,14 @@
       <c r="M414" s="15">
         <v>12094</v>
       </c>
-    </row>
-    <row r="415" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N414" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P414" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="415" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A415" s="5" t="s">
         <v>1341</v>
       </c>
@@ -43723,8 +45692,15 @@
       <c r="M415" s="15">
         <v>6432</v>
       </c>
-    </row>
-    <row r="416" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N415" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P415" s="2">
+        <f>_xlfn.XLOOKUP(C415,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="416" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A416" s="5" t="s">
         <v>1342</v>
       </c>
@@ -43752,8 +45728,15 @@
       <c r="M416" s="15">
         <v>6432</v>
       </c>
-    </row>
-    <row r="417" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N416" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P416" s="2">
+        <f>_xlfn.XLOOKUP(C416,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="417" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A417" s="5" t="s">
         <v>1343</v>
       </c>
@@ -43781,8 +45764,15 @@
       <c r="M417" s="15">
         <v>7641</v>
       </c>
-    </row>
-    <row r="418" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N417" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P417" s="2">
+        <f>_xlfn.XLOOKUP(C417,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="418" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A418" s="5" t="s">
         <v>1344</v>
       </c>
@@ -43810,8 +45800,15 @@
       <c r="M418" s="15">
         <v>7641</v>
       </c>
-    </row>
-    <row r="419" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N418" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P418" s="2">
+        <f>_xlfn.XLOOKUP(C418,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="419" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A419" s="5" t="s">
         <v>1345</v>
       </c>
@@ -43839,8 +45836,15 @@
       <c r="M419" s="15">
         <v>7641</v>
       </c>
-    </row>
-    <row r="420" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N419" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P419" s="2">
+        <f>_xlfn.XLOOKUP(C419,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="420" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A420" s="5" t="s">
         <v>1346</v>
       </c>
@@ -43868,8 +45872,14 @@
       <c r="M420" s="15">
         <v>623</v>
       </c>
-    </row>
-    <row r="421" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N420" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P420" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="421" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A421" s="5" t="s">
         <v>1347</v>
       </c>
@@ -43897,8 +45907,14 @@
       <c r="M421" s="15">
         <v>832</v>
       </c>
-    </row>
-    <row r="422" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N421" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P421" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="422" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A422" s="5" t="s">
         <v>1348</v>
       </c>
@@ -43926,8 +45942,14 @@
       <c r="M422" s="15">
         <v>1032</v>
       </c>
-    </row>
-    <row r="423" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N422" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P422" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="423" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A423" s="5" t="s">
         <v>1349</v>
       </c>
@@ -43955,8 +45977,14 @@
       <c r="M423" s="15">
         <v>1822</v>
       </c>
-    </row>
-    <row r="424" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N423" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P423" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="424" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A424" s="5" t="s">
         <v>1350</v>
       </c>
@@ -43984,8 +46012,15 @@
       <c r="M424" s="15">
         <v>1074</v>
       </c>
-    </row>
-    <row r="425" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N424" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P424" s="2">
+        <f>_xlfn.XLOOKUP(C424,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="425" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A425" s="5" t="s">
         <v>1351</v>
       </c>
@@ -44013,8 +46048,15 @@
       <c r="M425" s="15">
         <v>720</v>
       </c>
-    </row>
-    <row r="426" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N425" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P425" s="2">
+        <f>_xlfn.XLOOKUP(C425,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="426" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A426" s="5" t="s">
         <v>1352</v>
       </c>
@@ -44042,8 +46084,15 @@
       <c r="M426" s="15">
         <v>1015</v>
       </c>
-    </row>
-    <row r="427" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N426" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P426" s="2">
+        <f>_xlfn.XLOOKUP(C426,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="427" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A427" s="5" t="s">
         <v>1353</v>
       </c>
@@ -44071,8 +46120,15 @@
       <c r="M427" s="15">
         <v>1130</v>
       </c>
-    </row>
-    <row r="428" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N427" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P427" s="2">
+        <f>_xlfn.XLOOKUP(C427,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="428" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A428" s="5" t="s">
         <v>1354</v>
       </c>
@@ -44100,8 +46156,15 @@
       <c r="M428" s="15">
         <v>1566</v>
       </c>
-    </row>
-    <row r="429" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N428" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P428" s="2">
+        <f>_xlfn.XLOOKUP(C428,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="429" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A429" s="5" t="s">
         <v>1355</v>
       </c>
@@ -44129,8 +46192,15 @@
       <c r="M429" s="15">
         <v>1254</v>
       </c>
-    </row>
-    <row r="430" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N429" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P429" s="2">
+        <f>_xlfn.XLOOKUP(C429,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="430" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A430" s="5" t="s">
         <v>1356</v>
       </c>
@@ -44158,8 +46228,15 @@
       <c r="M430" s="15">
         <v>1341</v>
       </c>
-    </row>
-    <row r="431" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N430" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P430" s="2">
+        <f>_xlfn.XLOOKUP(C430,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="431" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A431" s="5" t="s">
         <v>1357</v>
       </c>
@@ -44187,8 +46264,15 @@
       <c r="M431" s="15">
         <v>2236</v>
       </c>
-    </row>
-    <row r="432" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N431" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P431" s="2">
+        <f>_xlfn.XLOOKUP(C431,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="432" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A432" s="5" t="s">
         <v>1358</v>
       </c>
@@ -44216,8 +46300,15 @@
       <c r="M432" s="15">
         <v>866</v>
       </c>
-    </row>
-    <row r="433" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N432" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P432" s="2">
+        <f>_xlfn.XLOOKUP(C432,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="433" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A433" s="5" t="s">
         <v>1359</v>
       </c>
@@ -44245,8 +46336,15 @@
       <c r="M433" s="15">
         <v>1380</v>
       </c>
-    </row>
-    <row r="434" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N433" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P433" s="2">
+        <f>_xlfn.XLOOKUP(C433,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="434" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A434" s="5" t="s">
         <v>2697</v>
       </c>
@@ -44274,8 +46372,15 @@
       <c r="M434" s="15">
         <v>3200</v>
       </c>
-    </row>
-    <row r="435" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N434" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P434" s="2">
+        <f>_xlfn.XLOOKUP(C434,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="435" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A435" s="5" t="s">
         <v>2698</v>
       </c>
@@ -44303,8 +46408,15 @@
       <c r="M435" s="15">
         <v>2043</v>
       </c>
-    </row>
-    <row r="436" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N435" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P435" s="2">
+        <f>_xlfn.XLOOKUP(C435,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="436" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A436" s="5" t="s">
         <v>2699</v>
       </c>
@@ -44332,8 +46444,15 @@
       <c r="M436" s="15">
         <v>2016</v>
       </c>
-    </row>
-    <row r="437" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N436" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P436" s="2">
+        <f>_xlfn.XLOOKUP(C436,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="437" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A437" s="5" t="s">
         <v>2700</v>
       </c>
@@ -44361,8 +46480,15 @@
       <c r="M437" s="15">
         <v>2722</v>
       </c>
-    </row>
-    <row r="438" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N437" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P437" s="2">
+        <f>_xlfn.XLOOKUP(C437,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="438" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A438" s="18" t="s">
         <v>2696</v>
       </c>
@@ -44390,8 +46516,15 @@
       <c r="M438" s="15">
         <v>589</v>
       </c>
-    </row>
-    <row r="439" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N438" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P438" s="2">
+        <f>_xlfn.XLOOKUP(C438,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="439" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A439" s="5" t="s">
         <v>2701</v>
       </c>
@@ -44419,8 +46552,15 @@
       <c r="M439" s="15">
         <v>724</v>
       </c>
-    </row>
-    <row r="440" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N439" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P439" s="2">
+        <f>_xlfn.XLOOKUP(C439,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="440" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A440" s="5" t="s">
         <v>2702</v>
       </c>
@@ -44448,8 +46588,15 @@
       <c r="M440" s="15">
         <v>175</v>
       </c>
-    </row>
-    <row r="441" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N440" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P440" s="2">
+        <f>_xlfn.XLOOKUP(C440,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="441" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A441" s="5" t="s">
         <v>2703</v>
       </c>
@@ -44477,8 +46624,15 @@
       <c r="M441" s="15">
         <v>113</v>
       </c>
-    </row>
-    <row r="442" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N441" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P441" s="2">
+        <f>_xlfn.XLOOKUP(C441,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="442" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A442" s="5" t="s">
         <v>2704</v>
       </c>
@@ -44506,8 +46660,15 @@
       <c r="M442" s="15">
         <v>179</v>
       </c>
-    </row>
-    <row r="443" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N442" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P442" s="2">
+        <f>_xlfn.XLOOKUP(C442,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="443" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A443" s="5" t="s">
         <v>1360</v>
       </c>
@@ -44535,8 +46696,15 @@
       <c r="M443" s="15">
         <v>230</v>
       </c>
-    </row>
-    <row r="444" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N443" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P443" s="2">
+        <f>_xlfn.XLOOKUP(C443,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="444" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A444" s="5" t="s">
         <v>3045</v>
       </c>
@@ -44564,8 +46732,14 @@
       <c r="M444" s="15">
         <v>230</v>
       </c>
-    </row>
-    <row r="445" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N444" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P444" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="445" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A445" s="5" t="s">
         <v>1361</v>
       </c>
@@ -44593,8 +46767,14 @@
       <c r="M445" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="446" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N445" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P445" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="446" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A446" s="5" t="s">
         <v>1362</v>
       </c>
@@ -44622,8 +46802,14 @@
       <c r="M446" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="447" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N446" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P446" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="447" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A447" s="5" t="s">
         <v>1363</v>
       </c>
@@ -44651,8 +46837,14 @@
       <c r="M447" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="448" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N447" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P447" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="448" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A448" s="5" t="s">
         <v>1364</v>
       </c>
@@ -44680,8 +46872,14 @@
       <c r="M448" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="449" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N448" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P448" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="449" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A449" s="5" t="s">
         <v>1365</v>
       </c>
@@ -44709,8 +46907,14 @@
       <c r="M449" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="450" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N449" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P449" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="450" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A450" s="5" t="s">
         <v>1366</v>
       </c>
@@ -44738,8 +46942,14 @@
       <c r="M450" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="451" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N450" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P450" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="451" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A451" s="5" t="s">
         <v>1367</v>
       </c>
@@ -44767,8 +46977,14 @@
       <c r="M451" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="452" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N451" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P451" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="452" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A452" s="5" t="s">
         <v>1368</v>
       </c>
@@ -44796,8 +47012,14 @@
       <c r="M452" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="453" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N452" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P452" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="453" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A453" s="5" t="s">
         <v>1369</v>
       </c>
@@ -44825,8 +47047,14 @@
       <c r="M453" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="454" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N453" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P453" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="454" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A454" s="5" t="s">
         <v>1370</v>
       </c>
@@ -44854,8 +47082,14 @@
       <c r="M454" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="455" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N454" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P454" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="455" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A455" s="5" t="s">
         <v>1371</v>
       </c>
@@ -44883,8 +47117,14 @@
       <c r="M455" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="456" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N455" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P455" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="456" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A456" s="5" t="s">
         <v>1372</v>
       </c>
@@ -44912,8 +47152,14 @@
       <c r="M456" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="457" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N456" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P456" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="457" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A457" s="5" t="s">
         <v>1373</v>
       </c>
@@ -44941,8 +47187,14 @@
       <c r="M457" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="458" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N457" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P457" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="458" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A458" s="5" t="s">
         <v>1374</v>
       </c>
@@ -44970,8 +47222,14 @@
       <c r="M458" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="459" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N458" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P458" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="459" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A459" s="5" t="s">
         <v>1375</v>
       </c>
@@ -44999,8 +47257,14 @@
       <c r="M459" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="460" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N459" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P459" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="460" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A460" s="5" t="s">
         <v>1376</v>
       </c>
@@ -45028,8 +47292,14 @@
       <c r="M460" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="461" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N460" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P460" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="461" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A461" s="5" t="s">
         <v>1377</v>
       </c>
@@ -45057,8 +47327,14 @@
       <c r="M461" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="462" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N461" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P461" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="462" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A462" s="5" t="s">
         <v>1378</v>
       </c>
@@ -45086,8 +47362,14 @@
       <c r="M462" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="463" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N462" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P462" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="463" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A463" s="5" t="s">
         <v>1379</v>
       </c>
@@ -45115,8 +47397,14 @@
       <c r="M463" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="464" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N463" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P463" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="464" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A464" s="5" t="s">
         <v>1380</v>
       </c>
@@ -45144,8 +47432,14 @@
       <c r="M464" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="465" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N464" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P464" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="465" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A465" s="5" t="s">
         <v>1381</v>
       </c>
@@ -45173,8 +47467,14 @@
       <c r="M465" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="466" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N465" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P465" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="466" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A466" s="5" t="s">
         <v>1382</v>
       </c>
@@ -45202,8 +47502,14 @@
       <c r="M466" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="467" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N466" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P466" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="467" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A467" s="5" t="s">
         <v>1383</v>
       </c>
@@ -45231,8 +47537,14 @@
       <c r="M467" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="468" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N467" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P467" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="468" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A468" s="5" t="s">
         <v>1384</v>
       </c>
@@ -45260,8 +47572,14 @@
       <c r="M468" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="469" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N468" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P468" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="469" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A469" s="5" t="s">
         <v>1385</v>
       </c>
@@ -45289,8 +47607,14 @@
       <c r="M469" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="470" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N469" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P469" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="470" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A470" s="5" t="s">
         <v>1386</v>
       </c>
@@ -45318,8 +47642,14 @@
       <c r="M470" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="471" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N470" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P470" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="471" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A471" s="5" t="s">
         <v>1387</v>
       </c>
@@ -45347,8 +47677,14 @@
       <c r="M471" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="472" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N471" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P471" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="472" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A472" s="5" t="s">
         <v>1388</v>
       </c>
@@ -45376,8 +47712,14 @@
       <c r="M472" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="473" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N472" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P472" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="473" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A473" s="5" t="s">
         <v>1389</v>
       </c>
@@ -45405,8 +47747,14 @@
       <c r="M473" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="474" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N473" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P473" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="474" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A474" s="5" t="s">
         <v>1390</v>
       </c>
@@ -45434,8 +47782,14 @@
       <c r="M474" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="475" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N474" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P474" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="475" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A475" s="5" t="s">
         <v>1391</v>
       </c>
@@ -45463,8 +47817,14 @@
       <c r="M475" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="476" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N475" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P475" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="476" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A476" s="5" t="s">
         <v>1392</v>
       </c>
@@ -45492,8 +47852,14 @@
       <c r="M476" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="477" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N476" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P476" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="477" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A477" s="5" t="s">
         <v>1393</v>
       </c>
@@ -45521,8 +47887,14 @@
       <c r="M477" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="478" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N477" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P477" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="478" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A478" s="5" t="s">
         <v>1394</v>
       </c>
@@ -45550,8 +47922,14 @@
       <c r="M478" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="479" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N478" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P478" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="479" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A479" s="5" t="s">
         <v>1395</v>
       </c>
@@ -45579,8 +47957,14 @@
       <c r="M479" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="480" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N479" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P479" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="480" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A480" s="5" t="s">
         <v>1396</v>
       </c>
@@ -45608,8 +47992,14 @@
       <c r="M480" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="481" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N480" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P480" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="481" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A481" s="5" t="s">
         <v>1397</v>
       </c>
@@ -45637,8 +48027,14 @@
       <c r="M481" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="482" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N481" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P481" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="482" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A482" s="5" t="s">
         <v>1398</v>
       </c>
@@ -45666,8 +48062,14 @@
       <c r="M482" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="483" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N482" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P482" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="483" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A483" s="5" t="s">
         <v>1399</v>
       </c>
@@ -45695,8 +48097,14 @@
       <c r="M483" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="484" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N483" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P483" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="484" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A484" s="5" t="s">
         <v>1617</v>
       </c>
@@ -45721,7 +48129,7 @@
       <c r="L484" s="5"/>
       <c r="M484" s="15"/>
     </row>
-    <row r="485" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A485" s="5" t="s">
         <v>1618</v>
       </c>
@@ -45746,7 +48154,7 @@
       <c r="L485" s="5"/>
       <c r="M485" s="15"/>
     </row>
-    <row r="486" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A486" s="5" t="s">
         <v>1619</v>
       </c>
@@ -45771,7 +48179,7 @@
       <c r="L486" s="5"/>
       <c r="M486" s="15"/>
     </row>
-    <row r="487" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A487" s="5" t="s">
         <v>1620</v>
       </c>
@@ -45796,7 +48204,7 @@
       <c r="L487" s="5"/>
       <c r="M487" s="15"/>
     </row>
-    <row r="488" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A488" s="5" t="s">
         <v>1621</v>
       </c>
@@ -45821,7 +48229,7 @@
       <c r="L488" s="5"/>
       <c r="M488" s="15"/>
     </row>
-    <row r="489" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A489" s="5" t="s">
         <v>1622</v>
       </c>
@@ -45846,7 +48254,7 @@
       <c r="L489" s="5"/>
       <c r="M489" s="15"/>
     </row>
-    <row r="490" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A490" s="5" t="s">
         <v>1623</v>
       </c>
@@ -45871,7 +48279,7 @@
       <c r="L490" s="5"/>
       <c r="M490" s="15"/>
     </row>
-    <row r="491" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A491" s="5" t="s">
         <v>1624</v>
       </c>
@@ -45896,7 +48304,7 @@
       <c r="L491" s="5"/>
       <c r="M491" s="15"/>
     </row>
-    <row r="492" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A492" s="5" t="s">
         <v>1625</v>
       </c>
@@ -45921,7 +48329,7 @@
       <c r="L492" s="5"/>
       <c r="M492" s="15"/>
     </row>
-    <row r="493" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A493" s="5" t="s">
         <v>1626</v>
       </c>
@@ -45946,7 +48354,7 @@
       <c r="L493" s="5"/>
       <c r="M493" s="15"/>
     </row>
-    <row r="494" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A494" s="5" t="s">
         <v>1627</v>
       </c>
@@ -45971,7 +48379,7 @@
       <c r="L494" s="5"/>
       <c r="M494" s="15"/>
     </row>
-    <row r="495" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A495" s="5" t="s">
         <v>1628</v>
       </c>
@@ -45996,7 +48404,7 @@
       <c r="L495" s="5"/>
       <c r="M495" s="15"/>
     </row>
-    <row r="496" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A496" s="5" t="s">
         <v>1629</v>
       </c>
@@ -55281,7 +57689,7 @@
       <c r="L864" s="5"/>
       <c r="M864" s="15"/>
     </row>
-    <row r="865" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="865" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A865" s="5" t="s">
         <v>2786</v>
       </c>
@@ -55306,7 +57714,7 @@
       <c r="L865" s="5"/>
       <c r="M865" s="15"/>
     </row>
-    <row r="866" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="866" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A866" s="5" t="s">
         <v>2788</v>
       </c>
@@ -55331,7 +57739,7 @@
       <c r="L866" s="5"/>
       <c r="M866" s="15"/>
     </row>
-    <row r="867" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="867" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A867" s="5" t="s">
         <v>2790</v>
       </c>
@@ -55356,7 +57764,7 @@
       <c r="L867" s="5"/>
       <c r="M867" s="15"/>
     </row>
-    <row r="868" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="868" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A868" s="5" t="s">
         <v>2792</v>
       </c>
@@ -55381,7 +57789,7 @@
       <c r="L868" s="5"/>
       <c r="M868" s="15"/>
     </row>
-    <row r="869" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="869" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A869" s="5" t="s">
         <v>2801</v>
       </c>
@@ -55414,7 +57822,7 @@
         <v>443.37374279999995</v>
       </c>
     </row>
-    <row r="870" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="870" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A870" s="5" t="s">
         <v>2803</v>
       </c>
@@ -55445,7 +57853,7 @@
         <v>997.59092129999999</v>
       </c>
     </row>
-    <row r="871" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="871" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A871" s="5" t="s">
         <v>2805</v>
       </c>
@@ -55476,7 +57884,7 @@
         <v>1382.2828451999997</v>
       </c>
     </row>
-    <row r="872" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="872" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A872" s="5" t="s">
         <v>717</v>
       </c>
@@ -55511,7 +57919,7 @@
         <v>534.65657219999991</v>
       </c>
     </row>
-    <row r="873" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="873" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A873" s="5" t="s">
         <v>716</v>
       </c>
@@ -55546,7 +57954,7 @@
         <v>534.65657219999991</v>
       </c>
     </row>
-    <row r="874" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="874" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A874" s="5" t="s">
         <v>2808</v>
       </c>
@@ -55581,7 +57989,7 @@
         <v>912.8282939999998</v>
       </c>
     </row>
-    <row r="875" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="875" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A875" s="5" t="s">
         <v>2809</v>
       </c>
@@ -55616,7 +58024,7 @@
         <v>912.8282939999998</v>
       </c>
     </row>
-    <row r="876" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="876" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A876" s="5" t="s">
         <v>2810</v>
       </c>
@@ -55649,7 +58057,7 @@
         <v>1093.3791264000001</v>
       </c>
     </row>
-    <row r="877" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="877" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A877" s="5" t="s">
         <v>2811</v>
       </c>
@@ -55682,7 +58090,7 @@
         <v>1118.228652</v>
       </c>
     </row>
-    <row r="878" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="878" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A878" s="5" t="s">
         <v>2818</v>
       </c>
@@ -55706,10 +58114,18 @@
       <c r="K878" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="L878" s="5"/>
+      <c r="L878" s="22" t="s">
+        <v>9396</v>
+      </c>
       <c r="M878" s="15"/>
-    </row>
-    <row r="879" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N878" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P878" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="879" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A879" s="5" t="s">
         <v>2820</v>
       </c>
@@ -55745,8 +58161,14 @@
         <v>362</v>
       </c>
       <c r="M879" s="15"/>
-    </row>
-    <row r="880" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N879" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P879" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="880" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A880" s="5" t="s">
         <v>2826</v>
       </c>
@@ -55782,8 +58204,14 @@
         <v>392</v>
       </c>
       <c r="M880" s="15"/>
-    </row>
-    <row r="881" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N880" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P880" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="881" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A881" s="5" t="s">
         <v>2829</v>
       </c>
@@ -55819,8 +58247,14 @@
         <v>392</v>
       </c>
       <c r="M881" s="15"/>
-    </row>
-    <row r="882" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N881" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P881" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="882" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A882" s="5" t="s">
         <v>2838</v>
       </c>
@@ -55848,8 +58282,14 @@
         <v>369</v>
       </c>
       <c r="M882" s="15"/>
-    </row>
-    <row r="883" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N882" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P882" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="883" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A883" s="5" t="s">
         <v>2823</v>
       </c>
@@ -55878,13 +58318,21 @@
       <c r="J883" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="K883" s="5" t="s">
+      <c r="K883" s="22" t="s">
         <v>367</v>
       </c>
-      <c r="L883" s="5"/>
+      <c r="L883" s="22" t="s">
+        <v>9397</v>
+      </c>
       <c r="M883" s="15"/>
-    </row>
-    <row r="884" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N883" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P883" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="884" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A884" s="5" t="s">
         <v>2832</v>
       </c>
@@ -55919,7 +58367,7 @@
         <v>3998.5908929999996</v>
       </c>
     </row>
-    <row r="885" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="885" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A885" s="5" t="s">
         <v>2835</v>
       </c>
@@ -55954,7 +58402,7 @@
         <v>1948.4042896799995</v>
       </c>
     </row>
-    <row r="886" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="886" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A886" s="5" t="s">
         <v>2841</v>
       </c>
@@ -55983,7 +58431,7 @@
         <v>11675.918987999998</v>
       </c>
     </row>
-    <row r="887" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="887" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A887" s="5" t="s">
         <v>2843</v>
       </c>
@@ -56012,7 +58460,7 @@
         <v>11675.918987999998</v>
       </c>
     </row>
-    <row r="888" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="888" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A888" s="5" t="s">
         <v>2845</v>
       </c>
@@ -56039,7 +58487,7 @@
         <v>1428.8477220000002</v>
       </c>
     </row>
-    <row r="889" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="889" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A889" s="5" t="s">
         <v>2847</v>
       </c>
@@ -56066,7 +58514,7 @@
         <v>1528.2458244000002</v>
       </c>
     </row>
-    <row r="890" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="890" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A890" s="5" t="s">
         <v>2849</v>
       </c>
@@ -56093,7 +58541,7 @@
         <v>1900.9887084</v>
       </c>
     </row>
-    <row r="891" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="891" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A891" s="5" t="s">
         <v>2861</v>
       </c>
@@ -56128,7 +58576,7 @@
         <v>1693.3</v>
       </c>
     </row>
-    <row r="892" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="892" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A892" s="5" t="s">
         <v>3026</v>
       </c>
@@ -56163,7 +58611,7 @@
         <v>1693.3</v>
       </c>
     </row>
-    <row r="893" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="893" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A893" s="5" t="s">
         <v>2862</v>
       </c>
@@ -56198,7 +58646,7 @@
         <v>5083.8175999999994</v>
       </c>
     </row>
-    <row r="894" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="894" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A894" s="5" t="s">
         <v>2863</v>
       </c>
@@ -56233,7 +58681,7 @@
         <v>4617.7883999999995</v>
       </c>
     </row>
-    <row r="895" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="895" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A895" s="5" t="s">
         <v>2864</v>
       </c>
@@ -56268,7 +58716,7 @@
         <v>3186.0472</v>
       </c>
     </row>
-    <row r="896" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="896" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A896" s="5" t="s">
         <v>2865</v>
       </c>
@@ -56753,7 +59201,7 @@
         <v>2412.4747769999999</v>
       </c>
     </row>
-    <row r="913" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="913" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A913" s="5" t="s">
         <v>2882</v>
       </c>
@@ -56780,7 +59228,7 @@
         <v>1551.8080997999998</v>
       </c>
     </row>
-    <row r="914" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="914" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A914" s="5" t="s">
         <v>2883</v>
       </c>
@@ -56807,7 +59255,7 @@
         <v>2034.3030551999998</v>
       </c>
     </row>
-    <row r="915" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="915" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A915" s="5" t="s">
         <v>3029</v>
       </c>
@@ -56829,7 +59277,7 @@
       <c r="L915" s="5"/>
       <c r="M915" s="15"/>
     </row>
-    <row r="916" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="916" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A916" s="5" t="s">
         <v>3032</v>
       </c>
@@ -56856,7 +59304,7 @@
       <c r="L916" s="5"/>
       <c r="M916" s="15"/>
     </row>
-    <row r="917" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="917" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A917" s="5" t="s">
         <v>3034</v>
       </c>
@@ -56874,12 +59322,24 @@
       <c r="G917" s="5"/>
       <c r="H917" s="5"/>
       <c r="I917" s="5"/>
-      <c r="J917" s="5"/>
-      <c r="K917" s="5"/>
-      <c r="L917" s="5"/>
+      <c r="J917" s="22" t="s">
+        <v>356</v>
+      </c>
+      <c r="K917" s="22" t="s">
+        <v>361</v>
+      </c>
+      <c r="L917" s="22" t="s">
+        <v>361</v>
+      </c>
       <c r="M917" s="15"/>
-    </row>
-    <row r="918" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N917" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P917" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="918" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A918" s="5" t="s">
         <v>3036</v>
       </c>
@@ -56897,12 +59357,24 @@
       <c r="G918" s="5"/>
       <c r="H918" s="5"/>
       <c r="I918" s="5"/>
-      <c r="J918" s="5"/>
-      <c r="K918" s="5"/>
-      <c r="L918" s="5"/>
+      <c r="J918" s="23" t="s">
+        <v>355</v>
+      </c>
+      <c r="K918" s="22" t="s">
+        <v>9398</v>
+      </c>
+      <c r="L918" s="22" t="s">
+        <v>9398</v>
+      </c>
       <c r="M918" s="15"/>
-    </row>
-    <row r="919" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N918" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P918" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="919" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A919" s="5" t="s">
         <v>1209</v>
       </c>
@@ -56929,7 +59401,7 @@
       <c r="L919" s="5"/>
       <c r="M919" s="15"/>
     </row>
-    <row r="920" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="920" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A920" s="2" t="s">
         <v>3047</v>
       </c>
@@ -56939,8 +59411,14 @@
       <c r="D920" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="921" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N920" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P920" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="921" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A921" s="2" t="s">
         <v>3049</v>
       </c>
@@ -56950,8 +59428,14 @@
       <c r="D921" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="922" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N921" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P921" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="922" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A922" s="2" t="s">
         <v>3050</v>
       </c>
@@ -56961,8 +59445,14 @@
       <c r="D922" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="923" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N922" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P922" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="923" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A923" s="2" t="s">
         <v>3052</v>
       </c>
@@ -56972,8 +59462,14 @@
       <c r="D923" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="924" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N923" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P923" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="924" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A924" s="2" t="s">
         <v>3055</v>
       </c>
@@ -56983,8 +59479,14 @@
       <c r="D924" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="925" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N924" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P924" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="925" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A925" s="2" t="s">
         <v>5135</v>
       </c>
@@ -57001,7 +59503,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="926" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="926" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A926" s="2" t="s">
         <v>5136</v>
       </c>
@@ -57018,7 +59520,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="927" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="927" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A927" s="2" t="s">
         <v>5137</v>
       </c>
@@ -57035,7 +59537,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="928" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="928" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A928" s="2" t="s">
         <v>5138</v>
       </c>
@@ -92415,7 +94917,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="3009" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3009" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3009" s="2" t="s">
         <v>2867</v>
       </c>
@@ -92435,7 +94937,7 @@
         <v>2916</v>
       </c>
     </row>
-    <row r="3010" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3010" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3010" s="2" t="s">
         <v>9297</v>
       </c>
@@ -92451,8 +94953,17 @@
       <c r="K3010" s="5" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="3011" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L3010" s="2" t="s">
+        <v>9396</v>
+      </c>
+      <c r="N3010" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P3010" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3011" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3011" s="2" t="s">
         <v>9299</v>
       </c>
@@ -92469,7 +94980,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3012" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3012" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3012" s="2" t="s">
         <v>9302</v>
       </c>
@@ -92486,7 +94997,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3013" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3013" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3013" s="2" t="s">
         <v>9305</v>
       </c>
@@ -92503,7 +95014,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3014" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3014" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3014" s="2" t="s">
         <v>9308</v>
       </c>
@@ -92520,7 +95031,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3015" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3015" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3015" s="2" t="s">
         <v>9311</v>
       </c>
@@ -92537,7 +95048,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3016" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3016" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3016" s="2" t="s">
         <v>9314</v>
       </c>
@@ -92554,7 +95065,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3017" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3017" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3017" s="2" t="s">
         <v>9317</v>
       </c>
@@ -92571,7 +95082,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3018" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3018" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3018" s="2" t="s">
         <v>9320</v>
       </c>
@@ -92588,7 +95099,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3019" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3019" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3019" s="2" t="s">
         <v>9323</v>
       </c>
@@ -92605,7 +95116,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3020" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3020" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3020" s="2" t="s">
         <v>9326</v>
       </c>
@@ -92622,7 +95133,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3021" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3021" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3021" s="2" t="s">
         <v>9329</v>
       </c>
@@ -92639,7 +95150,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3022" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3022" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3022" s="2" t="s">
         <v>9332</v>
       </c>
@@ -92656,7 +95167,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3023" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3023" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3023" s="2" t="s">
         <v>9335</v>
       </c>
@@ -92673,7 +95184,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3024" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3024" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3024" s="2" t="s">
         <v>9338</v>
       </c>
@@ -92962,7 +95473,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3041" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3041" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3041" s="2" t="s">
         <v>9390</v>
       </c>
@@ -92975,8 +95486,15 @@
       <c r="E3041" s="2" t="s">
         <v>9391</v>
       </c>
+      <c r="N3041" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P3041" s="2" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:P3041" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}"/>
   <conditionalFormatting sqref="A1">
     <cfRule type="duplicateValues" dxfId="41" priority="111"/>
   </conditionalFormatting>
@@ -93000,8 +95518,8 @@
     <cfRule type="duplicateValues" dxfId="34" priority="101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B95">
-    <cfRule type="duplicateValues" dxfId="33" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B125">
     <cfRule type="duplicateValues" dxfId="31" priority="78"/>
@@ -93021,9 +95539,9 @@
     <cfRule type="duplicateValues" dxfId="25" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E400">
-    <cfRule type="duplicateValues" dxfId="24" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="11"/>
     <cfRule type="duplicateValues" dxfId="21" priority="12"/>
     <cfRule type="duplicateValues" dxfId="20" priority="13"/>
     <cfRule type="duplicateValues" dxfId="19" priority="14"/>
@@ -93031,23 +95549,23 @@
     <cfRule type="duplicateValues" dxfId="17" priority="16" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E837:E840">
-    <cfRule type="duplicateValues" dxfId="16" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="23" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="24" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="23" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="24" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3010">
-    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="7" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="7" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="1" priority="8" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:I1">

--- a/data/input/sku_master.xlsx
+++ b/data/input/sku_master.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\Nitesh Gdrive\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E66BC89-0C0A-45A7-9C57-06BC79507239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D752A317-1BC5-4DD4-AB06-18AF8D76DF95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$3041</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$S$3041</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28474,28 +28474,6 @@
     </dxf>
     <dxf>
       <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -28558,6 +28536,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -28570,6 +28568,8 @@
     </dxf>
     <dxf>
       <font>
+        <condense val="0"/>
+        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -28900,7 +28900,6 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="AA"/>
@@ -95494,7 +95493,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P3041" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}"/>
+  <autoFilter ref="A1:S3041" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}"/>
   <conditionalFormatting sqref="A1">
     <cfRule type="duplicateValues" dxfId="41" priority="111"/>
   </conditionalFormatting>
@@ -95518,8 +95517,8 @@
     <cfRule type="duplicateValues" dxfId="34" priority="101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B95">
-    <cfRule type="duplicateValues" dxfId="33" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B125">
     <cfRule type="duplicateValues" dxfId="31" priority="78"/>
@@ -95539,9 +95538,9 @@
     <cfRule type="duplicateValues" dxfId="25" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E400">
-    <cfRule type="duplicateValues" dxfId="24" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="10"/>
     <cfRule type="duplicateValues" dxfId="21" priority="12"/>
     <cfRule type="duplicateValues" dxfId="20" priority="13"/>
     <cfRule type="duplicateValues" dxfId="19" priority="14"/>
@@ -95549,23 +95548,23 @@
     <cfRule type="duplicateValues" dxfId="17" priority="16" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E837:E840">
-    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="23" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="24" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="23" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="24" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3010">
-    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="7" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="7" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
     <cfRule type="duplicateValues" dxfId="1" priority="8" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:I1">

--- a/data/input/sku_master.xlsx
+++ b/data/input/sku_master.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\Nitesh Gdrive\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D752A317-1BC5-4DD4-AB06-18AF8D76DF95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93541365-ACED-4337-978C-5E9A4F9468AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$S$3041</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$3041</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17439" uniqueCount="9404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17604" uniqueCount="9503">
   <si>
     <t>FBA SKU</t>
   </si>
@@ -28252,6 +28252,303 @@
   </si>
   <si>
     <t>T-Code (EAN)</t>
+  </si>
+  <si>
+    <t>B07WGWGMBM</t>
+  </si>
+  <si>
+    <t>B0H1K1XJBK</t>
+  </si>
+  <si>
+    <t>B0H1JTMVMW</t>
+  </si>
+  <si>
+    <t>B0H1K4MHH4</t>
+  </si>
+  <si>
+    <t>B0H1JZFQRZ</t>
+  </si>
+  <si>
+    <t>B0H1K1W6GJ</t>
+  </si>
+  <si>
+    <t>B0H44QP75W</t>
+  </si>
+  <si>
+    <t>B0H44XPFRC</t>
+  </si>
+  <si>
+    <t>B0H8XG2F43</t>
+  </si>
+  <si>
+    <t>B0H8XXYKBC</t>
+  </si>
+  <si>
+    <t>B0H8Y4Z1KK</t>
+  </si>
+  <si>
+    <t>B0H1K56S6V</t>
+  </si>
+  <si>
+    <t>B0H1K216VW</t>
+  </si>
+  <si>
+    <t>B0H1JTL93N</t>
+  </si>
+  <si>
+    <t>B0H8Y38KKY</t>
+  </si>
+  <si>
+    <t>B0H1K2HBC9</t>
+  </si>
+  <si>
+    <t>B0H1KB3F39</t>
+  </si>
+  <si>
+    <t>B0H1K5RK6V</t>
+  </si>
+  <si>
+    <t>B0H8XZ9N1P</t>
+  </si>
+  <si>
+    <t>B0H1K4MHGJ</t>
+  </si>
+  <si>
+    <t>B0H1JY5HK3</t>
+  </si>
+  <si>
+    <t>B0H1JN7L2Z</t>
+  </si>
+  <si>
+    <t>B0H2ZX1W6F</t>
+  </si>
+  <si>
+    <t>B0H2ZVD5RS</t>
+  </si>
+  <si>
+    <t>B0H312FS95</t>
+  </si>
+  <si>
+    <t>B0H2ZX6LSV</t>
+  </si>
+  <si>
+    <t>B0H2ZMP3LX</t>
+  </si>
+  <si>
+    <t>B0H2ZZQDC9</t>
+  </si>
+  <si>
+    <t>B0H2ZPG58N</t>
+  </si>
+  <si>
+    <t>B0H1JXJ5LV</t>
+  </si>
+  <si>
+    <t>B0H1K1N4X4</t>
+  </si>
+  <si>
+    <t>B0H2ZT21NJ</t>
+  </si>
+  <si>
+    <t>B0H2ZR4K77</t>
+  </si>
+  <si>
+    <t>FBA80118</t>
+  </si>
+  <si>
+    <t>FBA80257</t>
+  </si>
+  <si>
+    <t>FBA80258</t>
+  </si>
+  <si>
+    <t>FBA80259</t>
+  </si>
+  <si>
+    <t>FBA80262</t>
+  </si>
+  <si>
+    <t>FBA80263</t>
+  </si>
+  <si>
+    <t>FBA80265</t>
+  </si>
+  <si>
+    <t>FBA80266</t>
+  </si>
+  <si>
+    <t>FBA80268</t>
+  </si>
+  <si>
+    <t>FBA80269</t>
+  </si>
+  <si>
+    <t>FBA80270</t>
+  </si>
+  <si>
+    <t>FBA80271</t>
+  </si>
+  <si>
+    <t>FBA80272</t>
+  </si>
+  <si>
+    <t>FBA80273</t>
+  </si>
+  <si>
+    <t>FBA80274</t>
+  </si>
+  <si>
+    <t>FBA80275</t>
+  </si>
+  <si>
+    <t>FBA80276</t>
+  </si>
+  <si>
+    <t>FBA80277</t>
+  </si>
+  <si>
+    <t>FBA80278</t>
+  </si>
+  <si>
+    <t>FBA80279</t>
+  </si>
+  <si>
+    <t>FBA80280</t>
+  </si>
+  <si>
+    <t>FBA80281</t>
+  </si>
+  <si>
+    <t>FBA80282</t>
+  </si>
+  <si>
+    <t>FBA80283</t>
+  </si>
+  <si>
+    <t>FBA80284</t>
+  </si>
+  <si>
+    <t>FBA80285</t>
+  </si>
+  <si>
+    <t>FBA80288</t>
+  </si>
+  <si>
+    <t>FBA80290</t>
+  </si>
+  <si>
+    <t>FBA80292</t>
+  </si>
+  <si>
+    <t>FBA80260</t>
+  </si>
+  <si>
+    <t>FBA80261</t>
+  </si>
+  <si>
+    <t>FBA80286</t>
+  </si>
+  <si>
+    <t>FBA80289</t>
+  </si>
+  <si>
+    <t>FS5661</t>
+  </si>
+  <si>
+    <t>AX2467</t>
+  </si>
+  <si>
+    <t>AX2468</t>
+  </si>
+  <si>
+    <t>AX2652</t>
+  </si>
+  <si>
+    <t>AX4409</t>
+  </si>
+  <si>
+    <t>AX4410</t>
+  </si>
+  <si>
+    <t>DZ4715</t>
+  </si>
+  <si>
+    <t>DZ4724</t>
+  </si>
+  <si>
+    <t>CE1135</t>
+  </si>
+  <si>
+    <t>CE1136</t>
+  </si>
+  <si>
+    <t>CE1137</t>
+  </si>
+  <si>
+    <t>ES5503</t>
+  </si>
+  <si>
+    <t>ES5504</t>
+  </si>
+  <si>
+    <t>ES5505</t>
+  </si>
+  <si>
+    <t>ES5512</t>
+  </si>
+  <si>
+    <t>FS6180</t>
+  </si>
+  <si>
+    <t>FS6181</t>
+  </si>
+  <si>
+    <t>FS6182</t>
+  </si>
+  <si>
+    <t>FS6189</t>
+  </si>
+  <si>
+    <t>FS6194</t>
+  </si>
+  <si>
+    <t>FS6198SET</t>
+  </si>
+  <si>
+    <t>FS6199SET</t>
+  </si>
+  <si>
+    <t>MK7618</t>
+  </si>
+  <si>
+    <t>MK7619</t>
+  </si>
+  <si>
+    <t>MK7620</t>
+  </si>
+  <si>
+    <t>MK7621</t>
+  </si>
+  <si>
+    <t>MK7641</t>
+  </si>
+  <si>
+    <t>MK9273</t>
+  </si>
+  <si>
+    <t>MK9277</t>
+  </si>
+  <si>
+    <t>AX4174</t>
+  </si>
+  <si>
+    <t>AX4175</t>
+  </si>
+  <si>
+    <t>MK7626</t>
+  </si>
+  <si>
+    <t>MK7642</t>
   </si>
 </sst>
 </file>
@@ -28900,6 +29197,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="AA"/>
@@ -29583,7 +29881,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}">
-  <dimension ref="A1:S3041"/>
+  <dimension ref="A1:S3074"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.88671875" style="2" bestFit="1" customWidth="1"/>
@@ -95492,8 +95790,569 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="3042" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3042" s="2" t="s">
+        <v>9437</v>
+      </c>
+      <c r="C3042" s="2" t="s">
+        <v>9404</v>
+      </c>
+      <c r="D3042" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3042" s="2" t="s">
+        <v>9470</v>
+      </c>
+      <c r="J3042" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3043" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3043" s="2" t="s">
+        <v>9438</v>
+      </c>
+      <c r="C3043" s="2" t="s">
+        <v>9405</v>
+      </c>
+      <c r="D3043" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3043" s="2" t="s">
+        <v>9471</v>
+      </c>
+      <c r="J3043" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3044" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3044" s="2" t="s">
+        <v>9439</v>
+      </c>
+      <c r="C3044" s="2" t="s">
+        <v>9406</v>
+      </c>
+      <c r="D3044" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3044" s="2" t="s">
+        <v>9472</v>
+      </c>
+      <c r="J3044" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3045" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3045" s="2" t="s">
+        <v>9440</v>
+      </c>
+      <c r="C3045" s="2" t="s">
+        <v>9407</v>
+      </c>
+      <c r="D3045" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3045" s="2" t="s">
+        <v>9473</v>
+      </c>
+      <c r="J3045" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3046" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3046" s="2" t="s">
+        <v>9441</v>
+      </c>
+      <c r="C3046" s="2" t="s">
+        <v>9408</v>
+      </c>
+      <c r="D3046" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3046" s="2" t="s">
+        <v>9474</v>
+      </c>
+      <c r="J3046" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3047" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3047" s="2" t="s">
+        <v>9442</v>
+      </c>
+      <c r="C3047" s="2" t="s">
+        <v>9409</v>
+      </c>
+      <c r="D3047" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3047" s="2" t="s">
+        <v>9475</v>
+      </c>
+      <c r="J3047" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3048" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3048" s="2" t="s">
+        <v>9443</v>
+      </c>
+      <c r="C3048" s="2" t="s">
+        <v>9410</v>
+      </c>
+      <c r="D3048" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3048" s="2" t="s">
+        <v>9476</v>
+      </c>
+      <c r="J3048" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3049" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3049" s="2" t="s">
+        <v>9444</v>
+      </c>
+      <c r="C3049" s="2" t="s">
+        <v>9411</v>
+      </c>
+      <c r="D3049" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3049" s="2" t="s">
+        <v>9477</v>
+      </c>
+      <c r="J3049" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3050" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3050" s="2" t="s">
+        <v>9445</v>
+      </c>
+      <c r="C3050" s="2" t="s">
+        <v>9412</v>
+      </c>
+      <c r="D3050" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3050" s="2" t="s">
+        <v>9478</v>
+      </c>
+      <c r="J3050" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3051" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3051" s="2" t="s">
+        <v>9446</v>
+      </c>
+      <c r="C3051" s="2" t="s">
+        <v>9413</v>
+      </c>
+      <c r="D3051" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3051" s="2" t="s">
+        <v>9479</v>
+      </c>
+      <c r="J3051" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3052" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3052" s="2" t="s">
+        <v>9447</v>
+      </c>
+      <c r="C3052" s="2" t="s">
+        <v>9414</v>
+      </c>
+      <c r="D3052" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3052" s="2" t="s">
+        <v>9480</v>
+      </c>
+      <c r="J3052" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3053" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3053" s="2" t="s">
+        <v>9448</v>
+      </c>
+      <c r="C3053" s="2" t="s">
+        <v>9415</v>
+      </c>
+      <c r="D3053" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3053" s="2" t="s">
+        <v>9481</v>
+      </c>
+      <c r="J3053" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3054" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3054" s="2" t="s">
+        <v>9449</v>
+      </c>
+      <c r="C3054" s="2" t="s">
+        <v>9416</v>
+      </c>
+      <c r="D3054" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3054" s="2" t="s">
+        <v>9482</v>
+      </c>
+      <c r="J3054" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3055" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3055" s="2" t="s">
+        <v>9450</v>
+      </c>
+      <c r="C3055" s="2" t="s">
+        <v>9417</v>
+      </c>
+      <c r="D3055" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3055" s="2" t="s">
+        <v>9483</v>
+      </c>
+      <c r="J3055" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3056" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3056" s="2" t="s">
+        <v>9451</v>
+      </c>
+      <c r="C3056" s="2" t="s">
+        <v>9418</v>
+      </c>
+      <c r="D3056" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3056" s="2" t="s">
+        <v>9484</v>
+      </c>
+      <c r="J3056" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3057" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3057" s="2" t="s">
+        <v>9452</v>
+      </c>
+      <c r="C3057" s="2" t="s">
+        <v>9419</v>
+      </c>
+      <c r="D3057" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3057" s="2" t="s">
+        <v>9485</v>
+      </c>
+      <c r="J3057" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3058" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3058" s="2" t="s">
+        <v>9453</v>
+      </c>
+      <c r="C3058" s="2" t="s">
+        <v>9420</v>
+      </c>
+      <c r="D3058" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3058" s="2" t="s">
+        <v>9486</v>
+      </c>
+      <c r="J3058" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3059" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3059" s="2" t="s">
+        <v>9454</v>
+      </c>
+      <c r="C3059" s="2" t="s">
+        <v>9421</v>
+      </c>
+      <c r="D3059" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3059" s="2" t="s">
+        <v>9487</v>
+      </c>
+      <c r="J3059" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3060" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3060" s="2" t="s">
+        <v>9455</v>
+      </c>
+      <c r="C3060" s="2" t="s">
+        <v>9422</v>
+      </c>
+      <c r="D3060" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3060" s="2" t="s">
+        <v>9488</v>
+      </c>
+      <c r="J3060" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3061" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3061" s="2" t="s">
+        <v>9456</v>
+      </c>
+      <c r="C3061" s="2" t="s">
+        <v>9423</v>
+      </c>
+      <c r="D3061" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3061" s="2" t="s">
+        <v>9489</v>
+      </c>
+      <c r="J3061" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3062" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3062" s="2" t="s">
+        <v>9457</v>
+      </c>
+      <c r="C3062" s="2" t="s">
+        <v>9424</v>
+      </c>
+      <c r="D3062" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3062" s="2" t="s">
+        <v>9490</v>
+      </c>
+      <c r="J3062" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3063" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3063" s="2" t="s">
+        <v>9458</v>
+      </c>
+      <c r="C3063" s="2" t="s">
+        <v>9425</v>
+      </c>
+      <c r="D3063" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3063" s="2" t="s">
+        <v>9491</v>
+      </c>
+      <c r="J3063" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3064" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3064" s="2" t="s">
+        <v>9459</v>
+      </c>
+      <c r="C3064" s="2" t="s">
+        <v>9426</v>
+      </c>
+      <c r="D3064" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3064" s="2" t="s">
+        <v>9492</v>
+      </c>
+      <c r="J3064" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3065" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3065" s="2" t="s">
+        <v>9460</v>
+      </c>
+      <c r="C3065" s="2" t="s">
+        <v>9427</v>
+      </c>
+      <c r="D3065" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3065" s="2" t="s">
+        <v>9493</v>
+      </c>
+      <c r="J3065" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3066" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3066" s="2" t="s">
+        <v>9461</v>
+      </c>
+      <c r="C3066" s="2" t="s">
+        <v>9428</v>
+      </c>
+      <c r="D3066" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3066" s="2" t="s">
+        <v>9494</v>
+      </c>
+      <c r="J3066" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3067" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3067" s="2" t="s">
+        <v>9462</v>
+      </c>
+      <c r="C3067" s="2" t="s">
+        <v>9429</v>
+      </c>
+      <c r="D3067" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3067" s="2" t="s">
+        <v>9495</v>
+      </c>
+      <c r="J3067" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3068" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3068" s="2" t="s">
+        <v>9463</v>
+      </c>
+      <c r="C3068" s="2" t="s">
+        <v>9430</v>
+      </c>
+      <c r="D3068" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3068" s="2" t="s">
+        <v>9496</v>
+      </c>
+      <c r="J3068" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3069" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3069" s="2" t="s">
+        <v>9464</v>
+      </c>
+      <c r="C3069" s="2" t="s">
+        <v>9431</v>
+      </c>
+      <c r="D3069" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3069" s="2" t="s">
+        <v>9497</v>
+      </c>
+      <c r="J3069" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3070" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3070" s="2" t="s">
+        <v>9465</v>
+      </c>
+      <c r="C3070" s="2" t="s">
+        <v>9432</v>
+      </c>
+      <c r="D3070" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3070" s="2" t="s">
+        <v>9498</v>
+      </c>
+      <c r="J3070" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3071" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3071" s="2" t="s">
+        <v>9466</v>
+      </c>
+      <c r="C3071" s="2" t="s">
+        <v>9433</v>
+      </c>
+      <c r="D3071" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3071" s="2" t="s">
+        <v>9499</v>
+      </c>
+      <c r="J3071" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3072" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3072" s="2" t="s">
+        <v>9467</v>
+      </c>
+      <c r="C3072" s="2" t="s">
+        <v>9434</v>
+      </c>
+      <c r="D3072" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3072" s="2" t="s">
+        <v>9500</v>
+      </c>
+      <c r="J3072" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3073" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3073" s="2" t="s">
+        <v>9468</v>
+      </c>
+      <c r="C3073" s="2" t="s">
+        <v>9435</v>
+      </c>
+      <c r="D3073" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3073" s="2" t="s">
+        <v>9501</v>
+      </c>
+      <c r="J3073" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3074" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3074" s="2" t="s">
+        <v>9469</v>
+      </c>
+      <c r="C3074" s="2" t="s">
+        <v>9436</v>
+      </c>
+      <c r="D3074" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3074" s="2" t="s">
+        <v>9502</v>
+      </c>
+      <c r="J3074" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S3041" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}"/>
+  <autoFilter ref="A1:P3041" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}"/>
   <conditionalFormatting sqref="A1">
     <cfRule type="duplicateValues" dxfId="41" priority="111"/>
   </conditionalFormatting>

--- a/data/input/sku_master.xlsx
+++ b/data/input/sku_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\Nitesh Gdrive\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93541365-ACED-4337-978C-5E9A4F9468AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{375909CC-C73F-450E-82FD-1A8FC1FF50F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$3041</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$3073</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17604" uniqueCount="9503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17595" uniqueCount="9502">
   <si>
     <t>FBA SKU</t>
   </si>
@@ -8623,9 +8623,6 @@
   </si>
   <si>
     <t>Monitor Speaker Stand Pair</t>
-  </si>
-  <si>
-    <t>FBM79783</t>
   </si>
   <si>
     <t>FBA80074</t>
@@ -28771,6 +28768,28 @@
     </dxf>
     <dxf>
       <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -28833,26 +28852,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -28865,8 +28864,6 @@
     </dxf>
     <dxf>
       <font>
-        <condense val="0"/>
-        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -29881,7 +29878,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}">
-  <dimension ref="A1:S3074"/>
+  <dimension ref="A1:S3073"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.88671875" style="2" bestFit="1" customWidth="1"/>
@@ -29920,16 +29917,16 @@
         <v>518</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="G1" s="8" t="s">
+        <v>2949</v>
+      </c>
+      <c r="H1" s="8" t="s">
         <v>2950</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>2951</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>2952</v>
       </c>
       <c r="J1" s="7" t="s">
         <v>515</v>
@@ -29944,22 +29941,22 @@
         <v>437</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>9398</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>9399</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
+        <v>9394</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>9400</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>9395</v>
-      </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>9401</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>9402</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>9403</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -29995,10 +29992,10 @@
         <v>1260</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P2" s="2">
         <v>8</v>
@@ -30024,10 +30021,10 @@
         <v>2399</v>
       </c>
       <c r="G3" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>2953</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>2954</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>174</v>
@@ -30045,10 +30042,10 @@
         <v>1260</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P3" s="2">
         <v>8</v>
@@ -30074,13 +30071,13 @@
         <v>3999</v>
       </c>
       <c r="G4" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H4" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="I4" s="5" t="s">
         <v>2954</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>2955</v>
       </c>
       <c r="J4" s="6" t="s">
         <v>355</v>
@@ -30095,10 +30092,10 @@
         <v>1786</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P4" s="2">
         <v>6</v>
@@ -30124,13 +30121,13 @@
         <v>699</v>
       </c>
       <c r="G5" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>2956</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="I5" s="5" t="s">
         <v>2957</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>2958</v>
       </c>
       <c r="J5" s="6" t="s">
         <v>355</v>
@@ -30145,10 +30142,10 @@
         <v>413</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P5" s="2">
         <v>36</v>
@@ -30174,10 +30171,10 @@
         <v>699</v>
       </c>
       <c r="G6" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>744</v>
@@ -30195,10 +30192,10 @@
         <v>418</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P6" s="2">
         <v>36</v>
@@ -30224,10 +30221,10 @@
         <v>699</v>
       </c>
       <c r="G7" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>744</v>
@@ -30245,10 +30242,10 @@
         <v>413</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P7" s="2">
         <v>36</v>
@@ -30287,10 +30284,10 @@
         <v>413</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P8" s="2">
         <v>36</v>
@@ -30329,10 +30326,10 @@
         <v>558</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P9" s="2">
         <v>36</v>
@@ -30371,10 +30368,10 @@
         <v>633</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P10" s="2">
         <v>40</v>
@@ -30413,10 +30410,10 @@
         <v>1073</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P11" s="2">
         <v>36</v>
@@ -30455,10 +30452,10 @@
         <v>527</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P12" s="2" t="e">
         <v>#N/A</v>
@@ -30484,10 +30481,10 @@
         <v>2199</v>
       </c>
       <c r="G13" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H13" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>744</v>
@@ -30505,10 +30502,10 @@
         <v>1512</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P13" s="2">
         <v>8</v>
@@ -30547,10 +30544,10 @@
         <v>282</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P14" s="2" t="e">
         <v>#N/A</v>
@@ -30589,10 +30586,10 @@
         <v>282</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P15" s="2" t="e">
         <v>#N/A</v>
@@ -30631,10 +30628,10 @@
         <v>193</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P16" s="2" t="e">
         <v>#N/A</v>
@@ -30660,13 +30657,13 @@
         <v>2399</v>
       </c>
       <c r="G17" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H17" s="5" t="s">
         <v>2956</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="I17" s="5" t="s">
         <v>2957</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>2958</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>355</v>
@@ -30681,10 +30678,10 @@
         <v>1377</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P17" s="2">
         <v>6</v>
@@ -30710,10 +30707,10 @@
         <v>2999</v>
       </c>
       <c r="G18" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H18" s="5" t="s">
         <v>2953</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>2954</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>5</v>
@@ -30731,10 +30728,10 @@
         <v>1162</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P18" s="2">
         <v>6</v>
@@ -30760,10 +30757,10 @@
         <v>999</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>744</v>
@@ -30781,10 +30778,10 @@
         <v>533</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P19" s="2">
         <v>40</v>
@@ -30810,10 +30807,10 @@
         <v>1999</v>
       </c>
       <c r="G20" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H20" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>744</v>
@@ -30831,10 +30828,10 @@
         <v>516</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P20" s="2">
         <v>60</v>
@@ -30860,10 +30857,10 @@
         <v>1059</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>744</v>
@@ -30881,10 +30878,10 @@
         <v>606</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P21" s="2">
         <v>60</v>
@@ -30910,10 +30907,10 @@
         <v>1999</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I22" s="5" t="s">
         <v>22</v>
@@ -30931,10 +30928,10 @@
         <v>987</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P22" s="2">
         <v>8</v>
@@ -30960,13 +30957,13 @@
         <v>1399</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>356</v>
@@ -30981,10 +30978,10 @@
         <v>728</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P23" s="2">
         <v>12</v>
@@ -31010,10 +31007,10 @@
         <v>799</v>
       </c>
       <c r="G24" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H24" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I24" s="5" t="s">
         <v>744</v>
@@ -31031,10 +31028,10 @@
         <v>378</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P24" s="2">
         <v>12</v>
@@ -31060,10 +31057,10 @@
         <v>799</v>
       </c>
       <c r="G25" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H25" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I25" s="5" t="s">
         <v>744</v>
@@ -31081,10 +31078,10 @@
         <v>389</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P25" s="2">
         <v>12</v>
@@ -31110,10 +31107,10 @@
         <v>3799</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I26" s="5" t="s">
         <v>744</v>
@@ -31131,10 +31128,10 @@
         <v>2357</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P26" s="2">
         <v>2</v>
@@ -31160,10 +31157,10 @@
         <v>7199</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I27" s="5" t="s">
         <v>744</v>
@@ -31181,10 +31178,10 @@
         <v>4052</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P27" s="2">
         <v>2</v>
@@ -31210,10 +31207,10 @@
         <v>1499</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I28" s="5" t="s">
         <v>142</v>
@@ -31231,10 +31228,10 @@
         <v>769</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P28" s="2">
         <v>20</v>
@@ -31260,10 +31257,10 @@
         <v>899</v>
       </c>
       <c r="G29" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H29" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I29" s="5" t="s">
         <v>744</v>
@@ -31281,10 +31278,10 @@
         <v>444</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P29" s="2">
         <v>60</v>
@@ -31310,13 +31307,13 @@
         <v>999</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>2962</v>
+        <v>2961</v>
       </c>
       <c r="J30" s="6" t="s">
         <v>356</v>
@@ -31331,10 +31328,10 @@
         <v>490</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P30" s="2">
         <v>60</v>
@@ -31360,13 +31357,13 @@
         <v>1499</v>
       </c>
       <c r="G31" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H31" s="5" t="s">
         <v>2956</v>
       </c>
-      <c r="H31" s="5" t="s">
+      <c r="I31" s="5" t="s">
         <v>2957</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>2958</v>
       </c>
       <c r="J31" s="6" t="s">
         <v>356</v>
@@ -31381,10 +31378,10 @@
         <v>714</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P31" s="2">
         <v>60</v>
@@ -31410,10 +31407,10 @@
         <v>799</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I32" s="5" t="s">
         <v>104</v>
@@ -31431,10 +31428,10 @@
         <v>412</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P32" s="2">
         <v>50</v>
@@ -31460,10 +31457,10 @@
         <v>799</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I33" s="5" t="s">
         <v>744</v>
@@ -31481,10 +31478,10 @@
         <v>413</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P33" s="2">
         <v>50</v>
@@ -31523,10 +31520,10 @@
         <v>448</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P34" s="2">
         <v>20</v>
@@ -31563,10 +31560,10 @@
         <v>448</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P35" s="2" t="e">
         <v>#N/A</v>
@@ -31592,10 +31589,10 @@
         <v>999</v>
       </c>
       <c r="G36" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H36" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I36" s="5" t="s">
         <v>744</v>
@@ -31613,10 +31610,10 @@
         <v>409</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P36" s="2">
         <v>40</v>
@@ -31624,11 +31621,11 @@
     </row>
     <row r="37" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>3022</v>
+        <v>3021</v>
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5" t="s">
-        <v>3023</v>
+        <v>3022</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>6</v>
@@ -31653,10 +31650,10 @@
         <v>409</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P37" s="2">
         <v>40</v>
@@ -31664,7 +31661,7 @@
     </row>
     <row r="38" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>23</v>
@@ -31682,10 +31679,10 @@
         <v>1099</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I38" s="5" t="s">
         <v>744</v>
@@ -31703,10 +31700,10 @@
         <v>710</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P38" s="2">
         <v>60</v>
@@ -31745,10 +31742,10 @@
         <v>356</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P39" s="2">
         <v>50</v>
@@ -31785,10 +31782,10 @@
         <v>356</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P40" s="2">
         <v>50</v>
@@ -31814,13 +31811,13 @@
         <v>1199</v>
       </c>
       <c r="G41" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H41" s="5" t="s">
         <v>2956</v>
       </c>
-      <c r="H41" s="5" t="s">
+      <c r="I41" s="5" t="s">
         <v>2957</v>
-      </c>
-      <c r="I41" s="5" t="s">
-        <v>2958</v>
       </c>
       <c r="J41" s="6" t="s">
         <v>355</v>
@@ -31835,10 +31832,10 @@
         <v>562</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P41" s="2">
         <v>18</v>
@@ -31864,13 +31861,13 @@
         <v>299</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="J42" s="6" t="s">
         <v>356</v>
@@ -31885,10 +31882,10 @@
         <v>295</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P42" s="2">
         <v>100</v>
@@ -31914,13 +31911,13 @@
         <v>299</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="J43" s="6" t="s">
         <v>356</v>
@@ -31935,10 +31932,10 @@
         <v>295</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P43" s="2">
         <v>100</v>
@@ -31977,10 +31974,10 @@
         <v>193</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P44" s="2">
         <v>200</v>
@@ -32006,10 +32003,10 @@
         <v>1249</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I45" s="5" t="s">
         <v>744</v>
@@ -32027,10 +32024,10 @@
         <v>672</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P45" s="2">
         <v>20</v>
@@ -32056,10 +32053,10 @@
         <v>1699</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I46" s="5" t="s">
         <v>744</v>
@@ -32077,10 +32074,10 @@
         <v>896</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P46" s="2">
         <v>20</v>
@@ -32106,10 +32103,10 @@
         <v>1949</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I47" s="5" t="s">
         <v>744</v>
@@ -32127,10 +32124,10 @@
         <v>868</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P47" s="2">
         <v>12</v>
@@ -32156,10 +32153,10 @@
         <v>2699</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I48" s="5" t="s">
         <v>744</v>
@@ -32177,10 +32174,10 @@
         <v>961</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P48" s="2">
         <v>60</v>
@@ -32206,10 +32203,10 @@
         <v>3399</v>
       </c>
       <c r="G49" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H49" s="5" t="s">
         <v>2953</v>
-      </c>
-      <c r="H49" s="5" t="s">
-        <v>2954</v>
       </c>
       <c r="I49" s="5" t="s">
         <v>8</v>
@@ -32227,10 +32224,10 @@
         <v>1381</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P49" s="2">
         <v>8</v>
@@ -32256,10 +32253,10 @@
         <v>1999</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I50" s="5" t="s">
         <v>744</v>
@@ -32277,10 +32274,10 @@
         <v>810</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P50" s="2">
         <v>50</v>
@@ -32306,10 +32303,10 @@
         <v>1699</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I51" s="5" t="s">
         <v>744</v>
@@ -32327,10 +32324,10 @@
         <v>1089</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P51" s="2">
         <v>50</v>
@@ -32369,10 +32366,10 @@
         <v>1532</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P52" s="2" t="e">
         <v>#N/A</v>
@@ -32398,10 +32395,10 @@
         <v>209</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I53" s="5" t="s">
         <v>744</v>
@@ -32419,10 +32416,10 @@
         <v>1088</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P53" s="2">
         <v>6</v>
@@ -32448,10 +32445,10 @@
         <v>2499</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I54" s="5" t="s">
         <v>84</v>
@@ -32469,10 +32466,10 @@
         <v>1291</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P54" s="2">
         <v>20</v>
@@ -32498,10 +32495,10 @@
         <v>1499</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I55" s="5" t="s">
         <v>50</v>
@@ -32519,10 +32516,10 @@
         <v>560</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P55" s="2">
         <v>40</v>
@@ -32548,13 +32545,13 @@
         <v>999</v>
       </c>
       <c r="G56" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H56" s="5" t="s">
         <v>2956</v>
       </c>
-      <c r="H56" s="5" t="s">
+      <c r="I56" s="5" t="s">
         <v>2957</v>
-      </c>
-      <c r="I56" s="5" t="s">
-        <v>2958</v>
       </c>
       <c r="J56" s="6" t="s">
         <v>355</v>
@@ -32569,10 +32566,10 @@
         <v>1250</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P56" s="2">
         <v>18</v>
@@ -32598,10 +32595,10 @@
         <v>1199</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I57" s="5" t="s">
         <v>160</v>
@@ -32619,10 +32616,10 @@
         <v>483</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P57" s="2">
         <v>20</v>
@@ -32661,10 +32658,10 @@
         <v>2775</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P58" s="2" t="e">
         <v>#N/A</v>
@@ -32690,10 +32687,10 @@
         <v>3899</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I59" s="5" t="s">
         <v>744</v>
@@ -32711,10 +32708,10 @@
         <v>2775</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P59" s="2">
         <v>6</v>
@@ -32740,10 +32737,10 @@
         <v>1529</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I60" s="5" t="s">
         <v>744</v>
@@ -32761,10 +32758,10 @@
         <v>594</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P60" s="2">
         <v>40</v>
@@ -32790,10 +32787,10 @@
         <v>1399</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I61" s="5" t="s">
         <v>40</v>
@@ -32811,10 +32808,10 @@
         <v>560</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P61" s="2">
         <v>40</v>
@@ -32840,10 +32837,10 @@
         <v>1699</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I62" s="5" t="s">
         <v>178</v>
@@ -32861,10 +32858,10 @@
         <v>865</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P62" s="2">
         <v>24</v>
@@ -32890,10 +32887,10 @@
         <v>1949</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I63" s="5" t="s">
         <v>176</v>
@@ -32911,10 +32908,10 @@
         <v>814</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P63" s="2">
         <v>24</v>
@@ -32940,10 +32937,10 @@
         <v>1999</v>
       </c>
       <c r="G64" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H64" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H64" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I64" s="5" t="s">
         <v>744</v>
@@ -32961,10 +32958,10 @@
         <v>1392</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P64" s="2">
         <v>20</v>
@@ -32990,13 +32987,13 @@
         <v>1999</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>2965</v>
+        <v>2964</v>
       </c>
       <c r="J65" s="6" t="s">
         <v>355</v>
@@ -33011,10 +33008,10 @@
         <v>803</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P65" s="2">
         <v>20</v>
@@ -33040,10 +33037,10 @@
         <v>1999</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I66" s="5" t="s">
         <v>744</v>
@@ -33061,10 +33058,10 @@
         <v>1302</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P66" s="2">
         <v>32</v>
@@ -33090,13 +33087,13 @@
         <v>1999</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H67" s="5" t="s">
+        <v>2956</v>
+      </c>
+      <c r="I67" s="5" t="s">
         <v>2957</v>
-      </c>
-      <c r="I67" s="5" t="s">
-        <v>2958</v>
       </c>
       <c r="J67" s="6" t="s">
         <v>356</v>
@@ -33111,10 +33108,10 @@
         <v>594</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P67" s="2">
         <v>20</v>
@@ -33140,13 +33137,13 @@
         <v>1399</v>
       </c>
       <c r="G68" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H68" s="5" t="s">
         <v>2956</v>
       </c>
-      <c r="H68" s="5" t="s">
+      <c r="I68" s="5" t="s">
         <v>2957</v>
-      </c>
-      <c r="I68" s="5" t="s">
-        <v>2958</v>
       </c>
       <c r="J68" s="6" t="s">
         <v>355</v>
@@ -33161,10 +33158,10 @@
         <v>716</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P68" s="2">
         <v>6</v>
@@ -33203,10 +33200,10 @@
         <v>460</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O69" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P69" s="2">
         <v>50</v>
@@ -33232,10 +33229,10 @@
         <v>1999</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I70" s="5" t="s">
         <v>20</v>
@@ -33253,10 +33250,10 @@
         <v>984</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P70" s="2">
         <v>12</v>
@@ -33282,10 +33279,10 @@
         <v>2099</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I71" s="5" t="s">
         <v>32</v>
@@ -33303,10 +33300,10 @@
         <v>980</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="O71" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P71" s="2">
         <v>12</v>
@@ -33332,13 +33329,13 @@
         <v>2299</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="J72" s="6" t="s">
         <v>356</v>
@@ -33353,10 +33350,10 @@
         <v>1095</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O72" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P72" s="2">
         <v>12</v>
@@ -33382,13 +33379,13 @@
         <v>2049</v>
       </c>
       <c r="G73" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H73" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H73" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I73" s="5" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="J73" s="6" t="s">
         <v>356</v>
@@ -33403,10 +33400,10 @@
         <v>852</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O73" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P73" s="2">
         <v>12</v>
@@ -33432,13 +33429,13 @@
         <v>2499</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H74" s="5" t="s">
+        <v>2956</v>
+      </c>
+      <c r="I74" s="5" t="s">
         <v>2957</v>
-      </c>
-      <c r="I74" s="5" t="s">
-        <v>2958</v>
       </c>
       <c r="J74" s="6" t="s">
         <v>355</v>
@@ -33453,10 +33450,10 @@
         <v>1112</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O74" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P74" s="2">
         <v>24</v>
@@ -33482,10 +33479,10 @@
         <v>2299</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I75" s="5" t="s">
         <v>52</v>
@@ -33503,10 +33500,10 @@
         <v>1063</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O75" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P75" s="2">
         <v>16</v>
@@ -33532,13 +33529,13 @@
         <v>5999</v>
       </c>
       <c r="G76" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H76" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H76" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I76" s="5" t="s">
-        <v>2968</v>
+        <v>2967</v>
       </c>
       <c r="J76" s="6" t="s">
         <v>355</v>
@@ -33553,10 +33550,10 @@
         <v>2695</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="O76" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P76" s="2">
         <v>4</v>
@@ -33595,10 +33592,10 @@
         <v>721</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O77" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P77" s="2" t="e">
         <v>#N/A</v>
@@ -33624,10 +33621,10 @@
         <v>1799</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I78" s="5" t="s">
         <v>744</v>
@@ -33645,10 +33642,10 @@
         <v>536</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O78" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P78" s="2">
         <v>50</v>
@@ -33687,10 +33684,10 @@
         <v>1307</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O79" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P79" s="2">
         <v>4</v>
@@ -33729,10 +33726,10 @@
         <v>709</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O80" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P80" s="2">
         <v>20</v>
@@ -33758,10 +33755,10 @@
         <v>2499</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I81" s="5" t="s">
         <v>744</v>
@@ -33779,10 +33776,10 @@
         <v>1345</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O81" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P81" s="2">
         <v>30</v>
@@ -33821,10 +33818,10 @@
         <v>710</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O82" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P82" s="2" t="e">
         <v>#N/A</v>
@@ -33863,10 +33860,10 @@
         <v>1306</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O83" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P83" s="2" t="e">
         <v>#N/A</v>
@@ -33892,10 +33889,10 @@
         <v>1699</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I84" s="5" t="s">
         <v>744</v>
@@ -33913,10 +33910,10 @@
         <v>1306</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O84" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P84" s="2">
         <v>10</v>
@@ -33942,10 +33939,10 @@
         <v>2999</v>
       </c>
       <c r="G85" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H85" s="5" t="s">
         <v>2953</v>
-      </c>
-      <c r="H85" s="5" t="s">
-        <v>2954</v>
       </c>
       <c r="I85" s="5" t="s">
         <v>241</v>
@@ -33963,10 +33960,10 @@
         <v>1014</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O85" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P85" s="2">
         <v>20</v>
@@ -33992,13 +33989,13 @@
         <v>1499</v>
       </c>
       <c r="G86" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H86" s="5" t="s">
         <v>2956</v>
       </c>
-      <c r="H86" s="5" t="s">
+      <c r="I86" s="5" t="s">
         <v>2957</v>
-      </c>
-      <c r="I86" s="5" t="s">
-        <v>2958</v>
       </c>
       <c r="J86" s="6" t="s">
         <v>356</v>
@@ -34013,10 +34010,10 @@
         <v>1039</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O86" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P86" s="2" t="e">
         <v>#N/A</v>
@@ -34024,7 +34021,7 @@
     </row>
     <row r="87" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
-        <v>2944</v>
+        <v>2943</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>67</v>
@@ -34055,10 +34052,10 @@
         <v>1039</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O87" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P87" s="2">
         <v>20</v>
@@ -34097,10 +34094,10 @@
         <v>1837</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="O88" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P88" s="2">
         <v>6</v>
@@ -34139,10 +34136,10 @@
         <v>890</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O89" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P89" s="2">
         <v>8</v>
@@ -34181,10 +34178,10 @@
         <v>714</v>
       </c>
       <c r="N90" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O90" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P90" s="2">
         <v>30</v>
@@ -34223,10 +34220,10 @@
         <v>1422</v>
       </c>
       <c r="N91" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O91" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P91" s="2">
         <v>30</v>
@@ -34252,10 +34249,10 @@
         <v>1799</v>
       </c>
       <c r="G92" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H92" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H92" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I92" s="5" t="s">
         <v>744</v>
@@ -34273,10 +34270,10 @@
         <v>926</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O92" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P92" s="2">
         <v>20</v>
@@ -34315,10 +34312,10 @@
         <v>765</v>
       </c>
       <c r="N93" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O93" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P93" s="2">
         <v>10</v>
@@ -34326,7 +34323,7 @@
     </row>
     <row r="94" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
-        <v>3024</v>
+        <v>3023</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>123</v>
@@ -34357,10 +34354,10 @@
         <v>970</v>
       </c>
       <c r="N94" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O94" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P94" s="2">
         <v>6</v>
@@ -34386,13 +34383,13 @@
         <v>1499</v>
       </c>
       <c r="G95" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H95" s="5" t="s">
         <v>2956</v>
       </c>
-      <c r="H95" s="5" t="s">
+      <c r="I95" s="5" t="s">
         <v>2957</v>
-      </c>
-      <c r="I95" s="5" t="s">
-        <v>2958</v>
       </c>
       <c r="J95" s="6" t="s">
         <v>355</v>
@@ -34407,10 +34404,10 @@
         <v>954</v>
       </c>
       <c r="N95" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="O95" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P95" s="2">
         <v>9</v>
@@ -34436,13 +34433,13 @@
         <v>3149</v>
       </c>
       <c r="G96" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H96" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H96" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I96" s="5" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="J96" s="6" t="s">
         <v>355</v>
@@ -34457,10 +34454,10 @@
         <v>1443</v>
       </c>
       <c r="N96" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O96" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P96" s="2">
         <v>6</v>
@@ -34486,13 +34483,13 @@
         <v>799</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H97" s="5" t="s">
+        <v>2956</v>
+      </c>
+      <c r="I97" s="5" t="s">
         <v>2957</v>
-      </c>
-      <c r="I97" s="5" t="s">
-        <v>2958</v>
       </c>
       <c r="J97" s="6" t="s">
         <v>356</v>
@@ -34507,10 +34504,10 @@
         <v>371</v>
       </c>
       <c r="N97" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O97" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P97" s="2">
         <v>50</v>
@@ -34549,10 +34546,10 @@
         <v>975</v>
       </c>
       <c r="N98" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O98" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P98" s="2">
         <v>12</v>
@@ -34591,10 +34588,10 @@
         <v>969</v>
       </c>
       <c r="N99" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="O99" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P99" s="2">
         <v>14</v>
@@ -34633,10 +34630,10 @@
         <v>1175</v>
       </c>
       <c r="N100" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O100" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P100" s="2">
         <v>4</v>
@@ -34662,10 +34659,10 @@
         <v>999</v>
       </c>
       <c r="G101" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H101" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H101" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I101" s="5" t="s">
         <v>744</v>
@@ -34683,10 +34680,10 @@
         <v>501</v>
       </c>
       <c r="N101" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O101" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P101" s="2">
         <v>36</v>
@@ -34712,13 +34709,13 @@
         <v>999</v>
       </c>
       <c r="G102" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H102" s="5" t="s">
         <v>2956</v>
       </c>
-      <c r="H102" s="5" t="s">
+      <c r="I102" s="5" t="s">
         <v>2957</v>
-      </c>
-      <c r="I102" s="5" t="s">
-        <v>2958</v>
       </c>
       <c r="J102" s="6" t="s">
         <v>355</v>
@@ -34733,10 +34730,10 @@
         <v>501</v>
       </c>
       <c r="N102" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O102" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P102" s="2">
         <v>36</v>
@@ -34762,13 +34759,13 @@
         <v>5999</v>
       </c>
       <c r="G103" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H103" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H103" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I103" s="5" t="s">
-        <v>2970</v>
+        <v>2969</v>
       </c>
       <c r="J103" s="6" t="s">
         <v>355</v>
@@ -34783,10 +34780,10 @@
         <v>3423</v>
       </c>
       <c r="N103" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="O103" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P103" s="2">
         <v>1</v>
@@ -34812,10 +34809,10 @@
         <v>1999</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H104" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I104" s="5" t="s">
         <v>54</v>
@@ -34833,10 +34830,10 @@
         <v>829</v>
       </c>
       <c r="N104" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O104" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P104" s="2">
         <v>6</v>
@@ -34862,10 +34859,10 @@
         <v>1799</v>
       </c>
       <c r="G105" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H105" s="5" t="s">
         <v>2953</v>
-      </c>
-      <c r="H105" s="5" t="s">
-        <v>2954</v>
       </c>
       <c r="I105" s="5" t="s">
         <v>42</v>
@@ -34883,10 +34880,10 @@
         <v>818</v>
       </c>
       <c r="N105" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O105" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P105" s="2">
         <v>12</v>
@@ -34912,13 +34909,13 @@
         <v>16990</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H106" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I106" s="5" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
       <c r="J106" s="6" t="s">
         <v>355</v>
@@ -34933,10 +34930,10 @@
         <v>10158</v>
       </c>
       <c r="N106" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="O106" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P106" s="2">
         <v>1</v>
@@ -34975,10 +34972,10 @@
         <v>6416</v>
       </c>
       <c r="N107" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="O107" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P107" s="2">
         <v>1</v>
@@ -35017,10 +35014,10 @@
         <v>781</v>
       </c>
       <c r="N108" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O108" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P108" s="2" t="e">
         <v>#N/A</v>
@@ -35046,13 +35043,13 @@
         <v>899</v>
       </c>
       <c r="G109" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H109" s="5" t="s">
         <v>2956</v>
       </c>
-      <c r="H109" s="5" t="s">
+      <c r="I109" s="5" t="s">
         <v>2957</v>
-      </c>
-      <c r="I109" s="5" t="s">
-        <v>2958</v>
       </c>
       <c r="J109" s="6" t="s">
         <v>356</v>
@@ -35067,10 +35064,10 @@
         <v>436</v>
       </c>
       <c r="N109" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O109" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P109" s="2">
         <v>20</v>
@@ -35096,13 +35093,13 @@
         <v>2119</v>
       </c>
       <c r="G110" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H110" s="5" t="s">
         <v>2956</v>
       </c>
-      <c r="H110" s="5" t="s">
+      <c r="I110" s="5" t="s">
         <v>2957</v>
-      </c>
-      <c r="I110" s="5" t="s">
-        <v>2958</v>
       </c>
       <c r="J110" s="6" t="s">
         <v>356</v>
@@ -35117,10 +35114,10 @@
         <v>980</v>
       </c>
       <c r="N110" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O110" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P110" s="2">
         <v>12</v>
@@ -35159,10 +35156,10 @@
         <v>6146</v>
       </c>
       <c r="N111" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O111" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P111" s="2">
         <v>1</v>
@@ -35188,10 +35185,10 @@
         <v>5999</v>
       </c>
       <c r="G112" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H112" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H112" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I112" s="5" t="s">
         <v>744</v>
@@ -35209,10 +35206,10 @@
         <v>3229</v>
       </c>
       <c r="N112" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O112" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P112" s="2">
         <v>6</v>
@@ -35251,10 +35248,10 @@
         <v>963</v>
       </c>
       <c r="N113" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O113" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P113" s="2">
         <v>16</v>
@@ -35280,10 +35277,10 @@
         <v>4199</v>
       </c>
       <c r="G114" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H114" s="5" t="s">
         <v>2953</v>
-      </c>
-      <c r="H114" s="5" t="s">
-        <v>2954</v>
       </c>
       <c r="I114" s="5" t="s">
         <v>206</v>
@@ -35301,10 +35298,10 @@
         <v>2005</v>
       </c>
       <c r="N114" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O114" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P114" s="2">
         <v>4</v>
@@ -35330,10 +35327,10 @@
         <v>3499</v>
       </c>
       <c r="G115" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H115" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H115" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I115" s="5" t="s">
         <v>744</v>
@@ -35351,10 +35348,10 @@
         <v>1177</v>
       </c>
       <c r="N115" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O115" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P115" s="2">
         <v>20</v>
@@ -35393,10 +35390,10 @@
         <v>1227</v>
       </c>
       <c r="N116" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O116" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P116" s="2">
         <v>10</v>
@@ -35435,10 +35432,10 @@
         <v>2827</v>
       </c>
       <c r="N117" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O117" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P117" s="2" t="e">
         <v>#N/A</v>
@@ -35464,10 +35461,10 @@
         <v>799</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H118" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I118" s="5" t="s">
         <v>154</v>
@@ -35485,10 +35482,10 @@
         <v>373</v>
       </c>
       <c r="N118" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O118" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P118" s="2">
         <v>50</v>
@@ -35514,10 +35511,10 @@
         <v>749</v>
       </c>
       <c r="G119" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H119" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I119" s="5" t="s">
         <v>744</v>
@@ -35535,10 +35532,10 @@
         <v>324</v>
       </c>
       <c r="N119" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O119" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P119" s="2">
         <v>12</v>
@@ -35564,10 +35561,10 @@
         <v>599</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H120" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I120" s="5" t="s">
         <v>744</v>
@@ -35585,10 +35582,10 @@
         <v>261</v>
       </c>
       <c r="N120" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O120" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P120" s="2">
         <v>60</v>
@@ -35614,10 +35611,10 @@
         <v>599</v>
       </c>
       <c r="G121" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H121" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I121" s="5" t="s">
         <v>744</v>
@@ -35635,10 +35632,10 @@
         <v>297</v>
       </c>
       <c r="N121" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O121" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P121" s="2">
         <v>50</v>
@@ -35664,10 +35661,10 @@
         <v>2399</v>
       </c>
       <c r="G122" s="5" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I122" s="5" t="s">
         <v>744</v>
@@ -35685,10 +35682,10 @@
         <v>1307</v>
       </c>
       <c r="N122" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O122" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P122" s="2">
         <v>8</v>
@@ -35714,10 +35711,10 @@
         <v>399</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H123" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I123" s="5" t="s">
         <v>1612</v>
@@ -35735,10 +35732,10 @@
         <v>145</v>
       </c>
       <c r="N123" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O123" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P123" s="2">
         <v>100</v>
@@ -35764,10 +35761,10 @@
         <v>4999</v>
       </c>
       <c r="G124" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H124" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I124" s="5" t="s">
         <v>58</v>
@@ -35785,10 +35782,10 @@
         <v>2004</v>
       </c>
       <c r="N124" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O124" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P124" s="2">
         <v>20</v>
@@ -35814,13 +35811,13 @@
         <v>1499</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H125" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I125" s="5" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
       <c r="J125" s="6" t="s">
         <v>356</v>
@@ -35835,10 +35832,10 @@
         <v>663</v>
       </c>
       <c r="N125" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O125" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P125" s="2">
         <v>12</v>
@@ -35864,10 +35861,10 @@
         <v>1499</v>
       </c>
       <c r="G126" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H126" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I126" s="5" t="s">
         <v>239</v>
@@ -35885,10 +35882,10 @@
         <v>899</v>
       </c>
       <c r="N126" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O126" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P126" s="2">
         <v>40</v>
@@ -35927,10 +35924,10 @@
         <v>82</v>
       </c>
       <c r="N127" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O127" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P127" s="2" t="e">
         <v>#N/A</v>
@@ -35969,10 +35966,10 @@
         <v>40</v>
       </c>
       <c r="N128" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O128" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P128" s="2" t="e">
         <v>#N/A</v>
@@ -36011,10 +36008,10 @@
         <v>300</v>
       </c>
       <c r="N129" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O129" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P129" s="2" t="e">
         <v>#N/A</v>
@@ -36053,10 +36050,10 @@
         <v>250</v>
       </c>
       <c r="N130" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O130" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P130" s="2" t="e">
         <v>#N/A</v>
@@ -36095,10 +36092,10 @@
         <v>108</v>
       </c>
       <c r="N131" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O131" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P131" s="2" t="e">
         <v>#N/A</v>
@@ -36137,10 +36134,10 @@
         <v>145</v>
       </c>
       <c r="N132" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O132" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P132" s="2" t="e">
         <v>#N/A</v>
@@ -36179,10 +36176,10 @@
         <v>35</v>
       </c>
       <c r="N133" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O133" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P133" s="2" t="e">
         <v>#N/A</v>
@@ -36221,10 +36218,10 @@
         <v>45</v>
       </c>
       <c r="N134" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O134" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P134" s="2" t="e">
         <v>#N/A</v>
@@ -36263,10 +36260,10 @@
         <v>350</v>
       </c>
       <c r="N135" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O135" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P135" s="2" t="e">
         <v>#N/A</v>
@@ -36305,10 +36302,10 @@
         <v>350</v>
       </c>
       <c r="N136" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O136" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P136" s="2" t="e">
         <v>#N/A</v>
@@ -36347,10 +36344,10 @@
         <v>350</v>
       </c>
       <c r="N137" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O137" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P137" s="2" t="e">
         <v>#N/A</v>
@@ -36389,10 +36386,10 @@
         <v>45</v>
       </c>
       <c r="N138" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O138" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P138" s="2" t="e">
         <v>#N/A</v>
@@ -36431,10 +36428,10 @@
         <v>45</v>
       </c>
       <c r="N139" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O139" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P139" s="2" t="e">
         <v>#N/A</v>
@@ -36473,10 +36470,10 @@
         <v>45</v>
       </c>
       <c r="N140" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O140" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P140" s="2" t="e">
         <v>#N/A</v>
@@ -36515,10 +36512,10 @@
         <v>45</v>
       </c>
       <c r="N141" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O141" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P141" s="2" t="e">
         <v>#N/A</v>
@@ -36557,10 +36554,10 @@
         <v>2350</v>
       </c>
       <c r="N142" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O142" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P142" s="2" t="e">
         <v>#N/A</v>
@@ -36599,10 +36596,10 @@
         <v>500</v>
       </c>
       <c r="N143" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O143" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P143" s="2" t="e">
         <v>#N/A</v>
@@ -36641,10 +36638,10 @@
         <v>350</v>
       </c>
       <c r="N144" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O144" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P144" s="2" t="e">
         <v>#N/A</v>
@@ -36683,10 +36680,10 @@
         <v>350</v>
       </c>
       <c r="N145" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O145" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P145" s="2" t="e">
         <v>#N/A</v>
@@ -36725,10 +36722,10 @@
         <v>2000</v>
       </c>
       <c r="N146" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O146" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P146" s="2" t="e">
         <v>#N/A</v>
@@ -36767,10 +36764,10 @@
         <v>550</v>
       </c>
       <c r="N147" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O147" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P147" s="2" t="e">
         <v>#N/A</v>
@@ -36796,10 +36793,10 @@
         <v>5999</v>
       </c>
       <c r="G148" s="5" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="H148" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I148" s="5" t="s">
         <v>744</v>
@@ -36817,10 +36814,10 @@
         <v>0</v>
       </c>
       <c r="N148" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O148" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P148" s="2">
         <v>9</v>
@@ -36828,7 +36825,7 @@
     </row>
     <row r="149" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="5" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B149" s="14"/>
       <c r="C149" s="5" t="s">
@@ -36842,7 +36839,7 @@
       </c>
       <c r="F149" s="5"/>
       <c r="G149" s="5" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="H149" s="5"/>
       <c r="I149" s="5"/>
@@ -36859,10 +36856,10 @@
         <v>0</v>
       </c>
       <c r="N149" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O149" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P149" s="2">
         <v>9</v>
@@ -36884,13 +36881,13 @@
       </c>
       <c r="F150" s="5"/>
       <c r="G150" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H150" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H150" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I150" s="5" t="s">
-        <v>2979</v>
+        <v>2978</v>
       </c>
       <c r="J150" s="5" t="s">
         <v>1097</v>
@@ -36919,13 +36916,13 @@
       </c>
       <c r="F151" s="5"/>
       <c r="G151" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H151" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H151" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I151" s="5" t="s">
-        <v>2980</v>
+        <v>2979</v>
       </c>
       <c r="J151" s="5" t="s">
         <v>1098</v>
@@ -36954,13 +36951,13 @@
       </c>
       <c r="F152" s="5"/>
       <c r="G152" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H152" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H152" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I152" s="5" t="s">
-        <v>2981</v>
+        <v>2980</v>
       </c>
       <c r="J152" s="5" t="s">
         <v>1100</v>
@@ -36989,13 +36986,13 @@
       </c>
       <c r="F153" s="5"/>
       <c r="G153" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H153" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H153" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I153" s="5" t="s">
-        <v>2980</v>
+        <v>2979</v>
       </c>
       <c r="J153" s="5" t="s">
         <v>1098</v>
@@ -37024,13 +37021,13 @@
       </c>
       <c r="F154" s="5"/>
       <c r="G154" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H154" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H154" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I154" s="5" t="s">
-        <v>2982</v>
+        <v>2981</v>
       </c>
       <c r="J154" s="5" t="s">
         <v>1103</v>
@@ -37059,10 +37056,10 @@
       </c>
       <c r="F155" s="5"/>
       <c r="G155" s="5" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="H155" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I155" s="5" t="s">
         <v>744</v>
@@ -37094,10 +37091,10 @@
       </c>
       <c r="F156" s="16"/>
       <c r="G156" s="16" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H156" s="16" t="s">
         <v>2956</v>
-      </c>
-      <c r="H156" s="16" t="s">
-        <v>2957</v>
       </c>
       <c r="I156" s="16" t="s">
         <v>744</v>
@@ -37131,13 +37128,13 @@
       </c>
       <c r="F157" s="5"/>
       <c r="G157" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H157" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I157" s="5" t="s">
-        <v>2983</v>
+        <v>2982</v>
       </c>
       <c r="J157" s="5" t="s">
         <v>1106</v>
@@ -37166,13 +37163,13 @@
       </c>
       <c r="F158" s="5"/>
       <c r="G158" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H158" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I158" s="5" t="s">
-        <v>2984</v>
+        <v>2983</v>
       </c>
       <c r="J158" s="5" t="s">
         <v>1108</v>
@@ -37201,13 +37198,13 @@
       </c>
       <c r="F159" s="5"/>
       <c r="G159" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H159" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H159" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I159" s="5" t="s">
-        <v>2985</v>
+        <v>2984</v>
       </c>
       <c r="J159" s="5" t="s">
         <v>1097</v>
@@ -37236,10 +37233,10 @@
       </c>
       <c r="F160" s="5"/>
       <c r="G160" s="5" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="H160" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I160" s="5" t="s">
         <v>744</v>
@@ -37271,13 +37268,13 @@
       </c>
       <c r="F161" s="5"/>
       <c r="G161" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H161" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H161" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I161" s="5" t="s">
-        <v>2986</v>
+        <v>2985</v>
       </c>
       <c r="J161" s="5" t="s">
         <v>1098</v>
@@ -37306,13 +37303,13 @@
       </c>
       <c r="F162" s="5"/>
       <c r="G162" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H162" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H162" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I162" s="5" t="s">
-        <v>2986</v>
+        <v>2985</v>
       </c>
       <c r="J162" s="5" t="s">
         <v>1098</v>
@@ -37341,13 +37338,13 @@
       </c>
       <c r="F163" s="5"/>
       <c r="G163" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H163" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H163" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I163" s="5" t="s">
-        <v>2987</v>
+        <v>2986</v>
       </c>
       <c r="J163" s="5" t="s">
         <v>2851</v>
@@ -37376,13 +37373,13 @@
       </c>
       <c r="F164" s="5"/>
       <c r="G164" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H164" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H164" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I164" s="5" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="J164" s="5" t="s">
         <v>1108</v>
@@ -37411,13 +37408,13 @@
       </c>
       <c r="F165" s="5"/>
       <c r="G165" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H165" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I165" s="5" t="s">
-        <v>2985</v>
+        <v>2984</v>
       </c>
       <c r="J165" s="5" t="s">
         <v>1097</v>
@@ -37446,13 +37443,13 @@
       </c>
       <c r="F166" s="5"/>
       <c r="G166" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H166" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I166" s="5" t="s">
-        <v>2982</v>
+        <v>2981</v>
       </c>
       <c r="J166" s="5" t="s">
         <v>1103</v>
@@ -37481,10 +37478,10 @@
       </c>
       <c r="F167" s="5"/>
       <c r="G167" s="5" t="s">
-        <v>2973</v>
+        <v>2972</v>
       </c>
       <c r="H167" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I167" s="5" t="s">
         <v>744</v>
@@ -37516,13 +37513,13 @@
       </c>
       <c r="F168" s="5"/>
       <c r="G168" s="5" t="s">
+        <v>2988</v>
+      </c>
+      <c r="H168" s="5" t="s">
+        <v>2953</v>
+      </c>
+      <c r="I168" s="5" t="s">
         <v>2989</v>
-      </c>
-      <c r="H168" s="5" t="s">
-        <v>2954</v>
-      </c>
-      <c r="I168" s="5" t="s">
-        <v>2990</v>
       </c>
       <c r="J168" s="5" t="s">
         <v>1117</v>
@@ -37551,13 +37548,13 @@
       </c>
       <c r="F169" s="5"/>
       <c r="G169" s="5" t="s">
+        <v>2988</v>
+      </c>
+      <c r="H169" s="5" t="s">
+        <v>2953</v>
+      </c>
+      <c r="I169" s="5" t="s">
         <v>2989</v>
-      </c>
-      <c r="H169" s="5" t="s">
-        <v>2954</v>
-      </c>
-      <c r="I169" s="5" t="s">
-        <v>2990</v>
       </c>
       <c r="J169" s="5" t="s">
         <v>1117</v>
@@ -37586,10 +37583,10 @@
       </c>
       <c r="F170" s="5"/>
       <c r="G170" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H170" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I170" s="5" t="s">
         <v>744</v>
@@ -37621,10 +37618,10 @@
       </c>
       <c r="F171" s="5"/>
       <c r="G171" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H171" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I171" s="5" t="s">
         <v>744</v>
@@ -37652,14 +37649,14 @@
         <v>520</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>2949</v>
+        <v>2948</v>
       </c>
       <c r="F172" s="5"/>
       <c r="G172" s="5" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="H172" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I172" s="5" t="s">
         <v>744</v>
@@ -37691,10 +37688,10 @@
       </c>
       <c r="F173" s="5"/>
       <c r="G173" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H173" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I173" s="5" t="s">
         <v>744</v>
@@ -37726,13 +37723,13 @@
       </c>
       <c r="F174" s="5"/>
       <c r="G174" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H174" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H174" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I174" s="5" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
       <c r="J174" s="5" t="s">
         <v>1113</v>
@@ -37761,10 +37758,10 @@
       </c>
       <c r="F175" s="5"/>
       <c r="G175" s="5" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="H175" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I175" s="5" t="s">
         <v>744</v>
@@ -37796,13 +37793,13 @@
       </c>
       <c r="F176" s="5"/>
       <c r="G176" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H176" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I176" s="5" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="J176" s="5" t="s">
         <v>1126</v>
@@ -37831,10 +37828,10 @@
       </c>
       <c r="F177" s="5"/>
       <c r="G177" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H177" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I177" s="5" t="s">
         <v>749</v>
@@ -37866,13 +37863,13 @@
       </c>
       <c r="F178" s="5"/>
       <c r="G178" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H178" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I178" s="5" t="s">
-        <v>2982</v>
+        <v>2981</v>
       </c>
       <c r="J178" s="5" t="s">
         <v>1103</v>
@@ -37901,13 +37898,13 @@
       </c>
       <c r="F179" s="5"/>
       <c r="G179" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H179" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I179" s="5" t="s">
-        <v>2982</v>
+        <v>2981</v>
       </c>
       <c r="J179" s="5" t="s">
         <v>1103</v>
@@ -37936,13 +37933,13 @@
       </c>
       <c r="F180" s="5"/>
       <c r="G180" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H180" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I180" s="5" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="J180" s="5" t="s">
         <v>1126</v>
@@ -37971,10 +37968,10 @@
       </c>
       <c r="F181" s="5"/>
       <c r="G181" s="5" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="H181" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I181" s="5" t="s">
         <v>744</v>
@@ -38006,10 +38003,10 @@
       </c>
       <c r="F182" s="5"/>
       <c r="G182" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H182" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I182" s="5" t="s">
         <v>744</v>
@@ -38041,13 +38038,13 @@
       </c>
       <c r="F183" s="5"/>
       <c r="G183" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H183" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I183" s="5" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="J183" s="5" t="s">
         <v>1098</v>
@@ -38076,13 +38073,13 @@
       </c>
       <c r="F184" s="5"/>
       <c r="G184" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H184" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I184" s="5" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="J184" s="5" t="s">
         <v>1108</v>
@@ -38111,13 +38108,13 @@
       </c>
       <c r="F185" s="5"/>
       <c r="G185" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H185" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I185" s="5" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
       <c r="J185" s="5" t="s">
         <v>1113</v>
@@ -38146,13 +38143,13 @@
       </c>
       <c r="F186" s="5"/>
       <c r="G186" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H186" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H186" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I186" s="5" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="J186" s="5" t="s">
         <v>1113</v>
@@ -38181,10 +38178,10 @@
       </c>
       <c r="F187" s="5"/>
       <c r="G187" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H187" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H187" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I187" s="5" t="s">
         <v>744</v>
@@ -38216,13 +38213,13 @@
       </c>
       <c r="F188" s="5"/>
       <c r="G188" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H188" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I188" s="5" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="J188" s="5" t="s">
         <v>1108</v>
@@ -38251,13 +38248,13 @@
       </c>
       <c r="F189" s="5"/>
       <c r="G189" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H189" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H189" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I189" s="5" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="J189" s="5" t="s">
         <v>1126</v>
@@ -38286,10 +38283,10 @@
       </c>
       <c r="F190" s="5"/>
       <c r="G190" s="5" t="s">
+        <v>2988</v>
+      </c>
+      <c r="H190" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H190" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I190" s="5" t="s">
         <v>744</v>
@@ -38321,13 +38318,13 @@
       </c>
       <c r="F191" s="5"/>
       <c r="G191" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H191" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I191" s="5" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="J191" s="5" t="s">
         <v>1126</v>
@@ -38356,10 +38353,10 @@
       </c>
       <c r="F192" s="5"/>
       <c r="G192" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H192" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I192" s="5" t="s">
         <v>744</v>
@@ -38391,13 +38388,13 @@
       </c>
       <c r="F193" s="5"/>
       <c r="G193" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H193" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I193" s="5" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
       <c r="J193" s="5" t="s">
         <v>1098</v>
@@ -38426,13 +38423,13 @@
       </c>
       <c r="F194" s="5"/>
       <c r="G194" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H194" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I194" s="5" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="J194" s="5" t="s">
         <v>1097</v>
@@ -38461,13 +38458,13 @@
       </c>
       <c r="F195" s="5"/>
       <c r="G195" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H195" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I195" s="5" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
       <c r="J195" s="5" t="s">
         <v>1113</v>
@@ -38496,13 +38493,13 @@
       </c>
       <c r="F196" s="5"/>
       <c r="G196" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H196" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I196" s="5" t="s">
-        <v>3000</v>
+        <v>2999</v>
       </c>
       <c r="J196" s="5" t="s">
         <v>1113</v>
@@ -38531,10 +38528,10 @@
       </c>
       <c r="F197" s="5"/>
       <c r="G197" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H197" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I197" s="5" t="s">
         <v>744</v>
@@ -38566,13 +38563,13 @@
       </c>
       <c r="F198" s="5"/>
       <c r="G198" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H198" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I198" s="5" t="s">
-        <v>2987</v>
+        <v>2986</v>
       </c>
       <c r="J198" s="5" t="s">
         <v>2851</v>
@@ -38601,13 +38598,13 @@
       </c>
       <c r="F199" s="5"/>
       <c r="G199" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H199" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H199" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I199" s="5" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="J199" s="5" t="s">
         <v>1108</v>
@@ -38636,13 +38633,13 @@
       </c>
       <c r="F200" s="5"/>
       <c r="G200" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H200" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I200" s="5" t="s">
-        <v>2981</v>
+        <v>2980</v>
       </c>
       <c r="J200" s="5" t="s">
         <v>1124</v>
@@ -38671,10 +38668,10 @@
       </c>
       <c r="F201" s="5"/>
       <c r="G201" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H201" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I201" s="5" t="s">
         <v>744</v>
@@ -38706,13 +38703,13 @@
       </c>
       <c r="F202" s="5"/>
       <c r="G202" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H202" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H202" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I202" s="5" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="J202" s="5" t="s">
         <v>1126</v>
@@ -38741,13 +38738,13 @@
       </c>
       <c r="F203" s="5"/>
       <c r="G203" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H203" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I203" s="5" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="J203" s="5" t="s">
         <v>1108</v>
@@ -38776,10 +38773,10 @@
       </c>
       <c r="F204" s="5"/>
       <c r="G204" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H204" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H204" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I204" s="5" t="s">
         <v>744</v>
@@ -38811,13 +38808,13 @@
       </c>
       <c r="F205" s="5"/>
       <c r="G205" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H205" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I205" s="5" t="s">
-        <v>3001</v>
+        <v>3000</v>
       </c>
       <c r="J205" s="5" t="s">
         <v>1126</v>
@@ -38846,10 +38843,10 @@
       </c>
       <c r="F206" s="5"/>
       <c r="G206" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H206" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H206" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I206" s="5" t="s">
         <v>744</v>
@@ -38881,13 +38878,13 @@
       </c>
       <c r="F207" s="5"/>
       <c r="G207" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H207" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I207" s="5" t="s">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="J207" s="5" t="s">
         <v>1126</v>
@@ -38916,13 +38913,13 @@
       </c>
       <c r="F208" s="5"/>
       <c r="G208" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H208" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I208" s="5" t="s">
-        <v>2986</v>
+        <v>2985</v>
       </c>
       <c r="J208" s="5" t="s">
         <v>1098</v>
@@ -38951,13 +38948,13 @@
       </c>
       <c r="F209" s="5"/>
       <c r="G209" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H209" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I209" s="5" t="s">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="J209" s="5" t="s">
         <v>1106</v>
@@ -38986,10 +38983,10 @@
       </c>
       <c r="F210" s="5"/>
       <c r="G210" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H210" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H210" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I210" s="5" t="s">
         <v>744</v>
@@ -39021,13 +39018,13 @@
       </c>
       <c r="F211" s="5"/>
       <c r="G211" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H211" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I211" s="5" t="s">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="J211" s="5" t="s">
         <v>1106</v>
@@ -39056,13 +39053,13 @@
       </c>
       <c r="F212" s="5"/>
       <c r="G212" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H212" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I212" s="5" t="s">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="J212" s="5" t="s">
         <v>1124</v>
@@ -39091,13 +39088,13 @@
       </c>
       <c r="F213" s="5"/>
       <c r="G213" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H213" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I213" s="5" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
       <c r="J213" s="5" t="s">
         <v>1098</v>
@@ -39126,10 +39123,10 @@
       </c>
       <c r="F214" s="5"/>
       <c r="G214" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H214" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I214" s="5" t="s">
         <v>744</v>
@@ -39161,10 +39158,10 @@
       </c>
       <c r="F215" s="5"/>
       <c r="G215" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H215" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H215" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I215" s="5" t="s">
         <v>744</v>
@@ -39196,13 +39193,13 @@
       </c>
       <c r="F216" s="5"/>
       <c r="G216" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H216" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I216" s="5" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="J216" s="5" t="s">
         <v>1126</v>
@@ -39231,13 +39228,13 @@
       </c>
       <c r="F217" s="5"/>
       <c r="G217" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H217" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I217" s="5" t="s">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="J217" s="5" t="s">
         <v>1106</v>
@@ -39266,13 +39263,13 @@
       </c>
       <c r="F218" s="5"/>
       <c r="G218" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H218" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I218" s="5" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="J218" s="5" t="s">
         <v>1098</v>
@@ -39301,13 +39298,13 @@
       </c>
       <c r="F219" s="5"/>
       <c r="G219" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H219" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I219" s="5" t="s">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="J219" s="5" t="s">
         <v>1098</v>
@@ -39336,13 +39333,13 @@
       </c>
       <c r="F220" s="5"/>
       <c r="G220" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H220" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I220" s="5" t="s">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="J220" s="5" t="s">
         <v>1106</v>
@@ -39371,13 +39368,13 @@
       </c>
       <c r="F221" s="5"/>
       <c r="G221" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H221" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I221" s="5" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="J221" s="5" t="s">
         <v>1113</v>
@@ -39406,13 +39403,13 @@
       </c>
       <c r="F222" s="5"/>
       <c r="G222" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H222" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I222" s="5" t="s">
-        <v>3001</v>
+        <v>3000</v>
       </c>
       <c r="J222" s="5" t="s">
         <v>1126</v>
@@ -39441,10 +39438,10 @@
       </c>
       <c r="F223" s="5"/>
       <c r="G223" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H223" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I223" s="5" t="s">
         <v>744</v>
@@ -39476,13 +39473,13 @@
       </c>
       <c r="F224" s="5"/>
       <c r="G224" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H224" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I224" s="5" t="s">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="J224" s="5" t="s">
         <v>1098</v>
@@ -39511,13 +39508,13 @@
       </c>
       <c r="F225" s="5"/>
       <c r="G225" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H225" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I225" s="5" t="s">
-        <v>3000</v>
+        <v>2999</v>
       </c>
       <c r="J225" s="5" t="s">
         <v>1113</v>
@@ -39546,13 +39543,13 @@
       </c>
       <c r="F226" s="5"/>
       <c r="G226" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H226" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I226" s="5" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="J226" s="5" t="s">
         <v>1097</v>
@@ -39581,13 +39578,13 @@
       </c>
       <c r="F227" s="5"/>
       <c r="G227" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H227" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I227" s="5" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="J227" s="5" t="s">
         <v>1124</v>
@@ -39616,13 +39613,13 @@
       </c>
       <c r="F228" s="5"/>
       <c r="G228" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H228" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I228" s="5" t="s">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="J228" s="5" t="s">
         <v>1098</v>
@@ -39651,13 +39648,13 @@
       </c>
       <c r="F229" s="5"/>
       <c r="G229" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H229" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I229" s="5" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="J229" s="5" t="s">
         <v>1113</v>
@@ -39686,13 +39683,13 @@
       </c>
       <c r="F230" s="5"/>
       <c r="G230" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H230" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I230" s="5" t="s">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="J230" s="5" t="s">
         <v>1098</v>
@@ -39721,13 +39718,13 @@
       </c>
       <c r="F231" s="5"/>
       <c r="G231" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H231" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I231" s="5" t="s">
-        <v>2985</v>
+        <v>2984</v>
       </c>
       <c r="J231" s="5" t="s">
         <v>1124</v>
@@ -39756,13 +39753,13 @@
       </c>
       <c r="F232" s="5"/>
       <c r="G232" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H232" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I232" s="5" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="J232" s="5" t="s">
         <v>1124</v>
@@ -39791,13 +39788,13 @@
       </c>
       <c r="F233" s="5"/>
       <c r="G233" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H233" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I233" s="5" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
       <c r="J233" s="5" t="s">
         <v>1098</v>
@@ -39826,13 +39823,13 @@
       </c>
       <c r="F234" s="5"/>
       <c r="G234" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H234" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I234" s="5" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="J234" s="5" t="s">
         <v>1113</v>
@@ -39861,10 +39858,10 @@
       </c>
       <c r="F235" s="5"/>
       <c r="G235" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H235" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I235" s="5" t="s">
         <v>744</v>
@@ -39896,10 +39893,10 @@
       </c>
       <c r="F236" s="5"/>
       <c r="G236" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H236" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I236" s="5" t="s">
         <v>744</v>
@@ -39931,13 +39928,13 @@
       </c>
       <c r="F237" s="5"/>
       <c r="G237" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H237" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I237" s="5" t="s">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="J237" s="5" t="s">
         <v>1098</v>
@@ -39966,13 +39963,13 @@
       </c>
       <c r="F238" s="5"/>
       <c r="G238" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H238" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H238" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I238" s="5" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="J238" s="5" t="s">
         <v>1108</v>
@@ -40001,13 +39998,13 @@
       </c>
       <c r="F239" s="5"/>
       <c r="G239" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H239" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I239" s="5" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="J239" s="5" t="s">
         <v>1124</v>
@@ -40036,13 +40033,13 @@
       </c>
       <c r="F240" s="5"/>
       <c r="G240" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H240" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I240" s="5" t="s">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="J240" s="5" t="s">
         <v>1126</v>
@@ -40071,10 +40068,10 @@
       </c>
       <c r="F241" s="5"/>
       <c r="G241" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H241" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H241" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I241" s="5" t="s">
         <v>744</v>
@@ -40106,10 +40103,10 @@
       </c>
       <c r="F242" s="5"/>
       <c r="G242" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H242" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H242" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I242" s="5" t="s">
         <v>744</v>
@@ -40141,10 +40138,10 @@
       </c>
       <c r="F243" s="5"/>
       <c r="G243" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H243" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H243" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I243" s="5" t="s">
         <v>744</v>
@@ -40176,10 +40173,10 @@
       </c>
       <c r="F244" s="5"/>
       <c r="G244" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H244" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H244" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I244" s="5" t="s">
         <v>744</v>
@@ -40211,13 +40208,13 @@
       </c>
       <c r="F245" s="5"/>
       <c r="G245" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H245" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I245" s="5" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="J245" s="5" t="s">
         <v>1124</v>
@@ -40246,13 +40243,13 @@
       </c>
       <c r="F246" s="5"/>
       <c r="G246" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H246" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I246" s="5" t="s">
-        <v>2984</v>
+        <v>2983</v>
       </c>
       <c r="J246" s="5" t="s">
         <v>1108</v>
@@ -40281,13 +40278,13 @@
       </c>
       <c r="F247" s="5"/>
       <c r="G247" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H247" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I247" s="5" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="J247" s="5" t="s">
         <v>1143</v>
@@ -40316,13 +40313,13 @@
       </c>
       <c r="F248" s="5"/>
       <c r="G248" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H248" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I248" s="5" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="J248" s="5" t="s">
         <v>1124</v>
@@ -40351,13 +40348,13 @@
       </c>
       <c r="F249" s="5"/>
       <c r="G249" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H249" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I249" s="5" t="s">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="J249" s="5" t="s">
         <v>1146</v>
@@ -40386,13 +40383,13 @@
       </c>
       <c r="F250" s="5"/>
       <c r="G250" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H250" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I250" s="5" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="J250" s="5" t="s">
         <v>1148</v>
@@ -40421,10 +40418,10 @@
       </c>
       <c r="F251" s="5"/>
       <c r="G251" s="5" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="H251" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I251" s="5" t="s">
         <v>744</v>
@@ -40442,11 +40439,11 @@
     </row>
     <row r="252" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="5" t="s">
-        <v>3027</v>
+        <v>3026</v>
       </c>
       <c r="B252" s="5"/>
       <c r="C252" s="5" t="s">
-        <v>3028</v>
+        <v>3027</v>
       </c>
       <c r="D252" s="5" t="s">
         <v>520</v>
@@ -40456,10 +40453,10 @@
       </c>
       <c r="F252" s="5"/>
       <c r="G252" s="5" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="H252" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I252" s="5" t="s">
         <v>744</v>
@@ -40491,10 +40488,10 @@
       </c>
       <c r="F253" s="5"/>
       <c r="G253" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H253" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H253" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I253" s="5" t="s">
         <v>744</v>
@@ -40526,13 +40523,13 @@
       </c>
       <c r="F254" s="5"/>
       <c r="G254" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H254" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I254" s="5" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="J254" s="5" t="s">
         <v>1098</v>
@@ -40561,13 +40558,13 @@
       </c>
       <c r="F255" s="5"/>
       <c r="G255" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H255" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I255" s="5" t="s">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="J255" s="5" t="s">
         <v>1098</v>
@@ -40596,10 +40593,10 @@
       </c>
       <c r="F256" s="5"/>
       <c r="G256" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H256" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I256" s="5" t="s">
         <v>749</v>
@@ -40631,13 +40628,13 @@
       </c>
       <c r="F257" s="5"/>
       <c r="G257" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H257" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I257" s="5" t="s">
-        <v>3013</v>
+        <v>3012</v>
       </c>
       <c r="J257" s="5" t="s">
         <v>1098</v>
@@ -40666,13 +40663,13 @@
       </c>
       <c r="F258" s="5"/>
       <c r="G258" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H258" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I258" s="5" t="s">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="J258" s="5" t="s">
         <v>1098</v>
@@ -40701,13 +40698,13 @@
       </c>
       <c r="F259" s="5"/>
       <c r="G259" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H259" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I259" s="5" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="J259" s="5" t="s">
         <v>1143</v>
@@ -40736,13 +40733,13 @@
       </c>
       <c r="F260" s="5"/>
       <c r="G260" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H260" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I260" s="5" t="s">
-        <v>3013</v>
+        <v>3012</v>
       </c>
       <c r="J260" s="5" t="s">
         <v>1098</v>
@@ -40771,13 +40768,13 @@
       </c>
       <c r="F261" s="5"/>
       <c r="G261" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H261" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I261" s="5" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="J261" s="5" t="s">
         <v>1143</v>
@@ -40806,10 +40803,10 @@
       </c>
       <c r="F262" s="5"/>
       <c r="G262" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H262" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H262" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I262" s="5" t="s">
         <v>744</v>
@@ -40841,13 +40838,13 @@
       </c>
       <c r="F263" s="5"/>
       <c r="G263" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H263" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I263" s="5" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="J263" s="5" t="s">
         <v>1148</v>
@@ -40866,7 +40863,7 @@
       </c>
       <c r="B264" s="5"/>
       <c r="C264" s="5" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="D264" s="5" t="s">
         <v>520</v>
@@ -40876,10 +40873,10 @@
       </c>
       <c r="F264" s="5"/>
       <c r="G264" s="5" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="H264" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I264" s="5" t="s">
         <v>744</v>
@@ -40911,10 +40908,10 @@
       </c>
       <c r="F265" s="5"/>
       <c r="G265" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H265" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H265" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I265" s="5" t="s">
         <v>744</v>
@@ -40946,10 +40943,10 @@
       </c>
       <c r="F266" s="5"/>
       <c r="G266" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H266" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H266" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I266" s="5" t="s">
         <v>744</v>
@@ -40981,13 +40978,13 @@
       </c>
       <c r="F267" s="5"/>
       <c r="G267" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H267" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I267" s="5" t="s">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="J267" s="5" t="s">
         <v>1146</v>
@@ -41016,13 +41013,13 @@
       </c>
       <c r="F268" s="5"/>
       <c r="G268" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H268" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I268" s="5" t="s">
-        <v>3013</v>
+        <v>3012</v>
       </c>
       <c r="J268" s="5" t="s">
         <v>1098</v>
@@ -41051,10 +41048,10 @@
       </c>
       <c r="F269" s="5"/>
       <c r="G269" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H269" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H269" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I269" s="5" t="s">
         <v>744</v>
@@ -41086,10 +41083,10 @@
       </c>
       <c r="F270" s="5"/>
       <c r="G270" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H270" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H270" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I270" s="5" t="s">
         <v>744</v>
@@ -41121,10 +41118,10 @@
       </c>
       <c r="F271" s="5"/>
       <c r="G271" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H271" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H271" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I271" s="5" t="s">
         <v>744</v>
@@ -41156,13 +41153,13 @@
       </c>
       <c r="F272" s="5"/>
       <c r="G272" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H272" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I272" s="5" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="J272" s="5" t="s">
         <v>1113</v>
@@ -41191,10 +41188,10 @@
       </c>
       <c r="F273" s="5"/>
       <c r="G273" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H273" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H273" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I273" s="5" t="s">
         <v>744</v>
@@ -41226,10 +41223,10 @@
       </c>
       <c r="F274" s="5"/>
       <c r="G274" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H274" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H274" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I274" s="5" t="s">
         <v>744</v>
@@ -41261,13 +41258,13 @@
       </c>
       <c r="F275" s="5"/>
       <c r="G275" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H275" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I275" s="5" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="J275" s="5" t="s">
         <v>1148</v>
@@ -41296,13 +41293,13 @@
       </c>
       <c r="F276" s="5"/>
       <c r="G276" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H276" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I276" s="5" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="J276" s="5" t="s">
         <v>1148</v>
@@ -41331,10 +41328,10 @@
       </c>
       <c r="F277" s="5"/>
       <c r="G277" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H277" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H277" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I277" s="5" t="s">
         <v>744</v>
@@ -41366,13 +41363,13 @@
       </c>
       <c r="F278" s="5"/>
       <c r="G278" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H278" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I278" s="5" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="J278" s="5" t="s">
         <v>1113</v>
@@ -41401,10 +41398,10 @@
       </c>
       <c r="F279" s="5"/>
       <c r="G279" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H279" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H279" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I279" s="5" t="s">
         <v>744</v>
@@ -41436,10 +41433,10 @@
       </c>
       <c r="F280" s="5"/>
       <c r="G280" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H280" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H280" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I280" s="5" t="s">
         <v>744</v>
@@ -41471,10 +41468,10 @@
       </c>
       <c r="F281" s="5"/>
       <c r="G281" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H281" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H281" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I281" s="5" t="s">
         <v>744</v>
@@ -41506,10 +41503,10 @@
       </c>
       <c r="F282" s="5"/>
       <c r="G282" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H282" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H282" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I282" s="5" t="s">
         <v>744</v>
@@ -41541,10 +41538,10 @@
       </c>
       <c r="F283" s="5"/>
       <c r="G283" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H283" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H283" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I283" s="5" t="s">
         <v>744</v>
@@ -41576,10 +41573,10 @@
       </c>
       <c r="F284" s="5"/>
       <c r="G284" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H284" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H284" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I284" s="5" t="s">
         <v>744</v>
@@ -41611,13 +41608,13 @@
       </c>
       <c r="F285" s="5"/>
       <c r="G285" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H285" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I285" s="5" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="J285" s="5" t="s">
         <v>1148</v>
@@ -41646,13 +41643,13 @@
       </c>
       <c r="F286" s="5"/>
       <c r="G286" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H286" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I286" s="5" t="s">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="J286" s="5" t="s">
         <v>1098</v>
@@ -41681,10 +41678,10 @@
       </c>
       <c r="F287" s="5"/>
       <c r="G287" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H287" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H287" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I287" s="5" t="s">
         <v>744</v>
@@ -41716,13 +41713,13 @@
       </c>
       <c r="F288" s="5"/>
       <c r="G288" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H288" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I288" s="5" t="s">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="J288" s="5" t="s">
         <v>1146</v>
@@ -41751,10 +41748,10 @@
       </c>
       <c r="F289" s="5"/>
       <c r="G289" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H289" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H289" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I289" s="5" t="s">
         <v>744</v>
@@ -41786,10 +41783,10 @@
       </c>
       <c r="F290" s="5"/>
       <c r="G290" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H290" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H290" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I290" s="5" t="s">
         <v>744</v>
@@ -41821,13 +41818,13 @@
       </c>
       <c r="F291" s="5"/>
       <c r="G291" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H291" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I291" s="5" t="s">
-        <v>2979</v>
+        <v>2978</v>
       </c>
       <c r="J291" s="5" t="s">
         <v>1097</v>
@@ -41856,10 +41853,10 @@
       </c>
       <c r="F292" s="5"/>
       <c r="G292" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H292" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H292" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I292" s="5" t="s">
         <v>744</v>
@@ -41891,10 +41888,10 @@
       </c>
       <c r="F293" s="5"/>
       <c r="G293" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H293" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H293" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I293" s="5" t="s">
         <v>744</v>
@@ -41926,10 +41923,10 @@
       </c>
       <c r="F294" s="5"/>
       <c r="G294" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H294" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H294" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I294" s="5" t="s">
         <v>744</v>
@@ -41961,10 +41958,10 @@
       </c>
       <c r="F295" s="5"/>
       <c r="G295" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H295" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H295" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I295" s="5" t="s">
         <v>744</v>
@@ -41996,10 +41993,10 @@
       </c>
       <c r="F296" s="5"/>
       <c r="G296" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H296" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H296" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I296" s="5" t="s">
         <v>744</v>
@@ -42031,10 +42028,10 @@
       </c>
       <c r="F297" s="5"/>
       <c r="G297" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H297" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H297" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I297" s="5" t="s">
         <v>744</v>
@@ -42066,10 +42063,10 @@
       </c>
       <c r="F298" s="5"/>
       <c r="G298" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H298" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H298" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I298" s="5" t="s">
         <v>744</v>
@@ -42101,10 +42098,10 @@
       </c>
       <c r="F299" s="5"/>
       <c r="G299" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H299" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H299" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I299" s="5" t="s">
         <v>744</v>
@@ -42136,10 +42133,10 @@
       </c>
       <c r="F300" s="5"/>
       <c r="G300" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H300" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H300" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I300" s="5" t="s">
         <v>744</v>
@@ -42171,10 +42168,10 @@
       </c>
       <c r="F301" s="5"/>
       <c r="G301" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H301" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H301" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I301" s="5" t="s">
         <v>744</v>
@@ -42206,10 +42203,10 @@
       </c>
       <c r="F302" s="5"/>
       <c r="G302" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H302" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H302" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I302" s="5" t="s">
         <v>744</v>
@@ -42241,10 +42238,10 @@
       </c>
       <c r="F303" s="5"/>
       <c r="G303" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H303" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H303" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I303" s="5" t="s">
         <v>744</v>
@@ -42276,10 +42273,10 @@
       </c>
       <c r="F304" s="5"/>
       <c r="G304" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H304" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H304" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I304" s="5" t="s">
         <v>744</v>
@@ -42311,10 +42308,10 @@
       </c>
       <c r="F305" s="5"/>
       <c r="G305" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H305" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H305" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I305" s="5" t="s">
         <v>744</v>
@@ -42346,10 +42343,10 @@
       </c>
       <c r="F306" s="5"/>
       <c r="G306" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H306" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H306" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I306" s="5" t="s">
         <v>744</v>
@@ -42381,10 +42378,10 @@
       </c>
       <c r="F307" s="5"/>
       <c r="G307" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H307" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H307" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I307" s="5" t="s">
         <v>744</v>
@@ -42416,13 +42413,13 @@
       </c>
       <c r="F308" s="5"/>
       <c r="G308" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H308" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I308" s="5" t="s">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="J308" s="5" t="s">
         <v>1126</v>
@@ -42451,13 +42448,13 @@
       </c>
       <c r="F309" s="5"/>
       <c r="G309" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H309" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I309" s="5" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="J309" s="5" t="s">
         <v>1124</v>
@@ -42486,13 +42483,13 @@
       </c>
       <c r="F310" s="5"/>
       <c r="G310" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H310" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I310" s="5" t="s">
-        <v>2985</v>
+        <v>2984</v>
       </c>
       <c r="J310" s="5" t="s">
         <v>1124</v>
@@ -42521,13 +42518,13 @@
       </c>
       <c r="F311" s="5"/>
       <c r="G311" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H311" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I311" s="5" t="s">
-        <v>3015</v>
+        <v>3014</v>
       </c>
       <c r="J311" s="5" t="s">
         <v>1124</v>
@@ -42556,10 +42553,10 @@
       </c>
       <c r="F312" s="5"/>
       <c r="G312" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H312" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I312" s="5" t="s">
         <v>744</v>
@@ -42591,13 +42588,13 @@
       </c>
       <c r="F313" s="5"/>
       <c r="G313" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H313" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I313" s="5" t="s">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="J313" s="5" t="s">
         <v>1124</v>
@@ -42626,13 +42623,13 @@
       </c>
       <c r="F314" s="5"/>
       <c r="G314" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H314" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I314" s="5" t="s">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="J314" s="5" t="s">
         <v>1124</v>
@@ -42661,10 +42658,10 @@
       </c>
       <c r="F315" s="5"/>
       <c r="G315" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H315" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H315" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I315" s="5" t="s">
         <v>744</v>
@@ -42696,13 +42693,13 @@
       </c>
       <c r="F316" s="5"/>
       <c r="G316" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H316" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I316" s="5" t="s">
-        <v>2981</v>
+        <v>2980</v>
       </c>
       <c r="J316" s="5" t="s">
         <v>1124</v>
@@ -42731,13 +42728,13 @@
       </c>
       <c r="F317" s="5"/>
       <c r="G317" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H317" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I317" s="5" t="s">
-        <v>2981</v>
+        <v>2980</v>
       </c>
       <c r="J317" s="5" t="s">
         <v>1124</v>
@@ -42766,13 +42763,13 @@
       </c>
       <c r="F318" s="5"/>
       <c r="G318" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H318" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I318" s="5" t="s">
-        <v>3015</v>
+        <v>3014</v>
       </c>
       <c r="J318" s="5" t="s">
         <v>1124</v>
@@ -42801,10 +42798,10 @@
       </c>
       <c r="F319" s="5"/>
       <c r="G319" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H319" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I319" s="5" t="s">
         <v>744</v>
@@ -42836,10 +42833,10 @@
       </c>
       <c r="F320" s="5"/>
       <c r="G320" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H320" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I320" s="5" t="s">
         <v>744</v>
@@ -42871,10 +42868,10 @@
       </c>
       <c r="F321" s="5"/>
       <c r="G321" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H321" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I321" s="5" t="s">
         <v>744</v>
@@ -42906,10 +42903,10 @@
       </c>
       <c r="F322" s="5"/>
       <c r="G322" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H322" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I322" s="5" t="s">
         <v>744</v>
@@ -42941,10 +42938,10 @@
       </c>
       <c r="F323" s="5"/>
       <c r="G323" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H323" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H323" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I323" s="5" t="s">
         <v>744</v>
@@ -42976,10 +42973,10 @@
       </c>
       <c r="F324" s="5"/>
       <c r="G324" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H324" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I324" s="5" t="s">
         <v>744</v>
@@ -43011,13 +43008,13 @@
       </c>
       <c r="F325" s="5"/>
       <c r="G325" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H325" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H325" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I325" s="5" t="s">
-        <v>2983</v>
+        <v>2982</v>
       </c>
       <c r="J325" s="5" t="s">
         <v>1106</v>
@@ -43046,13 +43043,13 @@
       </c>
       <c r="F326" s="5"/>
       <c r="G326" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H326" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I326" s="5" t="s">
-        <v>3016</v>
+        <v>3015</v>
       </c>
       <c r="J326" s="5" t="s">
         <v>1106</v>
@@ -43081,13 +43078,13 @@
       </c>
       <c r="F327" s="5"/>
       <c r="G327" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H327" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H327" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I327" s="5" t="s">
-        <v>3017</v>
+        <v>3016</v>
       </c>
       <c r="J327" s="5" t="s">
         <v>1170</v>
@@ -43116,13 +43113,13 @@
       </c>
       <c r="F328" s="5"/>
       <c r="G328" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H328" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I328" s="5" t="s">
-        <v>3017</v>
+        <v>3016</v>
       </c>
       <c r="J328" s="5" t="s">
         <v>1170</v>
@@ -43151,13 +43148,13 @@
       </c>
       <c r="F329" s="5"/>
       <c r="G329" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H329" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H329" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I329" s="5" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="J329" s="5" t="s">
         <v>2795</v>
@@ -43182,14 +43179,14 @@
         <v>520</v>
       </c>
       <c r="E330" s="5" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="F330" s="5"/>
       <c r="G330" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H330" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I330" s="5" t="s">
         <v>744</v>
@@ -43217,14 +43214,14 @@
         <v>520</v>
       </c>
       <c r="E331" s="5" t="s">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="F331" s="5"/>
       <c r="G331" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H331" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I331" s="5" t="s">
         <v>744</v>
@@ -43256,10 +43253,10 @@
       </c>
       <c r="F332" s="5"/>
       <c r="G332" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H332" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I332" s="5" t="s">
         <v>744</v>
@@ -43291,13 +43288,13 @@
       </c>
       <c r="F333" s="5"/>
       <c r="G333" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H333" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I333" s="5" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="J333" s="5" t="s">
         <v>2795</v>
@@ -43326,13 +43323,13 @@
       </c>
       <c r="F334" s="5"/>
       <c r="G334" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H334" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I334" s="5" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="J334" s="5" t="s">
         <v>2795</v>
@@ -43361,13 +43358,13 @@
       </c>
       <c r="F335" s="5"/>
       <c r="G335" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H335" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I335" s="5" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="J335" s="5" t="s">
         <v>2795</v>
@@ -43396,13 +43393,13 @@
       </c>
       <c r="F336" s="5"/>
       <c r="G336" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H336" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H336" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I336" s="5" t="s">
-        <v>3016</v>
+        <v>3015</v>
       </c>
       <c r="J336" s="5" t="s">
         <v>1106</v>
@@ -43431,10 +43428,10 @@
       </c>
       <c r="F337" s="5"/>
       <c r="G337" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H337" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I337" s="5" t="s">
         <v>744</v>
@@ -43466,10 +43463,10 @@
       </c>
       <c r="F338" s="5"/>
       <c r="G338" s="5" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="H338" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I338" s="5" t="s">
         <v>744</v>
@@ -43501,10 +43498,10 @@
       </c>
       <c r="F339" s="5"/>
       <c r="G339" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H339" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I339" s="5" t="s">
         <v>744</v>
@@ -43526,7 +43523,7 @@
       </c>
       <c r="B340" s="5"/>
       <c r="C340" s="5" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="D340" s="5" t="s">
         <v>520</v>
@@ -43536,10 +43533,10 @@
       </c>
       <c r="F340" s="5"/>
       <c r="G340" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H340" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I340" s="5" t="s">
         <v>744</v>
@@ -43561,7 +43558,7 @@
       </c>
       <c r="B341" s="5"/>
       <c r="C341" s="5" t="s">
-        <v>2933</v>
+        <v>2932</v>
       </c>
       <c r="D341" s="5" t="s">
         <v>520</v>
@@ -43571,10 +43568,10 @@
       </c>
       <c r="F341" s="5"/>
       <c r="G341" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H341" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I341" s="5" t="s">
         <v>744</v>
@@ -43606,10 +43603,10 @@
       </c>
       <c r="F342" s="5"/>
       <c r="G342" s="5" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="H342" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I342" s="5" t="s">
         <v>744</v>
@@ -43631,7 +43628,7 @@
       </c>
       <c r="B343" s="5"/>
       <c r="C343" s="5" t="s">
-        <v>2934</v>
+        <v>2933</v>
       </c>
       <c r="D343" s="5" t="s">
         <v>520</v>
@@ -43641,10 +43638,10 @@
       </c>
       <c r="F343" s="5"/>
       <c r="G343" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H343" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I343" s="5" t="s">
         <v>744</v>
@@ -43666,7 +43663,7 @@
       </c>
       <c r="B344" s="5"/>
       <c r="C344" s="5" t="s">
-        <v>2935</v>
+        <v>2934</v>
       </c>
       <c r="D344" s="5" t="s">
         <v>520</v>
@@ -43676,10 +43673,10 @@
       </c>
       <c r="F344" s="5"/>
       <c r="G344" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H344" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I344" s="5" t="s">
         <v>744</v>
@@ -43701,7 +43698,7 @@
       </c>
       <c r="B345" s="5"/>
       <c r="C345" s="5" t="s">
-        <v>2936</v>
+        <v>2935</v>
       </c>
       <c r="D345" s="5" t="s">
         <v>520</v>
@@ -43711,10 +43708,10 @@
       </c>
       <c r="F345" s="5"/>
       <c r="G345" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H345" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I345" s="5" t="s">
         <v>744</v>
@@ -43736,7 +43733,7 @@
       </c>
       <c r="B346" s="5"/>
       <c r="C346" s="5" t="s">
-        <v>2937</v>
+        <v>2936</v>
       </c>
       <c r="D346" s="5" t="s">
         <v>520</v>
@@ -43746,10 +43743,10 @@
       </c>
       <c r="F346" s="5"/>
       <c r="G346" s="5" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="H346" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I346" s="5" t="s">
         <v>744</v>
@@ -43771,7 +43768,7 @@
       </c>
       <c r="B347" s="5"/>
       <c r="C347" s="5" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="D347" s="5" t="s">
         <v>520</v>
@@ -43781,10 +43778,10 @@
       </c>
       <c r="F347" s="5"/>
       <c r="G347" s="5" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="H347" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I347" s="5" t="s">
         <v>744</v>
@@ -43806,7 +43803,7 @@
       </c>
       <c r="B348" s="5"/>
       <c r="C348" s="5" t="s">
-        <v>2939</v>
+        <v>2938</v>
       </c>
       <c r="D348" s="5" t="s">
         <v>520</v>
@@ -43816,10 +43813,10 @@
       </c>
       <c r="F348" s="5"/>
       <c r="G348" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H348" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I348" s="5" t="s">
         <v>744</v>
@@ -43841,7 +43838,7 @@
       </c>
       <c r="B349" s="5"/>
       <c r="C349" s="5" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
       <c r="D349" s="5" t="s">
         <v>520</v>
@@ -43851,10 +43848,10 @@
       </c>
       <c r="F349" s="5"/>
       <c r="G349" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H349" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I349" s="5" t="s">
         <v>744</v>
@@ -43876,7 +43873,7 @@
       </c>
       <c r="B350" s="5"/>
       <c r="C350" s="5" t="s">
-        <v>2941</v>
+        <v>2940</v>
       </c>
       <c r="D350" s="5" t="s">
         <v>520</v>
@@ -43886,10 +43883,10 @@
       </c>
       <c r="F350" s="5"/>
       <c r="G350" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H350" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I350" s="5" t="s">
         <v>744</v>
@@ -43911,7 +43908,7 @@
       </c>
       <c r="B351" s="5"/>
       <c r="C351" s="5" t="s">
-        <v>2942</v>
+        <v>2941</v>
       </c>
       <c r="D351" s="5" t="s">
         <v>520</v>
@@ -43921,10 +43918,10 @@
       </c>
       <c r="F351" s="5"/>
       <c r="G351" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H351" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I351" s="5" t="s">
         <v>744</v>
@@ -44957,7 +44954,7 @@
         <v>3269</v>
       </c>
       <c r="N386" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P386" s="2">
         <f>_xlfn.XLOOKUP(C386,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -44993,7 +44990,7 @@
         <v>3943</v>
       </c>
       <c r="N387" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P387" s="2">
         <f>_xlfn.XLOOKUP(C387,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -45029,7 +45026,7 @@
         <v>3943</v>
       </c>
       <c r="N388" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P388" s="2">
         <f>_xlfn.XLOOKUP(C388,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -45065,7 +45062,7 @@
         <v>3943</v>
       </c>
       <c r="N389" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P389" s="2">
         <f>_xlfn.XLOOKUP(C389,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -45101,7 +45098,7 @@
         <v>3943</v>
       </c>
       <c r="N390" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P390" s="2">
         <f>_xlfn.XLOOKUP(C390,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -45137,7 +45134,7 @@
         <v>3607</v>
       </c>
       <c r="N391" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P391" s="2" t="s">
         <v>744</v>
@@ -45172,7 +45169,7 @@
         <v>3607</v>
       </c>
       <c r="N392" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P392" s="2" t="s">
         <v>744</v>
@@ -45207,7 +45204,7 @@
         <v>3607</v>
       </c>
       <c r="N393" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P393" s="2" t="s">
         <v>744</v>
@@ -45242,7 +45239,7 @@
         <v>3607</v>
       </c>
       <c r="N394" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P394" s="2" t="s">
         <v>744</v>
@@ -45277,7 +45274,7 @@
         <v>3272</v>
       </c>
       <c r="N395" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P395" s="2" t="s">
         <v>744</v>
@@ -45312,7 +45309,7 @@
         <v>3272</v>
       </c>
       <c r="N396" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P396" s="2" t="s">
         <v>744</v>
@@ -45347,7 +45344,7 @@
         <v>3262</v>
       </c>
       <c r="N397" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P397" s="2" t="s">
         <v>744</v>
@@ -45382,7 +45379,7 @@
         <v>3262</v>
       </c>
       <c r="N398" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P398" s="2" t="s">
         <v>744</v>
@@ -45417,7 +45414,7 @@
         <v>7852</v>
       </c>
       <c r="N399" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P399" s="2">
         <f>_xlfn.XLOOKUP(C399,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -45453,7 +45450,7 @@
         <v>6978</v>
       </c>
       <c r="N400" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P400" s="2">
         <f>_xlfn.XLOOKUP(C400,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -45489,7 +45486,7 @@
         <v>7852</v>
       </c>
       <c r="N401" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P401" s="2">
         <f>_xlfn.XLOOKUP(C401,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -45525,7 +45522,7 @@
         <v>7852</v>
       </c>
       <c r="N402" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P402" s="2">
         <f>_xlfn.XLOOKUP(C402,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -45561,7 +45558,7 @@
         <v>6978</v>
       </c>
       <c r="N403" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P403" s="2">
         <f>_xlfn.XLOOKUP(C403,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -45597,7 +45594,7 @@
         <v>10654</v>
       </c>
       <c r="N404" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P404" s="2">
         <f>_xlfn.XLOOKUP(C404,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -45633,7 +45630,7 @@
         <v>10654</v>
       </c>
       <c r="N405" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P405" s="2">
         <f>_xlfn.XLOOKUP(C405,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -45669,7 +45666,7 @@
         <v>7018</v>
       </c>
       <c r="N406" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P406" s="2">
         <f>_xlfn.XLOOKUP(C406,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -45705,7 +45702,7 @@
         <v>7018</v>
       </c>
       <c r="N407" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P407" s="2">
         <f>_xlfn.XLOOKUP(C407,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -45741,7 +45738,7 @@
         <v>7018</v>
       </c>
       <c r="N408" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P408" s="2">
         <f>_xlfn.XLOOKUP(C408,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -45777,7 +45774,7 @@
         <v>7018</v>
       </c>
       <c r="N409" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P409" s="2">
         <f>_xlfn.XLOOKUP(C409,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -45813,7 +45810,7 @@
         <v>11345</v>
       </c>
       <c r="N410" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P410" s="2">
         <f>_xlfn.XLOOKUP(C410,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -45849,7 +45846,7 @@
         <v>11345</v>
       </c>
       <c r="N411" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P411" s="2">
         <f>_xlfn.XLOOKUP(C411,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -45885,7 +45882,7 @@
         <v>11345</v>
       </c>
       <c r="N412" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P412" s="2" t="s">
         <v>744</v>
@@ -45920,7 +45917,7 @@
         <v>11345</v>
       </c>
       <c r="N413" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P413" s="2" t="s">
         <v>744</v>
@@ -45955,7 +45952,7 @@
         <v>12094</v>
       </c>
       <c r="N414" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P414" s="2" t="s">
         <v>744</v>
@@ -45990,7 +45987,7 @@
         <v>6432</v>
       </c>
       <c r="N415" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P415" s="2">
         <f>_xlfn.XLOOKUP(C415,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46026,7 +46023,7 @@
         <v>6432</v>
       </c>
       <c r="N416" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P416" s="2">
         <f>_xlfn.XLOOKUP(C416,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46062,7 +46059,7 @@
         <v>7641</v>
       </c>
       <c r="N417" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P417" s="2">
         <f>_xlfn.XLOOKUP(C417,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46098,7 +46095,7 @@
         <v>7641</v>
       </c>
       <c r="N418" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P418" s="2">
         <f>_xlfn.XLOOKUP(C418,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46134,7 +46131,7 @@
         <v>7641</v>
       </c>
       <c r="N419" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P419" s="2">
         <f>_xlfn.XLOOKUP(C419,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46170,7 +46167,7 @@
         <v>623</v>
       </c>
       <c r="N420" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P420" s="2" t="s">
         <v>744</v>
@@ -46205,7 +46202,7 @@
         <v>832</v>
       </c>
       <c r="N421" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P421" s="2" t="s">
         <v>744</v>
@@ -46240,7 +46237,7 @@
         <v>1032</v>
       </c>
       <c r="N422" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P422" s="2" t="s">
         <v>744</v>
@@ -46275,7 +46272,7 @@
         <v>1822</v>
       </c>
       <c r="N423" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P423" s="2" t="s">
         <v>744</v>
@@ -46310,7 +46307,7 @@
         <v>1074</v>
       </c>
       <c r="N424" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P424" s="2">
         <f>_xlfn.XLOOKUP(C424,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46346,7 +46343,7 @@
         <v>720</v>
       </c>
       <c r="N425" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P425" s="2">
         <f>_xlfn.XLOOKUP(C425,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46382,7 +46379,7 @@
         <v>1015</v>
       </c>
       <c r="N426" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P426" s="2">
         <f>_xlfn.XLOOKUP(C426,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46418,7 +46415,7 @@
         <v>1130</v>
       </c>
       <c r="N427" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P427" s="2">
         <f>_xlfn.XLOOKUP(C427,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46454,7 +46451,7 @@
         <v>1566</v>
       </c>
       <c r="N428" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P428" s="2">
         <f>_xlfn.XLOOKUP(C428,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46490,7 +46487,7 @@
         <v>1254</v>
       </c>
       <c r="N429" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P429" s="2">
         <f>_xlfn.XLOOKUP(C429,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46526,7 +46523,7 @@
         <v>1341</v>
       </c>
       <c r="N430" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P430" s="2">
         <f>_xlfn.XLOOKUP(C430,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46562,7 +46559,7 @@
         <v>2236</v>
       </c>
       <c r="N431" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P431" s="2">
         <f>_xlfn.XLOOKUP(C431,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46598,7 +46595,7 @@
         <v>866</v>
       </c>
       <c r="N432" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P432" s="2">
         <f>_xlfn.XLOOKUP(C432,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46634,7 +46631,7 @@
         <v>1380</v>
       </c>
       <c r="N433" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P433" s="2">
         <f>_xlfn.XLOOKUP(C433,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46670,7 +46667,7 @@
         <v>3200</v>
       </c>
       <c r="N434" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P434" s="2">
         <f>_xlfn.XLOOKUP(C434,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46706,7 +46703,7 @@
         <v>2043</v>
       </c>
       <c r="N435" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P435" s="2">
         <f>_xlfn.XLOOKUP(C435,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46742,7 +46739,7 @@
         <v>2016</v>
       </c>
       <c r="N436" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P436" s="2">
         <f>_xlfn.XLOOKUP(C436,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46778,7 +46775,7 @@
         <v>2722</v>
       </c>
       <c r="N437" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P437" s="2">
         <f>_xlfn.XLOOKUP(C437,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46814,7 +46811,7 @@
         <v>589</v>
       </c>
       <c r="N438" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P438" s="2">
         <f>_xlfn.XLOOKUP(C438,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46850,7 +46847,7 @@
         <v>724</v>
       </c>
       <c r="N439" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P439" s="2">
         <f>_xlfn.XLOOKUP(C439,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46886,7 +46883,7 @@
         <v>175</v>
       </c>
       <c r="N440" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P440" s="2">
         <f>_xlfn.XLOOKUP(C440,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46922,7 +46919,7 @@
         <v>113</v>
       </c>
       <c r="N441" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P441" s="2">
         <f>_xlfn.XLOOKUP(C441,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46958,7 +46955,7 @@
         <v>179</v>
       </c>
       <c r="N442" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P442" s="2">
         <f>_xlfn.XLOOKUP(C442,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46994,7 +46991,7 @@
         <v>230</v>
       </c>
       <c r="N443" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P443" s="2">
         <f>_xlfn.XLOOKUP(C443,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -47003,11 +47000,11 @@
     </row>
     <row r="444" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A444" s="5" t="s">
-        <v>3045</v>
+        <v>3044</v>
       </c>
       <c r="B444" s="5"/>
       <c r="C444" s="20" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="D444" s="5" t="s">
         <v>521</v>
@@ -47030,7 +47027,7 @@
         <v>230</v>
       </c>
       <c r="N444" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P444" s="2" t="s">
         <v>744</v>
@@ -47065,7 +47062,7 @@
         <v>0</v>
       </c>
       <c r="N445" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P445" s="2" t="s">
         <v>744</v>
@@ -47100,7 +47097,7 @@
         <v>0</v>
       </c>
       <c r="N446" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P446" s="2" t="s">
         <v>744</v>
@@ -47135,7 +47132,7 @@
         <v>0</v>
       </c>
       <c r="N447" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P447" s="2" t="s">
         <v>744</v>
@@ -47170,7 +47167,7 @@
         <v>0</v>
       </c>
       <c r="N448" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P448" s="2" t="s">
         <v>744</v>
@@ -47205,7 +47202,7 @@
         <v>0</v>
       </c>
       <c r="N449" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P449" s="2" t="s">
         <v>744</v>
@@ -47240,7 +47237,7 @@
         <v>0</v>
       </c>
       <c r="N450" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P450" s="2" t="s">
         <v>744</v>
@@ -47275,7 +47272,7 @@
         <v>0</v>
       </c>
       <c r="N451" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P451" s="2" t="s">
         <v>744</v>
@@ -47310,7 +47307,7 @@
         <v>0</v>
       </c>
       <c r="N452" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P452" s="2" t="s">
         <v>744</v>
@@ -47345,7 +47342,7 @@
         <v>0</v>
       </c>
       <c r="N453" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P453" s="2" t="s">
         <v>744</v>
@@ -47380,7 +47377,7 @@
         <v>0</v>
       </c>
       <c r="N454" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P454" s="2" t="s">
         <v>744</v>
@@ -47415,7 +47412,7 @@
         <v>0</v>
       </c>
       <c r="N455" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P455" s="2" t="s">
         <v>744</v>
@@ -47450,7 +47447,7 @@
         <v>0</v>
       </c>
       <c r="N456" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P456" s="2" t="s">
         <v>744</v>
@@ -47485,7 +47482,7 @@
         <v>0</v>
       </c>
       <c r="N457" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P457" s="2" t="s">
         <v>744</v>
@@ -47520,7 +47517,7 @@
         <v>0</v>
       </c>
       <c r="N458" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P458" s="2" t="s">
         <v>744</v>
@@ -47555,7 +47552,7 @@
         <v>0</v>
       </c>
       <c r="N459" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P459" s="2" t="s">
         <v>744</v>
@@ -47590,7 +47587,7 @@
         <v>0</v>
       </c>
       <c r="N460" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P460" s="2" t="s">
         <v>744</v>
@@ -47625,7 +47622,7 @@
         <v>0</v>
       </c>
       <c r="N461" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P461" s="2" t="s">
         <v>744</v>
@@ -47660,7 +47657,7 @@
         <v>0</v>
       </c>
       <c r="N462" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P462" s="2" t="s">
         <v>744</v>
@@ -47695,7 +47692,7 @@
         <v>0</v>
       </c>
       <c r="N463" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P463" s="2" t="s">
         <v>744</v>
@@ -47730,7 +47727,7 @@
         <v>0</v>
       </c>
       <c r="N464" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P464" s="2" t="s">
         <v>744</v>
@@ -47765,7 +47762,7 @@
         <v>0</v>
       </c>
       <c r="N465" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P465" s="2" t="s">
         <v>744</v>
@@ -47800,7 +47797,7 @@
         <v>0</v>
       </c>
       <c r="N466" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P466" s="2" t="s">
         <v>744</v>
@@ -47835,7 +47832,7 @@
         <v>0</v>
       </c>
       <c r="N467" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P467" s="2" t="s">
         <v>744</v>
@@ -47870,7 +47867,7 @@
         <v>0</v>
       </c>
       <c r="N468" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P468" s="2" t="s">
         <v>744</v>
@@ -47905,7 +47902,7 @@
         <v>0</v>
       </c>
       <c r="N469" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P469" s="2" t="s">
         <v>744</v>
@@ -47940,7 +47937,7 @@
         <v>0</v>
       </c>
       <c r="N470" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P470" s="2" t="s">
         <v>744</v>
@@ -47975,7 +47972,7 @@
         <v>0</v>
       </c>
       <c r="N471" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P471" s="2" t="s">
         <v>744</v>
@@ -48010,7 +48007,7 @@
         <v>0</v>
       </c>
       <c r="N472" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P472" s="2" t="s">
         <v>744</v>
@@ -48045,7 +48042,7 @@
         <v>0</v>
       </c>
       <c r="N473" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P473" s="2" t="s">
         <v>744</v>
@@ -48080,7 +48077,7 @@
         <v>0</v>
       </c>
       <c r="N474" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P474" s="2" t="s">
         <v>744</v>
@@ -48115,7 +48112,7 @@
         <v>0</v>
       </c>
       <c r="N475" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P475" s="2" t="s">
         <v>744</v>
@@ -48150,7 +48147,7 @@
         <v>0</v>
       </c>
       <c r="N476" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P476" s="2" t="s">
         <v>744</v>
@@ -48185,7 +48182,7 @@
         <v>0</v>
       </c>
       <c r="N477" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P477" s="2" t="s">
         <v>744</v>
@@ -48220,7 +48217,7 @@
         <v>0</v>
       </c>
       <c r="N478" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P478" s="2" t="s">
         <v>744</v>
@@ -48255,7 +48252,7 @@
         <v>0</v>
       </c>
       <c r="N479" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P479" s="2" t="s">
         <v>744</v>
@@ -48290,7 +48287,7 @@
         <v>0</v>
       </c>
       <c r="N480" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P480" s="2" t="s">
         <v>744</v>
@@ -48325,7 +48322,7 @@
         <v>0</v>
       </c>
       <c r="N481" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P481" s="2" t="s">
         <v>744</v>
@@ -48360,7 +48357,7 @@
         <v>0</v>
       </c>
       <c r="N482" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P482" s="2" t="s">
         <v>744</v>
@@ -48395,7 +48392,7 @@
         <v>0</v>
       </c>
       <c r="N483" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P483" s="2" t="s">
         <v>744</v>
@@ -57192,13 +57189,13 @@
       </c>
       <c r="F835" s="5"/>
       <c r="G835" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H835" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I835" s="5" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="J835" s="5" t="s">
         <v>2794</v>
@@ -57227,13 +57224,13 @@
       </c>
       <c r="F836" s="5"/>
       <c r="G836" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H836" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I836" s="5" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="J836" s="5" t="s">
         <v>2794</v>
@@ -57262,10 +57259,10 @@
       </c>
       <c r="F837" s="5"/>
       <c r="G837" s="5" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="H837" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I837" s="5" t="s">
         <v>744</v>
@@ -57297,10 +57294,10 @@
       </c>
       <c r="F838" s="5"/>
       <c r="G838" s="5" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="H838" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I838" s="5" t="s">
         <v>744</v>
@@ -57332,10 +57329,10 @@
       </c>
       <c r="F839" s="5"/>
       <c r="G839" s="5" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="H839" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I839" s="5" t="s">
         <v>744</v>
@@ -57367,10 +57364,10 @@
       </c>
       <c r="F840" s="5"/>
       <c r="G840" s="5" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="H840" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I840" s="5" t="s">
         <v>744</v>
@@ -58100,10 +58097,10 @@
       </c>
       <c r="F869" s="5"/>
       <c r="G869" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H869" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I869" s="5" t="s">
         <v>744</v>
@@ -58134,7 +58131,7 @@
       <c r="F870" s="5"/>
       <c r="G870" s="5"/>
       <c r="H870" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I870" s="5" t="s">
         <v>744</v>
@@ -58165,7 +58162,7 @@
       <c r="F871" s="5"/>
       <c r="G871" s="5"/>
       <c r="H871" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I871" s="5" t="s">
         <v>744</v>
@@ -58197,10 +58194,10 @@
       </c>
       <c r="F872" s="5"/>
       <c r="G872" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H872" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I872" s="5" t="s">
         <v>744</v>
@@ -58222,7 +58219,7 @@
       </c>
       <c r="B873" s="5"/>
       <c r="C873" s="5" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="D873" s="5" t="s">
         <v>520</v>
@@ -58232,10 +58229,10 @@
       </c>
       <c r="F873" s="5"/>
       <c r="G873" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H873" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I873" s="5" t="s">
         <v>744</v>
@@ -58257,7 +58254,7 @@
       </c>
       <c r="B874" s="5"/>
       <c r="C874" s="5" t="s">
-        <v>2945</v>
+        <v>2944</v>
       </c>
       <c r="D874" s="5" t="s">
         <v>520</v>
@@ -58267,10 +58264,10 @@
       </c>
       <c r="F874" s="5"/>
       <c r="G874" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H874" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I874" s="5" t="s">
         <v>744</v>
@@ -58292,7 +58289,7 @@
       </c>
       <c r="B875" s="5"/>
       <c r="C875" s="5" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="D875" s="5" t="s">
         <v>520</v>
@@ -58302,10 +58299,10 @@
       </c>
       <c r="F875" s="5"/>
       <c r="G875" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H875" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I875" s="5" t="s">
         <v>744</v>
@@ -58335,10 +58332,10 @@
       </c>
       <c r="F876" s="5"/>
       <c r="G876" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H876" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I876" s="5" t="s">
         <v>744</v>
@@ -58368,10 +58365,10 @@
       </c>
       <c r="F877" s="5"/>
       <c r="G877" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H877" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I877" s="5" t="s">
         <v>744</v>
@@ -58412,11 +58409,11 @@
         <v>357</v>
       </c>
       <c r="L878" s="22" t="s">
-        <v>9396</v>
+        <v>9395</v>
       </c>
       <c r="M878" s="15"/>
       <c r="N878" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P878" s="2">
         <v>1</v>
@@ -58440,13 +58437,13 @@
         <v>6199</v>
       </c>
       <c r="G879" s="5" t="s">
+        <v>2972</v>
+      </c>
+      <c r="H879" s="5" t="s">
+        <v>2953</v>
+      </c>
+      <c r="I879" s="5" t="s">
         <v>2973</v>
-      </c>
-      <c r="H879" s="5" t="s">
-        <v>2954</v>
-      </c>
-      <c r="I879" s="5" t="s">
-        <v>2974</v>
       </c>
       <c r="J879" s="6" t="s">
         <v>355</v>
@@ -58459,7 +58456,7 @@
       </c>
       <c r="M879" s="15"/>
       <c r="N879" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P879" s="2" t="e">
         <v>#N/A</v>
@@ -58483,13 +58480,13 @@
         <v>10199</v>
       </c>
       <c r="G880" s="5" t="s">
-        <v>2973</v>
+        <v>2972</v>
       </c>
       <c r="H880" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I880" s="5" t="s">
-        <v>2975</v>
+        <v>2974</v>
       </c>
       <c r="J880" s="6" t="s">
         <v>355</v>
@@ -58502,7 +58499,7 @@
       </c>
       <c r="M880" s="15"/>
       <c r="N880" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P880" s="2">
         <v>1</v>
@@ -58526,13 +58523,13 @@
         <v>12499</v>
       </c>
       <c r="G881" s="5" t="s">
-        <v>2973</v>
+        <v>2972</v>
       </c>
       <c r="H881" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I881" s="5" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
       <c r="J881" s="6" t="s">
         <v>355</v>
@@ -58545,7 +58542,7 @@
       </c>
       <c r="M881" s="15"/>
       <c r="N881" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P881" s="2">
         <v>1</v>
@@ -58580,7 +58577,7 @@
       </c>
       <c r="M882" s="15"/>
       <c r="N882" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P882" s="2">
         <v>4</v>
@@ -58604,13 +58601,13 @@
         <v>2299</v>
       </c>
       <c r="G883" s="5" t="s">
-        <v>2973</v>
+        <v>2972</v>
       </c>
       <c r="H883" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I883" s="5" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="J883" s="5" t="s">
         <v>356</v>
@@ -58619,11 +58616,11 @@
         <v>367</v>
       </c>
       <c r="L883" s="22" t="s">
-        <v>9397</v>
+        <v>9396</v>
       </c>
       <c r="M883" s="15"/>
       <c r="N883" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P883" s="2">
         <v>50</v>
@@ -58645,10 +58642,10 @@
       </c>
       <c r="F884" s="5"/>
       <c r="G884" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H884" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I884" s="5" t="s">
         <v>744</v>
@@ -58680,10 +58677,10 @@
       </c>
       <c r="F885" s="5"/>
       <c r="G885" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H885" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I885" s="5" t="s">
         <v>744</v>
@@ -58705,7 +58702,7 @@
       </c>
       <c r="B886" s="5"/>
       <c r="C886" s="19" t="s">
-        <v>3041</v>
+        <v>3040</v>
       </c>
       <c r="D886" s="5" t="s">
         <v>520</v>
@@ -58734,7 +58731,7 @@
       </c>
       <c r="B887" s="5"/>
       <c r="C887" s="19" t="s">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="D887" s="5" t="s">
         <v>520</v>
@@ -58840,11 +58837,11 @@
     </row>
     <row r="891" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A891" s="5" t="s">
-        <v>2861</v>
+        <v>3025</v>
       </c>
       <c r="B891" s="5"/>
       <c r="C891" s="5" t="s">
-        <v>2884</v>
+        <v>2883</v>
       </c>
       <c r="D891" s="5" t="s">
         <v>520</v>
@@ -58854,10 +58851,10 @@
       </c>
       <c r="F891" s="5"/>
       <c r="G891" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H891" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I891" s="5" t="s">
         <v>744</v>
@@ -58875,7 +58872,7 @@
     </row>
     <row r="892" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A892" s="5" t="s">
-        <v>3026</v>
+        <v>2861</v>
       </c>
       <c r="B892" s="5"/>
       <c r="C892" s="5" t="s">
@@ -58885,27 +58882,27 @@
         <v>520</v>
       </c>
       <c r="E892" s="5" t="s">
-        <v>946</v>
+        <v>2889</v>
       </c>
       <c r="F892" s="5"/>
       <c r="G892" s="5" t="s">
-        <v>2989</v>
+        <v>2958</v>
       </c>
       <c r="H892" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I892" s="5" t="s">
         <v>744</v>
       </c>
       <c r="J892" s="5" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="K892" s="5" t="s">
-        <v>1099</v>
+        <v>2910</v>
       </c>
       <c r="L892" s="5"/>
       <c r="M892" s="15">
-        <v>1693.3</v>
+        <v>5083.8175999999994</v>
       </c>
     </row>
     <row r="893" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -58924,10 +58921,10 @@
       </c>
       <c r="F893" s="5"/>
       <c r="G893" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H893" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I893" s="5" t="s">
         <v>744</v>
@@ -58940,7 +58937,7 @@
       </c>
       <c r="L893" s="5"/>
       <c r="M893" s="15">
-        <v>5083.8175999999994</v>
+        <v>4617.7883999999995</v>
       </c>
     </row>
     <row r="894" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -58959,10 +58956,10 @@
       </c>
       <c r="F894" s="5"/>
       <c r="G894" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H894" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I894" s="5" t="s">
         <v>744</v>
@@ -58975,7 +58972,7 @@
       </c>
       <c r="L894" s="5"/>
       <c r="M894" s="15">
-        <v>4617.7883999999995</v>
+        <v>3186.0472</v>
       </c>
     </row>
     <row r="895" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -58994,10 +58991,10 @@
       </c>
       <c r="F895" s="5"/>
       <c r="G895" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H895" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I895" s="5" t="s">
         <v>744</v>
@@ -59010,7 +59007,7 @@
       </c>
       <c r="L895" s="5"/>
       <c r="M895" s="15">
-        <v>3186.0472</v>
+        <v>3401.5623999999998</v>
       </c>
     </row>
     <row r="896" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -59029,10 +59026,10 @@
       </c>
       <c r="F896" s="5"/>
       <c r="G896" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H896" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I896" s="5" t="s">
         <v>744</v>
@@ -59045,7 +59042,7 @@
       </c>
       <c r="L896" s="5"/>
       <c r="M896" s="15">
-        <v>3401.5623999999998</v>
+        <v>9756.83</v>
       </c>
     </row>
     <row r="897" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -59053,9 +59050,7 @@
         <v>2866</v>
       </c>
       <c r="B897" s="5"/>
-      <c r="C897" s="5" t="s">
-        <v>2889</v>
-      </c>
+      <c r="C897" s="5"/>
       <c r="D897" s="5" t="s">
         <v>520</v>
       </c>
@@ -59063,15 +59058,9 @@
         <v>2894</v>
       </c>
       <c r="F897" s="5"/>
-      <c r="G897" s="5" t="s">
-        <v>2959</v>
-      </c>
-      <c r="H897" s="5" t="s">
-        <v>2957</v>
-      </c>
-      <c r="I897" s="5" t="s">
-        <v>744</v>
-      </c>
+      <c r="G897" s="5"/>
+      <c r="H897" s="5"/>
+      <c r="I897" s="5"/>
       <c r="J897" s="5" t="s">
         <v>1124</v>
       </c>
@@ -59080,7 +59069,7 @@
       </c>
       <c r="L897" s="5"/>
       <c r="M897" s="15">
-        <v>9756.83</v>
+        <v>5471.3886000000002</v>
       </c>
     </row>
     <row r="898" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -59088,7 +59077,9 @@
         <v>2867</v>
       </c>
       <c r="B898" s="5"/>
-      <c r="C898" s="5"/>
+      <c r="C898" t="s">
+        <v>3039</v>
+      </c>
       <c r="D898" s="5" t="s">
         <v>520</v>
       </c>
@@ -59115,9 +59106,7 @@
         <v>2868</v>
       </c>
       <c r="B899" s="5"/>
-      <c r="C899" t="s">
-        <v>3040</v>
-      </c>
+      <c r="C899" s="5"/>
       <c r="D899" s="5" t="s">
         <v>520</v>
       </c>
@@ -59129,14 +59118,14 @@
       <c r="H899" s="5"/>
       <c r="I899" s="5"/>
       <c r="J899" s="5" t="s">
-        <v>1124</v>
+        <v>2794</v>
       </c>
       <c r="K899" s="5" t="s">
         <v>2917</v>
       </c>
       <c r="L899" s="5"/>
       <c r="M899" s="15">
-        <v>5471.3886000000002</v>
+        <v>1365.6045599999998</v>
       </c>
     </row>
     <row r="900" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -59163,7 +59152,7 @@
       </c>
       <c r="L900" s="5"/>
       <c r="M900" s="15">
-        <v>1365.6045599999998</v>
+        <v>1201.7320127999999</v>
       </c>
     </row>
     <row r="901" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -59190,7 +59179,7 @@
       </c>
       <c r="L901" s="5"/>
       <c r="M901" s="15">
-        <v>1201.7320127999999</v>
+        <v>1775.2859279999998</v>
       </c>
     </row>
     <row r="902" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -59213,11 +59202,11 @@
         <v>2794</v>
       </c>
       <c r="K902" s="5" t="s">
-        <v>2920</v>
+        <v>2917</v>
       </c>
       <c r="L902" s="5"/>
       <c r="M902" s="15">
-        <v>1775.2859279999998</v>
+        <v>2731.2091199999995</v>
       </c>
     </row>
     <row r="903" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -59225,26 +59214,34 @@
         <v>2872</v>
       </c>
       <c r="B903" s="5"/>
-      <c r="C903" s="5"/>
+      <c r="C903" s="5" t="s">
+        <v>2942</v>
+      </c>
       <c r="D903" s="5" t="s">
         <v>520</v>
       </c>
       <c r="E903" s="5" t="s">
-        <v>2900</v>
+        <v>1078</v>
       </c>
       <c r="F903" s="5"/>
-      <c r="G903" s="5"/>
-      <c r="H903" s="5"/>
-      <c r="I903" s="5"/>
+      <c r="G903" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H903" s="5" t="s">
+        <v>2956</v>
+      </c>
+      <c r="I903" s="5" t="s">
+        <v>744</v>
+      </c>
       <c r="J903" s="5" t="s">
-        <v>2794</v>
+        <v>2795</v>
       </c>
       <c r="K903" s="5" t="s">
-        <v>2918</v>
+        <v>2856</v>
       </c>
       <c r="L903" s="5"/>
       <c r="M903" s="15">
-        <v>2731.2091199999995</v>
+        <v>1544.9101177499999</v>
       </c>
     </row>
     <row r="904" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -59252,34 +59249,26 @@
         <v>2873</v>
       </c>
       <c r="B904" s="5"/>
-      <c r="C904" s="5" t="s">
-        <v>2943</v>
-      </c>
+      <c r="C904" s="5"/>
       <c r="D904" s="5" t="s">
         <v>520</v>
       </c>
       <c r="E904" s="5" t="s">
-        <v>1078</v>
+        <v>2900</v>
       </c>
       <c r="F904" s="5"/>
-      <c r="G904" s="5" t="s">
-        <v>2953</v>
-      </c>
-      <c r="H904" s="5" t="s">
-        <v>2957</v>
-      </c>
-      <c r="I904" s="5" t="s">
-        <v>744</v>
-      </c>
+      <c r="G904" s="5"/>
+      <c r="H904" s="5"/>
+      <c r="I904" s="5"/>
       <c r="J904" s="5" t="s">
-        <v>2795</v>
+        <v>1152</v>
       </c>
       <c r="K904" s="5" t="s">
-        <v>2856</v>
+        <v>2920</v>
       </c>
       <c r="L904" s="5"/>
       <c r="M904" s="15">
-        <v>1544.9101177499999</v>
+        <v>2592.4323549599999</v>
       </c>
     </row>
     <row r="905" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -59306,7 +59295,7 @@
       </c>
       <c r="L905" s="5"/>
       <c r="M905" s="15">
-        <v>2592.4323549599999</v>
+        <v>4146.8485356000001</v>
       </c>
     </row>
     <row r="906" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -59333,7 +59322,7 @@
       </c>
       <c r="L906" s="5"/>
       <c r="M906" s="15">
-        <v>4146.8485356000001</v>
+        <v>1551.8080997999998</v>
       </c>
     </row>
     <row r="907" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -59360,7 +59349,7 @@
       </c>
       <c r="L907" s="5"/>
       <c r="M907" s="15">
-        <v>1551.8080997999998</v>
+        <v>1549.2000189600001</v>
       </c>
     </row>
     <row r="908" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -59387,7 +59376,7 @@
       </c>
       <c r="L908" s="5"/>
       <c r="M908" s="15">
-        <v>1549.2000189600001</v>
+        <v>2070.8161869599999</v>
       </c>
     </row>
     <row r="909" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -59414,7 +59403,7 @@
       </c>
       <c r="L909" s="5"/>
       <c r="M909" s="15">
-        <v>2070.8161869599999</v>
+        <v>1073.2252656600001</v>
       </c>
     </row>
     <row r="910" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -59441,7 +59430,7 @@
       </c>
       <c r="L910" s="5"/>
       <c r="M910" s="15">
-        <v>1073.2252656600001</v>
+        <v>2216.8687139999997</v>
       </c>
     </row>
     <row r="911" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -59468,7 +59457,7 @@
       </c>
       <c r="L911" s="5"/>
       <c r="M911" s="15">
-        <v>2216.8687139999997</v>
+        <v>2412.4747769999999</v>
       </c>
     </row>
     <row r="912" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -59495,7 +59484,7 @@
       </c>
       <c r="L912" s="5"/>
       <c r="M912" s="15">
-        <v>2412.4747769999999</v>
+        <v>1551.8080997999998</v>
       </c>
     </row>
     <row r="913" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -59515,122 +59504,130 @@
       <c r="H913" s="5"/>
       <c r="I913" s="5"/>
       <c r="J913" s="5" t="s">
-        <v>1152</v>
+        <v>2851</v>
       </c>
       <c r="K913" s="5" t="s">
         <v>2929</v>
       </c>
       <c r="L913" s="5"/>
       <c r="M913" s="15">
-        <v>1551.8080997999998</v>
+        <v>2034.3030551999998</v>
       </c>
     </row>
     <row r="914" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A914" s="5" t="s">
-        <v>2883</v>
+        <v>3028</v>
       </c>
       <c r="B914" s="5"/>
-      <c r="C914" s="5"/>
+      <c r="C914" s="19" t="s">
+        <v>3042</v>
+      </c>
       <c r="D914" s="5" t="s">
         <v>520</v>
       </c>
       <c r="E914" s="5" t="s">
-        <v>2910</v>
+        <v>3029</v>
       </c>
       <c r="F914" s="5"/>
       <c r="G914" s="5"/>
       <c r="H914" s="5"/>
       <c r="I914" s="5"/>
-      <c r="J914" s="5" t="s">
-        <v>2851</v>
-      </c>
-      <c r="K914" s="5" t="s">
-        <v>2930</v>
-      </c>
+      <c r="K914" s="5"/>
       <c r="L914" s="5"/>
-      <c r="M914" s="15">
-        <v>2034.3030551999998</v>
-      </c>
+      <c r="M914" s="15"/>
     </row>
     <row r="915" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A915" s="5" t="s">
-        <v>3029</v>
+        <v>3031</v>
       </c>
       <c r="B915" s="5"/>
-      <c r="C915" s="19" t="s">
-        <v>3043</v>
+      <c r="C915" s="5" t="s">
+        <v>3037</v>
       </c>
       <c r="D915" s="5" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="E915" s="5" t="s">
-        <v>3030</v>
+        <v>1259</v>
       </c>
       <c r="F915" s="5"/>
       <c r="G915" s="5"/>
       <c r="H915" s="5"/>
       <c r="I915" s="5"/>
-      <c r="K915" s="5"/>
+      <c r="J915" s="16" t="s">
+        <v>1115</v>
+      </c>
+      <c r="K915" s="16" t="s">
+        <v>1292</v>
+      </c>
       <c r="L915" s="5"/>
       <c r="M915" s="15"/>
     </row>
     <row r="916" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A916" s="5" t="s">
-        <v>3032</v>
+        <v>3033</v>
       </c>
       <c r="B916" s="5"/>
       <c r="C916" s="5" t="s">
-        <v>3038</v>
+        <v>3032</v>
       </c>
       <c r="D916" s="5" t="s">
-        <v>522</v>
+        <v>6</v>
       </c>
       <c r="E916" s="5" t="s">
-        <v>1259</v>
+        <v>329</v>
       </c>
       <c r="F916" s="5"/>
       <c r="G916" s="5"/>
       <c r="H916" s="5"/>
       <c r="I916" s="5"/>
-      <c r="J916" s="16" t="s">
-        <v>1115</v>
-      </c>
-      <c r="K916" s="16" t="s">
-        <v>1292</v>
-      </c>
-      <c r="L916" s="5"/>
+      <c r="J916" s="22" t="s">
+        <v>356</v>
+      </c>
+      <c r="K916" s="22" t="s">
+        <v>361</v>
+      </c>
+      <c r="L916" s="22" t="s">
+        <v>361</v>
+      </c>
       <c r="M916" s="15"/>
+      <c r="N916" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P916" s="2" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="917" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A917" s="5" t="s">
-        <v>3034</v>
+        <v>3035</v>
       </c>
       <c r="B917" s="5"/>
       <c r="C917" s="5" t="s">
-        <v>3033</v>
+        <v>3036</v>
       </c>
       <c r="D917" s="5" t="s">
         <v>6</v>
       </c>
       <c r="E917" s="5" t="s">
-        <v>329</v>
+        <v>3034</v>
       </c>
       <c r="F917" s="5"/>
       <c r="G917" s="5"/>
       <c r="H917" s="5"/>
       <c r="I917" s="5"/>
-      <c r="J917" s="22" t="s">
-        <v>356</v>
+      <c r="J917" s="23" t="s">
+        <v>355</v>
       </c>
       <c r="K917" s="22" t="s">
-        <v>361</v>
+        <v>9397</v>
       </c>
       <c r="L917" s="22" t="s">
-        <v>361</v>
+        <v>9397</v>
       </c>
       <c r="M917" s="15"/>
       <c r="N917" s="2" t="s">
-        <v>9393</v>
+        <v>9391</v>
       </c>
       <c r="P917" s="2" t="e">
         <v>#N/A</v>
@@ -59638,72 +59635,54 @@
     </row>
     <row r="918" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A918" s="5" t="s">
-        <v>3036</v>
+        <v>1209</v>
       </c>
       <c r="B918" s="5"/>
       <c r="C918" s="5" t="s">
-        <v>3037</v>
+        <v>3038</v>
       </c>
       <c r="D918" s="5" t="s">
-        <v>6</v>
+        <v>522</v>
       </c>
       <c r="E918" s="5" t="s">
-        <v>3035</v>
+        <v>1259</v>
       </c>
       <c r="F918" s="5"/>
       <c r="G918" s="5"/>
       <c r="H918" s="5"/>
       <c r="I918" s="5"/>
-      <c r="J918" s="23" t="s">
-        <v>355</v>
-      </c>
-      <c r="K918" s="22" t="s">
-        <v>9398</v>
-      </c>
-      <c r="L918" s="22" t="s">
-        <v>9398</v>
-      </c>
+      <c r="J918" s="16" t="s">
+        <v>1115</v>
+      </c>
+      <c r="K918" s="16" t="s">
+        <v>1292</v>
+      </c>
+      <c r="L918" s="5"/>
       <c r="M918" s="15"/>
-      <c r="N918" s="2" t="s">
-        <v>9392</v>
-      </c>
-      <c r="P918" s="2" t="e">
+    </row>
+    <row r="919" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A919" s="2" t="s">
+        <v>3046</v>
+      </c>
+      <c r="C919" s="2" t="s">
+        <v>3045</v>
+      </c>
+      <c r="D919" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N919" s="2" t="s">
+        <v>9391</v>
+      </c>
+      <c r="P919" s="2" t="e">
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="919" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A919" s="5" t="s">
-        <v>1209</v>
-      </c>
-      <c r="B919" s="5"/>
-      <c r="C919" s="5" t="s">
-        <v>3039</v>
-      </c>
-      <c r="D919" s="5" t="s">
-        <v>522</v>
-      </c>
-      <c r="E919" s="5" t="s">
-        <v>1259</v>
-      </c>
-      <c r="F919" s="5"/>
-      <c r="G919" s="5"/>
-      <c r="H919" s="5"/>
-      <c r="I919" s="5"/>
-      <c r="J919" s="16" t="s">
-        <v>1115</v>
-      </c>
-      <c r="K919" s="16" t="s">
-        <v>1292</v>
-      </c>
-      <c r="L919" s="5"/>
-      <c r="M919" s="15"/>
     </row>
     <row r="920" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A920" s="2" t="s">
+        <v>3048</v>
+      </c>
+      <c r="C920" s="2" t="s">
         <v>3047</v>
-      </c>
-      <c r="C920" s="2" t="s">
-        <v>3046</v>
       </c>
       <c r="D920" s="2" t="s">
         <v>6</v>
@@ -59720,13 +59699,13 @@
         <v>3049</v>
       </c>
       <c r="C921" s="2" t="s">
-        <v>3048</v>
+        <v>3050</v>
       </c>
       <c r="D921" s="2" t="s">
         <v>6</v>
       </c>
       <c r="N921" s="2" t="s">
-        <v>9393</v>
+        <v>9391</v>
       </c>
       <c r="P921" s="2" t="e">
         <v>#N/A</v>
@@ -59734,10 +59713,10 @@
     </row>
     <row r="922" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A922" s="2" t="s">
-        <v>3050</v>
+        <v>3051</v>
       </c>
       <c r="C922" s="2" t="s">
-        <v>3051</v>
+        <v>3052</v>
       </c>
       <c r="D922" s="2" t="s">
         <v>6</v>
@@ -59751,7 +59730,7 @@
     </row>
     <row r="923" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A923" s="2" t="s">
-        <v>3052</v>
+        <v>3054</v>
       </c>
       <c r="C923" s="2" t="s">
         <v>3053</v>
@@ -59760,7 +59739,7 @@
         <v>6</v>
       </c>
       <c r="N923" s="2" t="s">
-        <v>9393</v>
+        <v>9391</v>
       </c>
       <c r="P923" s="2" t="e">
         <v>#N/A</v>
@@ -59768,19 +59747,19 @@
     </row>
     <row r="924" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A924" s="2" t="s">
+        <v>5134</v>
+      </c>
+      <c r="C924" s="2" t="s">
+        <v>7214</v>
+      </c>
+      <c r="D924" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E924" s="2" t="s">
         <v>3055</v>
       </c>
-      <c r="C924" s="2" t="s">
-        <v>3054</v>
-      </c>
-      <c r="D924" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="N924" s="2" t="s">
-        <v>9392</v>
-      </c>
-      <c r="P924" s="2" t="e">
-        <v>#N/A</v>
+      <c r="J924" s="5" t="s">
+        <v>2644</v>
       </c>
     </row>
     <row r="925" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -64605,7 +64584,7 @@
         <v>2643</v>
       </c>
       <c r="E1208" s="2" t="s">
-        <v>3339</v>
+        <v>3230</v>
       </c>
       <c r="J1208" s="5" t="s">
         <v>2644</v>
@@ -64622,7 +64601,7 @@
         <v>2643</v>
       </c>
       <c r="E1209" s="2" t="s">
-        <v>3231</v>
+        <v>3339</v>
       </c>
       <c r="J1209" s="5" t="s">
         <v>2644</v>
@@ -71167,7 +71146,7 @@
         <v>2643</v>
       </c>
       <c r="E1594" s="2" t="s">
-        <v>3724</v>
+        <v>3713</v>
       </c>
       <c r="J1594" s="5" t="s">
         <v>2644</v>
@@ -71184,7 +71163,7 @@
         <v>2643</v>
       </c>
       <c r="E1595" s="2" t="s">
-        <v>3714</v>
+        <v>3724</v>
       </c>
       <c r="J1595" s="5" t="s">
         <v>2644</v>
@@ -74805,7 +74784,7 @@
         <v>2643</v>
       </c>
       <c r="E1808" s="2" t="s">
-        <v>3937</v>
+        <v>3244</v>
       </c>
       <c r="J1808" s="5" t="s">
         <v>2644</v>
@@ -74822,7 +74801,7 @@
         <v>2643</v>
       </c>
       <c r="E1809" s="2" t="s">
-        <v>3245</v>
+        <v>3937</v>
       </c>
       <c r="J1809" s="5" t="s">
         <v>2644</v>
@@ -75088,13 +75067,13 @@
         <v>6035</v>
       </c>
       <c r="C1825" s="2" t="s">
-        <v>8115</v>
+        <v>7831</v>
       </c>
       <c r="D1825" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E1825" s="2" t="s">
-        <v>3953</v>
+        <v>3671</v>
       </c>
       <c r="J1825" s="5" t="s">
         <v>2644</v>
@@ -75105,13 +75084,13 @@
         <v>6036</v>
       </c>
       <c r="C1826" s="2" t="s">
-        <v>7832</v>
+        <v>8115</v>
       </c>
       <c r="D1826" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E1826" s="2" t="s">
-        <v>3672</v>
+        <v>3953</v>
       </c>
       <c r="J1826" s="5" t="s">
         <v>2644</v>
@@ -85016,7 +84995,7 @@
         <v>6619</v>
       </c>
       <c r="C2409" s="2" t="s">
-        <v>8698</v>
+        <v>8625</v>
       </c>
       <c r="D2409" s="2" t="s">
         <v>2643</v>
@@ -85033,7 +85012,7 @@
         <v>6620</v>
       </c>
       <c r="C2410" s="2" t="s">
-        <v>8626</v>
+        <v>8698</v>
       </c>
       <c r="D2410" s="2" t="s">
         <v>2643</v>
@@ -85727,10 +85706,10 @@
     </row>
     <row r="2451" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2451" s="2" t="s">
-        <v>6661</v>
+        <v>5398</v>
       </c>
       <c r="C2451" s="2" t="s">
-        <v>8739</v>
+        <v>7478</v>
       </c>
       <c r="D2451" s="2" t="s">
         <v>2643</v>
@@ -85744,10 +85723,10 @@
     </row>
     <row r="2452" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2452" s="2" t="s">
-        <v>5399</v>
+        <v>6661</v>
       </c>
       <c r="C2452" s="2" t="s">
-        <v>7479</v>
+        <v>8739</v>
       </c>
       <c r="D2452" s="2" t="s">
         <v>2643</v>
@@ -94705,8 +94684,8 @@
       <c r="A2979" s="2" t="s">
         <v>7188</v>
       </c>
-      <c r="C2979" s="2" t="s">
-        <v>9266</v>
+      <c r="C2979" s="2">
+        <v>0</v>
       </c>
       <c r="D2979" s="2" t="s">
         <v>2643</v>
@@ -94722,8 +94701,8 @@
       <c r="A2980" s="2" t="s">
         <v>7189</v>
       </c>
-      <c r="C2980" s="2">
-        <v>0</v>
+      <c r="C2980" s="2" t="s">
+        <v>9266</v>
       </c>
       <c r="D2980" s="2" t="s">
         <v>2643</v>
@@ -95008,8 +94987,8 @@
       </c>
     </row>
     <row r="2997" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2997" s="2" t="s">
-        <v>7206</v>
+      <c r="A2997" s="2">
+        <v>0</v>
       </c>
       <c r="C2997" s="2" t="s">
         <v>9283</v>
@@ -95042,8 +95021,8 @@
       </c>
     </row>
     <row r="2999" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2999" s="2">
-        <v>0</v>
+      <c r="A2999" s="2" t="s">
+        <v>7206</v>
       </c>
       <c r="C2999" s="2" t="s">
         <v>9285</v>
@@ -95179,99 +95158,99 @@
     </row>
     <row r="3007" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3007" s="2" t="s">
-        <v>7214</v>
-      </c>
-      <c r="C3007" s="2" t="s">
         <v>9293</v>
       </c>
-      <c r="D3007" s="2" t="s">
-        <v>2643</v>
+      <c r="D3007" s="5" t="s">
+        <v>520</v>
       </c>
       <c r="E3007" s="2" t="s">
-        <v>5134</v>
-      </c>
-      <c r="J3007" s="5" t="s">
-        <v>2644</v>
+        <v>9294</v>
+      </c>
+      <c r="G3007" s="2" t="s">
+        <v>2952</v>
+      </c>
+      <c r="J3007" s="2" t="s">
+        <v>1097</v>
+      </c>
+      <c r="K3007" s="2" t="s">
+        <v>1097</v>
       </c>
     </row>
     <row r="3008" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3008" s="2" t="s">
-        <v>9294</v>
+        <v>2866</v>
+      </c>
+      <c r="C3008" s="2" t="s">
+        <v>9295</v>
       </c>
       <c r="D3008" s="5" t="s">
         <v>520</v>
       </c>
       <c r="E3008" s="2" t="s">
-        <v>9295</v>
-      </c>
-      <c r="G3008" s="2" t="s">
-        <v>2953</v>
+        <v>2894</v>
       </c>
       <c r="J3008" s="2" t="s">
-        <v>1097</v>
+        <v>1124</v>
       </c>
       <c r="K3008" s="2" t="s">
-        <v>1097</v>
+        <v>2915</v>
       </c>
     </row>
     <row r="3009" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3009" s="2" t="s">
-        <v>2867</v>
-      </c>
-      <c r="C3009" s="2" t="s">
         <v>9296</v>
       </c>
       <c r="D3009" s="5" t="s">
-        <v>520</v>
-      </c>
-      <c r="E3009" s="2" t="s">
-        <v>2895</v>
-      </c>
-      <c r="J3009" s="2" t="s">
-        <v>1124</v>
-      </c>
-      <c r="K3009" s="2" t="s">
-        <v>2916</v>
+        <v>6</v>
+      </c>
+      <c r="E3009" s="21" t="s">
+        <v>9297</v>
+      </c>
+      <c r="J3009" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="K3009" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="L3009" s="2" t="s">
+        <v>9395</v>
+      </c>
+      <c r="N3009" s="2" t="s">
+        <v>9391</v>
+      </c>
+      <c r="P3009" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="3010" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3010" s="2" t="s">
-        <v>9297</v>
-      </c>
-      <c r="D3010" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3010" s="21" t="s">
         <v>9298</v>
       </c>
-      <c r="J3010" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="K3010" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="L3010" s="2" t="s">
-        <v>9396</v>
-      </c>
-      <c r="N3010" s="2" t="s">
-        <v>9392</v>
-      </c>
-      <c r="P3010" s="2">
-        <v>20</v>
+      <c r="C3010" s="2" t="s">
+        <v>9299</v>
+      </c>
+      <c r="D3010" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3010" s="2" t="s">
+        <v>9300</v>
+      </c>
+      <c r="J3010" s="5" t="s">
+        <v>2644</v>
       </c>
     </row>
     <row r="3011" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3011" s="2" t="s">
-        <v>9299</v>
+        <v>9301</v>
       </c>
       <c r="C3011" s="2" t="s">
-        <v>9300</v>
+        <v>9302</v>
       </c>
       <c r="D3011" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3011" s="2" t="s">
-        <v>9301</v>
+        <v>9303</v>
       </c>
       <c r="J3011" s="5" t="s">
         <v>2644</v>
@@ -95279,16 +95258,16 @@
     </row>
     <row r="3012" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3012" s="2" t="s">
-        <v>9302</v>
+        <v>9304</v>
       </c>
       <c r="C3012" s="2" t="s">
-        <v>9303</v>
+        <v>9305</v>
       </c>
       <c r="D3012" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3012" s="2" t="s">
-        <v>9304</v>
+        <v>9306</v>
       </c>
       <c r="J3012" s="5" t="s">
         <v>2644</v>
@@ -95296,16 +95275,16 @@
     </row>
     <row r="3013" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3013" s="2" t="s">
-        <v>9305</v>
+        <v>9307</v>
       </c>
       <c r="C3013" s="2" t="s">
-        <v>9306</v>
+        <v>9308</v>
       </c>
       <c r="D3013" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3013" s="2" t="s">
-        <v>9307</v>
+        <v>9309</v>
       </c>
       <c r="J3013" s="5" t="s">
         <v>2644</v>
@@ -95313,16 +95292,16 @@
     </row>
     <row r="3014" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3014" s="2" t="s">
-        <v>9308</v>
+        <v>9310</v>
       </c>
       <c r="C3014" s="2" t="s">
-        <v>9309</v>
+        <v>9311</v>
       </c>
       <c r="D3014" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3014" s="2" t="s">
-        <v>9310</v>
+        <v>9312</v>
       </c>
       <c r="J3014" s="5" t="s">
         <v>2644</v>
@@ -95330,16 +95309,16 @@
     </row>
     <row r="3015" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3015" s="2" t="s">
-        <v>9311</v>
+        <v>9313</v>
       </c>
       <c r="C3015" s="2" t="s">
-        <v>9312</v>
+        <v>9314</v>
       </c>
       <c r="D3015" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3015" s="2" t="s">
-        <v>9313</v>
+        <v>9315</v>
       </c>
       <c r="J3015" s="5" t="s">
         <v>2644</v>
@@ -95347,16 +95326,16 @@
     </row>
     <row r="3016" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3016" s="2" t="s">
-        <v>9314</v>
+        <v>9316</v>
       </c>
       <c r="C3016" s="2" t="s">
-        <v>9315</v>
+        <v>9317</v>
       </c>
       <c r="D3016" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3016" s="2" t="s">
-        <v>9316</v>
+        <v>9318</v>
       </c>
       <c r="J3016" s="5" t="s">
         <v>2644</v>
@@ -95364,16 +95343,16 @@
     </row>
     <row r="3017" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3017" s="2" t="s">
-        <v>9317</v>
+        <v>9319</v>
       </c>
       <c r="C3017" s="2" t="s">
-        <v>9318</v>
+        <v>9320</v>
       </c>
       <c r="D3017" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3017" s="2" t="s">
-        <v>9319</v>
+        <v>9321</v>
       </c>
       <c r="J3017" s="5" t="s">
         <v>2644</v>
@@ -95381,16 +95360,16 @@
     </row>
     <row r="3018" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3018" s="2" t="s">
-        <v>9320</v>
+        <v>9322</v>
       </c>
       <c r="C3018" s="2" t="s">
-        <v>9321</v>
+        <v>9323</v>
       </c>
       <c r="D3018" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3018" s="2" t="s">
-        <v>9322</v>
+        <v>9324</v>
       </c>
       <c r="J3018" s="5" t="s">
         <v>2644</v>
@@ -95398,16 +95377,16 @@
     </row>
     <row r="3019" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3019" s="2" t="s">
-        <v>9323</v>
+        <v>9325</v>
       </c>
       <c r="C3019" s="2" t="s">
-        <v>9324</v>
+        <v>9326</v>
       </c>
       <c r="D3019" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3019" s="2" t="s">
-        <v>9325</v>
+        <v>9327</v>
       </c>
       <c r="J3019" s="5" t="s">
         <v>2644</v>
@@ -95415,16 +95394,16 @@
     </row>
     <row r="3020" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3020" s="2" t="s">
-        <v>9326</v>
+        <v>9328</v>
       </c>
       <c r="C3020" s="2" t="s">
-        <v>9327</v>
+        <v>9329</v>
       </c>
       <c r="D3020" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3020" s="2" t="s">
-        <v>9328</v>
+        <v>9330</v>
       </c>
       <c r="J3020" s="5" t="s">
         <v>2644</v>
@@ -95432,16 +95411,16 @@
     </row>
     <row r="3021" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3021" s="2" t="s">
-        <v>9329</v>
+        <v>9331</v>
       </c>
       <c r="C3021" s="2" t="s">
-        <v>9330</v>
+        <v>9332</v>
       </c>
       <c r="D3021" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3021" s="2" t="s">
-        <v>9331</v>
+        <v>9333</v>
       </c>
       <c r="J3021" s="5" t="s">
         <v>2644</v>
@@ -95449,16 +95428,16 @@
     </row>
     <row r="3022" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3022" s="2" t="s">
-        <v>9332</v>
+        <v>9334</v>
       </c>
       <c r="C3022" s="2" t="s">
-        <v>9333</v>
+        <v>9335</v>
       </c>
       <c r="D3022" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3022" s="2" t="s">
-        <v>9334</v>
+        <v>9336</v>
       </c>
       <c r="J3022" s="5" t="s">
         <v>2644</v>
@@ -95466,16 +95445,16 @@
     </row>
     <row r="3023" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3023" s="2" t="s">
-        <v>9335</v>
+        <v>9337</v>
       </c>
       <c r="C3023" s="2" t="s">
-        <v>9336</v>
+        <v>9338</v>
       </c>
       <c r="D3023" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3023" s="2" t="s">
-        <v>9337</v>
+        <v>9339</v>
       </c>
       <c r="J3023" s="5" t="s">
         <v>2644</v>
@@ -95483,314 +95462,314 @@
     </row>
     <row r="3024" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3024" s="2" t="s">
-        <v>9338</v>
+        <v>9340</v>
       </c>
       <c r="C3024" s="2" t="s">
-        <v>9339</v>
+        <v>9341</v>
       </c>
       <c r="D3024" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3024" s="2" t="s">
-        <v>9340</v>
+        <v>9342</v>
       </c>
       <c r="J3024" s="5" t="s">
         <v>2644</v>
       </c>
     </row>
-    <row r="3025" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3025" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3025" s="2" t="s">
-        <v>9341</v>
+        <v>9343</v>
       </c>
       <c r="C3025" s="2" t="s">
-        <v>9342</v>
+        <v>9344</v>
       </c>
       <c r="D3025" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3025" s="2" t="s">
-        <v>9343</v>
+        <v>9345</v>
       </c>
       <c r="J3025" s="5" t="s">
         <v>2644</v>
       </c>
     </row>
-    <row r="3026" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3026" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3026" s="2" t="s">
-        <v>9344</v>
+        <v>9346</v>
       </c>
       <c r="C3026" s="2" t="s">
-        <v>9345</v>
+        <v>9347</v>
       </c>
       <c r="D3026" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3026" s="2" t="s">
-        <v>9346</v>
+        <v>9348</v>
       </c>
       <c r="J3026" s="5" t="s">
         <v>2644</v>
       </c>
     </row>
-    <row r="3027" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3027" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3027" s="2" t="s">
-        <v>9347</v>
+        <v>9349</v>
       </c>
       <c r="C3027" s="2" t="s">
-        <v>9348</v>
+        <v>9350</v>
       </c>
       <c r="D3027" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3027" s="2" t="s">
-        <v>9349</v>
+        <v>9351</v>
       </c>
       <c r="J3027" s="5" t="s">
         <v>2644</v>
       </c>
     </row>
-    <row r="3028" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3028" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3028" s="2" t="s">
-        <v>9350</v>
+        <v>9352</v>
       </c>
       <c r="C3028" s="2" t="s">
-        <v>9351</v>
+        <v>9353</v>
       </c>
       <c r="D3028" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3028" s="2" t="s">
-        <v>9352</v>
+        <v>9354</v>
       </c>
       <c r="J3028" s="5" t="s">
         <v>2644</v>
       </c>
     </row>
-    <row r="3029" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3029" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3029" s="2" t="s">
-        <v>9353</v>
+        <v>9355</v>
       </c>
       <c r="C3029" s="2" t="s">
-        <v>9354</v>
+        <v>9356</v>
       </c>
       <c r="D3029" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3029" s="2" t="s">
-        <v>9355</v>
+        <v>9357</v>
       </c>
       <c r="J3029" s="5" t="s">
         <v>2644</v>
       </c>
     </row>
-    <row r="3030" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3030" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3030" s="2" t="s">
-        <v>9356</v>
+        <v>9358</v>
       </c>
       <c r="C3030" s="2" t="s">
-        <v>9357</v>
+        <v>9359</v>
       </c>
       <c r="D3030" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3030" s="2" t="s">
-        <v>9358</v>
+        <v>9360</v>
       </c>
       <c r="J3030" s="5" t="s">
         <v>2644</v>
       </c>
     </row>
-    <row r="3031" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3031" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3031" s="2" t="s">
-        <v>9359</v>
+        <v>9361</v>
       </c>
       <c r="C3031" s="2" t="s">
-        <v>9360</v>
+        <v>9362</v>
       </c>
       <c r="D3031" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3031" s="2" t="s">
-        <v>9361</v>
+        <v>9363</v>
       </c>
       <c r="J3031" s="5" t="s">
         <v>2644</v>
       </c>
     </row>
-    <row r="3032" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3032" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3032" s="2" t="s">
-        <v>9362</v>
+        <v>9364</v>
       </c>
       <c r="C3032" s="2" t="s">
-        <v>9363</v>
+        <v>9365</v>
       </c>
       <c r="D3032" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3032" s="2" t="s">
-        <v>9364</v>
+        <v>9366</v>
       </c>
       <c r="J3032" s="5" t="s">
         <v>2644</v>
       </c>
     </row>
-    <row r="3033" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3033" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3033" s="2" t="s">
-        <v>9365</v>
+        <v>9367</v>
       </c>
       <c r="C3033" s="2" t="s">
-        <v>9366</v>
+        <v>9368</v>
       </c>
       <c r="D3033" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3033" s="2" t="s">
-        <v>9367</v>
+        <v>9369</v>
       </c>
       <c r="J3033" s="5" t="s">
         <v>2644</v>
       </c>
     </row>
-    <row r="3034" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3034" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3034" s="2" t="s">
-        <v>9368</v>
+        <v>9370</v>
       </c>
       <c r="C3034" s="2" t="s">
-        <v>9369</v>
+        <v>9371</v>
       </c>
       <c r="D3034" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3034" s="2" t="s">
-        <v>9370</v>
+        <v>9372</v>
       </c>
       <c r="J3034" s="5" t="s">
         <v>2644</v>
       </c>
     </row>
-    <row r="3035" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3035" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3035" s="2" t="s">
-        <v>9371</v>
+        <v>9373</v>
       </c>
       <c r="C3035" s="2" t="s">
-        <v>9372</v>
+        <v>9374</v>
       </c>
       <c r="D3035" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3035" s="2" t="s">
-        <v>9373</v>
+        <v>9375</v>
       </c>
       <c r="J3035" s="5" t="s">
         <v>2644</v>
       </c>
     </row>
-    <row r="3036" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3036" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3036" s="2" t="s">
-        <v>9374</v>
+        <v>9376</v>
       </c>
       <c r="C3036" s="2" t="s">
-        <v>9375</v>
+        <v>9377</v>
       </c>
       <c r="D3036" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3036" s="2" t="s">
-        <v>9376</v>
+        <v>9378</v>
       </c>
       <c r="J3036" s="5" t="s">
         <v>2644</v>
       </c>
     </row>
-    <row r="3037" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3037" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3037" s="2" t="s">
-        <v>9377</v>
+        <v>9379</v>
       </c>
       <c r="C3037" s="2" t="s">
-        <v>9378</v>
+        <v>9380</v>
       </c>
       <c r="D3037" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3037" s="2" t="s">
-        <v>9379</v>
+        <v>9381</v>
       </c>
       <c r="J3037" s="5" t="s">
         <v>2644</v>
       </c>
     </row>
-    <row r="3038" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3038" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3038" s="2" t="s">
-        <v>9380</v>
+        <v>9382</v>
       </c>
       <c r="C3038" s="2" t="s">
-        <v>9381</v>
+        <v>9383</v>
       </c>
       <c r="D3038" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3038" s="2" t="s">
-        <v>9382</v>
+        <v>9384</v>
       </c>
       <c r="J3038" s="5" t="s">
         <v>2644</v>
       </c>
     </row>
-    <row r="3039" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3039" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3039" s="2" t="s">
-        <v>9383</v>
+        <v>9385</v>
       </c>
       <c r="C3039" s="2" t="s">
-        <v>9384</v>
+        <v>9386</v>
       </c>
       <c r="D3039" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3039" s="2" t="s">
-        <v>9385</v>
+        <v>9387</v>
       </c>
       <c r="J3039" s="5" t="s">
         <v>2644</v>
       </c>
     </row>
-    <row r="3040" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3040" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3040" s="2" t="s">
-        <v>9386</v>
+        <v>9389</v>
       </c>
       <c r="C3040" s="2" t="s">
-        <v>9387</v>
+        <v>9388</v>
       </c>
       <c r="D3040" s="2" t="s">
-        <v>2643</v>
+        <v>6</v>
       </c>
       <c r="E3040" s="2" t="s">
-        <v>9388</v>
-      </c>
-      <c r="J3040" s="5" t="s">
-        <v>2644</v>
-      </c>
-    </row>
-    <row r="3041" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>9390</v>
+      </c>
+      <c r="N3040" s="2" t="s">
+        <v>9391</v>
+      </c>
+      <c r="P3040" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="3041" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3041" s="2" t="s">
-        <v>9390</v>
+        <v>9436</v>
       </c>
       <c r="C3041" s="2" t="s">
-        <v>9389</v>
+        <v>9403</v>
       </c>
       <c r="D3041" s="2" t="s">
-        <v>6</v>
+        <v>2643</v>
       </c>
       <c r="E3041" s="2" t="s">
-        <v>9391</v>
-      </c>
-      <c r="N3041" s="2" t="s">
-        <v>9392</v>
-      </c>
-      <c r="P3041" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="3042" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>9469</v>
+      </c>
+      <c r="J3041" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3042" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3042" s="2" t="s">
         <v>9437</v>
       </c>
@@ -95807,7 +95786,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3043" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3043" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3043" s="2" t="s">
         <v>9438</v>
       </c>
@@ -95824,7 +95803,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3044" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3044" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3044" s="2" t="s">
         <v>9439</v>
       </c>
@@ -95841,7 +95820,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3045" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3045" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3045" s="2" t="s">
         <v>9440</v>
       </c>
@@ -95858,7 +95837,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3046" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3046" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3046" s="2" t="s">
         <v>9441</v>
       </c>
@@ -95875,7 +95854,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3047" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3047" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3047" s="2" t="s">
         <v>9442</v>
       </c>
@@ -95892,7 +95871,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3048" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3048" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3048" s="2" t="s">
         <v>9443</v>
       </c>
@@ -95909,7 +95888,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3049" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3049" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3049" s="2" t="s">
         <v>9444</v>
       </c>
@@ -95926,7 +95905,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3050" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3050" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3050" s="2" t="s">
         <v>9445</v>
       </c>
@@ -95943,7 +95922,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3051" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3051" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3051" s="2" t="s">
         <v>9446</v>
       </c>
@@ -95960,7 +95939,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3052" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3052" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3052" s="2" t="s">
         <v>9447</v>
       </c>
@@ -95977,7 +95956,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3053" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3053" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3053" s="2" t="s">
         <v>9448</v>
       </c>
@@ -95994,7 +95973,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3054" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3054" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3054" s="2" t="s">
         <v>9449</v>
       </c>
@@ -96011,7 +95990,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3055" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3055" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3055" s="2" t="s">
         <v>9450</v>
       </c>
@@ -96028,7 +96007,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3056" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3056" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3056" s="2" t="s">
         <v>9451</v>
       </c>
@@ -96334,25 +96313,8 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3074" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3074" s="2" t="s">
-        <v>9469</v>
-      </c>
-      <c r="C3074" s="2" t="s">
-        <v>9436</v>
-      </c>
-      <c r="D3074" s="2" t="s">
-        <v>2643</v>
-      </c>
-      <c r="E3074" s="2" t="s">
-        <v>9502</v>
-      </c>
-      <c r="J3074" s="2" t="s">
-        <v>2644</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P3041" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}"/>
+  <autoFilter ref="A1:P3073" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}"/>
   <conditionalFormatting sqref="A1">
     <cfRule type="duplicateValues" dxfId="41" priority="111"/>
   </conditionalFormatting>
@@ -96376,8 +96338,8 @@
     <cfRule type="duplicateValues" dxfId="34" priority="101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B95">
-    <cfRule type="duplicateValues" dxfId="33" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B125">
     <cfRule type="duplicateValues" dxfId="31" priority="78"/>
@@ -96397,9 +96359,9 @@
     <cfRule type="duplicateValues" dxfId="25" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E400">
-    <cfRule type="duplicateValues" dxfId="24" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="11"/>
     <cfRule type="duplicateValues" dxfId="21" priority="12"/>
     <cfRule type="duplicateValues" dxfId="20" priority="13"/>
     <cfRule type="duplicateValues" dxfId="19" priority="14"/>
@@ -96407,23 +96369,23 @@
     <cfRule type="duplicateValues" dxfId="17" priority="16" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E837:E840">
-    <cfRule type="duplicateValues" dxfId="16" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="23" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="24" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="23" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="24" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3010">
-    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="7" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+  <conditionalFormatting sqref="E3009">
+    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="7" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="1" priority="8" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:I1">
